--- a/research/traditional_assets/database/data/jordan/jordan_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_retail_special_lines.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ase_jdfs" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.265</v>
+        <v>-0.07400000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-0.197</v>
       </c>
       <c r="G2">
-        <v>0.05140350877192982</v>
+        <v>0.03416557161629435</v>
       </c>
       <c r="H2">
-        <v>0.05140350877192982</v>
+        <v>0.03416557161629435</v>
       </c>
       <c r="I2">
-        <v>-0.5058479532163742</v>
+        <v>0.1655716162943495</v>
       </c>
       <c r="J2">
-        <v>-0.5058479532163742</v>
+        <v>0.1588325610346497</v>
       </c>
       <c r="K2">
-        <v>-8.32</v>
+        <v>10.9</v>
       </c>
       <c r="L2">
-        <v>-0.4865497076023392</v>
+        <v>0.1432325886990802</v>
       </c>
       <c r="M2">
-        <v>3.17</v>
+        <v>6.34</v>
       </c>
       <c r="N2">
-        <v>0.01280290791599354</v>
+        <v>0.02288808664259928</v>
       </c>
       <c r="O2">
-        <v>-0.3810096153846154</v>
+        <v>0.581651376146789</v>
       </c>
       <c r="P2">
-        <v>3.17</v>
+        <v>6.34</v>
       </c>
       <c r="Q2">
-        <v>0.01280290791599354</v>
+        <v>0.02288808664259928</v>
       </c>
       <c r="R2">
-        <v>-0.3810096153846154</v>
+        <v>0.581651376146789</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.3</v>
+        <v>34.1</v>
       </c>
       <c r="V2">
-        <v>0.07794830371567044</v>
+        <v>0.1231046931407942</v>
       </c>
       <c r="W2">
-        <v>-0.1131972789115646</v>
+        <v>0.1758064516129032</v>
       </c>
       <c r="X2">
-        <v>0.1092928424897272</v>
+        <v>0.1731026021607887</v>
       </c>
       <c r="Y2">
-        <v>-0.2224901214012919</v>
+        <v>0.002703849452114548</v>
       </c>
       <c r="Z2">
-        <v>0.293965961835998</v>
+        <v>1.510520047637951</v>
       </c>
       <c r="AA2">
-        <v>-0.1487020801100224</v>
+        <v>0.2399197676605169</v>
       </c>
       <c r="AB2">
-        <v>0.1076730513821734</v>
+        <v>0.1708400161109463</v>
       </c>
       <c r="AC2">
-        <v>-0.2563751314921958</v>
+        <v>0.06907975154957061</v>
       </c>
       <c r="AD2">
-        <v>7.68</v>
+        <v>7.86</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.68</v>
+        <v>7.86</v>
       </c>
       <c r="AG2">
-        <v>-11.62</v>
+        <v>-26.24</v>
       </c>
       <c r="AH2">
-        <v>0.03008461297398934</v>
+        <v>0.02759250157972337</v>
       </c>
       <c r="AI2">
-        <v>0.1102181400688863</v>
+        <v>0.1026645768025078</v>
       </c>
       <c r="AJ2">
-        <v>-0.04924146114077465</v>
+        <v>-0.1046418886584782</v>
       </c>
       <c r="AK2">
-        <v>-0.2306470821754665</v>
+        <v>-0.6179934055581724</v>
       </c>
       <c r="AL2">
-        <v>0.636</v>
+        <v>0.672</v>
       </c>
       <c r="AM2">
-        <v>0.01000000000000001</v>
+        <v>-0.02299999999999991</v>
       </c>
       <c r="AN2">
-        <v>-1.187017001545595</v>
+        <v>0.5205298013245033</v>
       </c>
       <c r="AO2">
-        <v>-13.60062893081761</v>
+        <v>18.75</v>
       </c>
       <c r="AP2">
-        <v>1.795981452859351</v>
+        <v>-1.737748344370861</v>
       </c>
       <c r="AQ2">
-        <v>-864.9999999999993</v>
+        <v>-547.8260869565239</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.265</v>
+        <v>-0.07400000000000001</v>
+      </c>
+      <c r="E3">
+        <v>-0.197</v>
       </c>
       <c r="G3">
-        <v>0.05140350877192982</v>
+        <v>0.03416557161629435</v>
       </c>
       <c r="H3">
-        <v>0.05140350877192982</v>
+        <v>0.03416557161629435</v>
       </c>
       <c r="I3">
-        <v>-0.5058479532163742</v>
+        <v>0.1655716162943495</v>
       </c>
       <c r="J3">
-        <v>-0.5058479532163742</v>
+        <v>0.1588325610346497</v>
       </c>
       <c r="K3">
-        <v>-8.32</v>
+        <v>10.9</v>
       </c>
       <c r="L3">
-        <v>-0.4865497076023392</v>
+        <v>0.1432325886990802</v>
       </c>
       <c r="M3">
-        <v>3.17</v>
+        <v>6.34</v>
       </c>
       <c r="N3">
-        <v>0.01280290791599354</v>
+        <v>0.02288808664259928</v>
       </c>
       <c r="O3">
-        <v>-0.3810096153846154</v>
+        <v>0.581651376146789</v>
       </c>
       <c r="P3">
-        <v>3.17</v>
+        <v>6.34</v>
       </c>
       <c r="Q3">
-        <v>0.01280290791599354</v>
+        <v>0.02288808664259928</v>
       </c>
       <c r="R3">
-        <v>-0.3810096153846154</v>
+        <v>0.581651376146789</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.3</v>
+        <v>34.1</v>
       </c>
       <c r="V3">
-        <v>0.07794830371567044</v>
+        <v>0.1231046931407942</v>
       </c>
       <c r="W3">
-        <v>-0.1131972789115646</v>
+        <v>0.1758064516129032</v>
       </c>
       <c r="X3">
-        <v>0.1092928424897272</v>
+        <v>0.1731026021607887</v>
       </c>
       <c r="Y3">
-        <v>-0.2224901214012919</v>
+        <v>0.002703849452114548</v>
       </c>
       <c r="Z3">
-        <v>0.293965961835998</v>
+        <v>1.510520047637951</v>
       </c>
       <c r="AA3">
-        <v>-0.1487020801100224</v>
+        <v>0.2399197676605169</v>
       </c>
       <c r="AB3">
-        <v>0.1076730513821734</v>
+        <v>0.1708400161109463</v>
       </c>
       <c r="AC3">
-        <v>-0.2563751314921958</v>
+        <v>0.06907975154957061</v>
       </c>
       <c r="AD3">
-        <v>7.68</v>
+        <v>7.86</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.68</v>
+        <v>7.86</v>
       </c>
       <c r="AG3">
-        <v>-11.62</v>
+        <v>-26.24</v>
       </c>
       <c r="AH3">
-        <v>0.03008461297398934</v>
+        <v>0.02759250157972337</v>
       </c>
       <c r="AI3">
-        <v>0.1102181400688863</v>
+        <v>0.1026645768025078</v>
       </c>
       <c r="AJ3">
-        <v>-0.04924146114077465</v>
+        <v>-0.1046418886584782</v>
       </c>
       <c r="AK3">
-        <v>-0.2306470821754665</v>
+        <v>-0.6179934055581724</v>
       </c>
       <c r="AL3">
-        <v>0.636</v>
+        <v>0.672</v>
       </c>
       <c r="AM3">
-        <v>0.01000000000000001</v>
+        <v>-0.02299999999999991</v>
       </c>
       <c r="AN3">
-        <v>-1.187017001545595</v>
+        <v>0.5205298013245033</v>
       </c>
       <c r="AO3">
-        <v>-13.60062893081761</v>
+        <v>18.75</v>
       </c>
       <c r="AP3">
-        <v>1.795981452859351</v>
+        <v>-1.737748344370861</v>
       </c>
       <c r="AQ3">
-        <v>-864.9999999999993</v>
+        <v>-547.8260869565239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jordanian Duty Free Shops (ASE:JDFS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASE:JDFS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Retail (Special Lines)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0275925015797234</v>
+      </c>
+      <c r="F2">
+        <v>0.17</v>
+      </c>
+      <c r="G2">
+        <v>277</v>
+      </c>
+      <c r="H2">
+        <v>244.873683144338</v>
+      </c>
+      <c r="I2">
+        <v>250.76</v>
+      </c>
+      <c r="J2">
+        <v>259.199883144337</v>
+      </c>
+      <c r="K2">
+        <v>7.86</v>
+      </c>
+      <c r="L2">
+        <v>48.4262</v>
+      </c>
+      <c r="M2">
+        <v>0.170840016110946</v>
+      </c>
+      <c r="N2">
+        <v>0.166540622558626</v>
+      </c>
+      <c r="O2">
+        <v>0.0911025688073395</v>
+      </c>
+      <c r="P2">
+        <v>0.044</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.173102602160789</v>
+      </c>
+      <c r="T2">
+        <v>0.191639304287502</v>
+      </c>
+      <c r="U2">
+        <v>0.981478118122463</v>
+      </c>
+      <c r="V2">
+        <v>1.11694360595971</v>
+      </c>
+      <c r="W2">
+        <v>4.606822527700068</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>277</v>
+      </c>
+      <c r="AB2">
+        <v>0.1368370824381754</v>
+      </c>
+      <c r="AC2">
+        <v>0.1138782110091743</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>15.1</v>
+      </c>
+      <c r="AH2">
+        <v>2.83</v>
+      </c>
+      <c r="AI2">
+        <v>1.650000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>7.86</v>
+      </c>
+      <c r="AK2">
+        <v>7.86</v>
+      </c>
+      <c r="AL2">
+        <v>0.672</v>
+      </c>
+      <c r="AM2">
+        <v>7.859999999999999</v>
+      </c>
+      <c r="AN2">
+        <v>34.1</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1701215554437126</v>
+      </c>
+      <c r="C2">
+        <v>286.2319087952224</v>
+      </c>
+      <c r="D2">
+        <v>252.1319087952224</v>
+      </c>
+      <c r="E2">
+        <v>-7.86</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>34.1</v>
+      </c>
+      <c r="H2">
+        <v>277</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>15.1</v>
+      </c>
+      <c r="K2">
+        <v>2.83</v>
+      </c>
+      <c r="L2">
+        <v>12.27</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.27</v>
+      </c>
+      <c r="O2">
+        <v>2.453999999999999</v>
+      </c>
+      <c r="P2">
+        <v>9.816000000000001</v>
+      </c>
+      <c r="Q2">
+        <v>12.646</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1701215554437126</v>
+      </c>
+      <c r="T2">
+        <v>0.9596927463214898</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1698365123328252</v>
+      </c>
+      <c r="C3">
+        <v>283.9317701542552</v>
+      </c>
+      <c r="D3">
+        <v>252.6803701542551</v>
+      </c>
+      <c r="E3">
+        <v>-5.0114</v>
+      </c>
+      <c r="F3">
+        <v>2.8486</v>
+      </c>
+      <c r="G3">
+        <v>34.1</v>
+      </c>
+      <c r="H3">
+        <v>277</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>15.1</v>
+      </c>
+      <c r="K3">
+        <v>2.83</v>
+      </c>
+      <c r="L3">
+        <v>12.27</v>
+      </c>
+      <c r="M3">
+        <v>0.13018102</v>
+      </c>
+      <c r="N3">
+        <v>12.13981898</v>
+      </c>
+      <c r="O3">
+        <v>2.427963795999999</v>
+      </c>
+      <c r="P3">
+        <v>9.711855184000001</v>
+      </c>
+      <c r="Q3">
+        <v>12.541855184</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1711827397301265</v>
+      </c>
+      <c r="T3">
+        <v>0.9674478392210575</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>94.25337119036243</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1695514692219378</v>
+      </c>
+      <c r="C4">
+        <v>281.6340228459882</v>
+      </c>
+      <c r="D4">
+        <v>253.2312228459882</v>
+      </c>
+      <c r="E4">
+        <v>-2.1628</v>
+      </c>
+      <c r="F4">
+        <v>5.6972</v>
+      </c>
+      <c r="G4">
+        <v>34.1</v>
+      </c>
+      <c r="H4">
+        <v>277</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>15.1</v>
+      </c>
+      <c r="K4">
+        <v>2.83</v>
+      </c>
+      <c r="L4">
+        <v>12.27</v>
+      </c>
+      <c r="M4">
+        <v>0.2603620400000001</v>
+      </c>
+      <c r="N4">
+        <v>12.00963796</v>
+      </c>
+      <c r="O4">
+        <v>2.401927591999999</v>
+      </c>
+      <c r="P4">
+        <v>9.607710367999999</v>
+      </c>
+      <c r="Q4">
+        <v>12.437710368</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.172265580838712</v>
+      </c>
+      <c r="T4">
+        <v>0.975361199322657</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>47.12668559518121</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1692664261110504</v>
+      </c>
+      <c r="C5">
+        <v>279.338682544176</v>
+      </c>
+      <c r="D5">
+        <v>253.784482544176</v>
+      </c>
+      <c r="E5">
+        <v>0.6857999999999995</v>
+      </c>
+      <c r="F5">
+        <v>8.5458</v>
+      </c>
+      <c r="G5">
+        <v>34.1</v>
+      </c>
+      <c r="H5">
+        <v>277</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>15.1</v>
+      </c>
+      <c r="K5">
+        <v>2.83</v>
+      </c>
+      <c r="L5">
+        <v>12.27</v>
+      </c>
+      <c r="M5">
+        <v>0.3905430600000001</v>
+      </c>
+      <c r="N5">
+        <v>11.87945694</v>
+      </c>
+      <c r="O5">
+        <v>2.375891387999999</v>
+      </c>
+      <c r="P5">
+        <v>9.503565552</v>
+      </c>
+      <c r="Q5">
+        <v>12.333565552</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1733707485680931</v>
+      </c>
+      <c r="T5">
+        <v>0.983437721488207</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>31.41779039678748</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1689813830001629</v>
+      </c>
+      <c r="C6">
+        <v>277.0457650598492</v>
+      </c>
+      <c r="D6">
+        <v>254.3401650598492</v>
+      </c>
+      <c r="E6">
+        <v>3.534400000000001</v>
+      </c>
+      <c r="F6">
+        <v>11.3944</v>
+      </c>
+      <c r="G6">
+        <v>34.1</v>
+      </c>
+      <c r="H6">
+        <v>277</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>15.1</v>
+      </c>
+      <c r="K6">
+        <v>2.83</v>
+      </c>
+      <c r="L6">
+        <v>12.27</v>
+      </c>
+      <c r="M6">
+        <v>0.5207240800000001</v>
+      </c>
+      <c r="N6">
+        <v>11.74927592</v>
+      </c>
+      <c r="O6">
+        <v>2.349855183999999</v>
+      </c>
+      <c r="P6">
+        <v>9.399420736</v>
+      </c>
+      <c r="Q6">
+        <v>12.229420736</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1744989406251697</v>
+      </c>
+      <c r="T6">
+        <v>0.9916825045322063</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>23.56334279759061</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1686963398892755</v>
+      </c>
+      <c r="C7">
+        <v>274.7552863428206</v>
+      </c>
+      <c r="D7">
+        <v>254.8982863428205</v>
+      </c>
+      <c r="E7">
+        <v>6.383000000000002</v>
+      </c>
+      <c r="F7">
+        <v>14.243</v>
+      </c>
+      <c r="G7">
+        <v>34.1</v>
+      </c>
+      <c r="H7">
+        <v>277</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>15.1</v>
+      </c>
+      <c r="K7">
+        <v>2.83</v>
+      </c>
+      <c r="L7">
+        <v>12.27</v>
+      </c>
+      <c r="M7">
+        <v>0.6509051000000001</v>
+      </c>
+      <c r="N7">
+        <v>11.6190949</v>
+      </c>
+      <c r="O7">
+        <v>2.32381898</v>
+      </c>
+      <c r="P7">
+        <v>9.295275920000002</v>
+      </c>
+      <c r="Q7">
+        <v>12.12527592</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1756508840939742</v>
+      </c>
+      <c r="T7">
+        <v>1.000100861956079</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>18.85067423807249</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1684112967783881</v>
+      </c>
+      <c r="C8">
+        <v>272.467262483211</v>
+      </c>
+      <c r="D8">
+        <v>255.458862483211</v>
+      </c>
+      <c r="E8">
+        <v>9.2316</v>
+      </c>
+      <c r="F8">
+        <v>17.0916</v>
+      </c>
+      <c r="G8">
+        <v>34.1</v>
+      </c>
+      <c r="H8">
+        <v>277</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>15.1</v>
+      </c>
+      <c r="K8">
+        <v>2.83</v>
+      </c>
+      <c r="L8">
+        <v>12.27</v>
+      </c>
+      <c r="M8">
+        <v>0.7810861200000001</v>
+      </c>
+      <c r="N8">
+        <v>11.48891388</v>
+      </c>
+      <c r="O8">
+        <v>2.297782776</v>
+      </c>
+      <c r="P8">
+        <v>9.191131104</v>
+      </c>
+      <c r="Q8">
+        <v>12.021131104</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1768273369982852</v>
+      </c>
+      <c r="T8">
+        <v>1.008698333367694</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>15.70889519839374</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1681262536675007</v>
+      </c>
+      <c r="C9">
+        <v>270.1817097129961</v>
+      </c>
+      <c r="D9">
+        <v>256.0219097129961</v>
+      </c>
+      <c r="E9">
+        <v>12.0802</v>
+      </c>
+      <c r="F9">
+        <v>19.9402</v>
+      </c>
+      <c r="G9">
+        <v>34.1</v>
+      </c>
+      <c r="H9">
+        <v>277</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>15.1</v>
+      </c>
+      <c r="K9">
+        <v>2.83</v>
+      </c>
+      <c r="L9">
+        <v>12.27</v>
+      </c>
+      <c r="M9">
+        <v>0.9112671400000003</v>
+      </c>
+      <c r="N9">
+        <v>11.35873286</v>
+      </c>
+      <c r="O9">
+        <v>2.271746572</v>
+      </c>
+      <c r="P9">
+        <v>9.086986288</v>
+      </c>
+      <c r="Q9">
+        <v>11.916986288</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1780290899650545</v>
+      </c>
+      <c r="T9">
+        <v>1.017480696637623</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>13.46476731290892</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1679436105566132</v>
+      </c>
+      <c r="C10">
+        <v>267.695192187257</v>
+      </c>
+      <c r="D10">
+        <v>256.383992187257</v>
+      </c>
+      <c r="E10">
+        <v>14.9288</v>
+      </c>
+      <c r="F10">
+        <v>22.7888</v>
+      </c>
+      <c r="G10">
+        <v>34.1</v>
+      </c>
+      <c r="H10">
+        <v>277</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>15.1</v>
+      </c>
+      <c r="K10">
+        <v>2.83</v>
+      </c>
+      <c r="L10">
+        <v>12.27</v>
+      </c>
+      <c r="M10">
+        <v>1.07791024</v>
+      </c>
+      <c r="N10">
+        <v>11.19208976</v>
+      </c>
+      <c r="O10">
+        <v>2.238417951999999</v>
+      </c>
+      <c r="P10">
+        <v>8.953671808000001</v>
+      </c>
+      <c r="Q10">
+        <v>11.783671808</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1792569679963187</v>
+      </c>
+      <c r="T10">
+        <v>1.026453980848202</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.38313705972401</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1679449674457258</v>
+      </c>
+      <c r="C11">
+        <v>264.8438984342249</v>
+      </c>
+      <c r="D11">
+        <v>256.3812984342248</v>
+      </c>
+      <c r="E11">
+        <v>17.7774</v>
+      </c>
+      <c r="F11">
+        <v>25.6374</v>
+      </c>
+      <c r="G11">
+        <v>34.1</v>
+      </c>
+      <c r="H11">
+        <v>277</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>15.1</v>
+      </c>
+      <c r="K11">
+        <v>2.83</v>
+      </c>
+      <c r="L11">
+        <v>12.27</v>
+      </c>
+      <c r="M11">
+        <v>1.31007114</v>
+      </c>
+      <c r="N11">
+        <v>10.95992886</v>
+      </c>
+      <c r="O11">
+        <v>2.191985771999999</v>
+      </c>
+      <c r="P11">
+        <v>8.767943088000001</v>
+      </c>
+      <c r="Q11">
+        <v>11.597943088</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1805118323579405</v>
+      </c>
+      <c r="T11">
+        <v>1.035624480096377</v>
+      </c>
+      <c r="U11">
+        <v>0.0511</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.04088</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>9.36590359512843</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1677031243348384</v>
+      </c>
+      <c r="C12">
+        <v>262.4763112188772</v>
+      </c>
+      <c r="D12">
+        <v>256.8623112188772</v>
+      </c>
+      <c r="E12">
+        <v>20.626</v>
+      </c>
+      <c r="F12">
+        <v>28.486</v>
+      </c>
+      <c r="G12">
+        <v>34.1</v>
+      </c>
+      <c r="H12">
+        <v>277</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>15.1</v>
+      </c>
+      <c r="K12">
+        <v>2.83</v>
+      </c>
+      <c r="L12">
+        <v>12.27</v>
+      </c>
+      <c r="M12">
+        <v>1.4556346</v>
+      </c>
+      <c r="N12">
+        <v>10.8143654</v>
+      </c>
+      <c r="O12">
+        <v>2.162873079999999</v>
+      </c>
+      <c r="P12">
+        <v>8.651492320000001</v>
+      </c>
+      <c r="Q12">
+        <v>11.48149232</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1817945825942649</v>
+      </c>
+      <c r="T12">
+        <v>1.044998768216733</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.04088</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.429313235615584</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.167628481223951</v>
+      </c>
+      <c r="C13">
+        <v>259.7765370204155</v>
+      </c>
+      <c r="D13">
+        <v>257.0111370204155</v>
+      </c>
+      <c r="E13">
+        <v>23.4746</v>
+      </c>
+      <c r="F13">
+        <v>31.3346</v>
+      </c>
+      <c r="G13">
+        <v>34.1</v>
+      </c>
+      <c r="H13">
+        <v>277</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>15.1</v>
+      </c>
+      <c r="K13">
+        <v>2.83</v>
+      </c>
+      <c r="L13">
+        <v>12.27</v>
+      </c>
+      <c r="M13">
+        <v>1.6607338</v>
+      </c>
+      <c r="N13">
+        <v>10.6092662</v>
+      </c>
+      <c r="O13">
+        <v>2.121853239999999</v>
+      </c>
+      <c r="P13">
+        <v>8.48741296</v>
+      </c>
+      <c r="Q13">
+        <v>11.31741296</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1831061586785966</v>
+      </c>
+      <c r="T13">
+        <v>1.054583714497098</v>
+      </c>
+      <c r="U13">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>7.388300280273694</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1674018381130636</v>
+      </c>
+      <c r="C14">
+        <v>257.3808839182336</v>
+      </c>
+      <c r="D14">
+        <v>257.4640839182336</v>
+      </c>
+      <c r="E14">
+        <v>26.3232</v>
+      </c>
+      <c r="F14">
+        <v>34.1832</v>
+      </c>
+      <c r="G14">
+        <v>34.1</v>
+      </c>
+      <c r="H14">
+        <v>277</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>15.1</v>
+      </c>
+      <c r="K14">
+        <v>2.83</v>
+      </c>
+      <c r="L14">
+        <v>12.27</v>
+      </c>
+      <c r="M14">
+        <v>1.8117096</v>
+      </c>
+      <c r="N14">
+        <v>10.4582904</v>
+      </c>
+      <c r="O14">
+        <v>2.091658079999999</v>
+      </c>
+      <c r="P14">
+        <v>8.366632320000001</v>
+      </c>
+      <c r="Q14">
+        <v>11.19663232</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1844475433102995</v>
+      </c>
+      <c r="T14">
+        <v>1.064386500465652</v>
+      </c>
+      <c r="U14">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.772608590250887</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1671751950021761</v>
+      </c>
+      <c r="C15">
+        <v>254.9868301482902</v>
+      </c>
+      <c r="D15">
+        <v>257.9186301482902</v>
+      </c>
+      <c r="E15">
+        <v>29.1718</v>
+      </c>
+      <c r="F15">
+        <v>37.0318</v>
+      </c>
+      <c r="G15">
+        <v>34.1</v>
+      </c>
+      <c r="H15">
+        <v>277</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>15.1</v>
+      </c>
+      <c r="K15">
+        <v>2.83</v>
+      </c>
+      <c r="L15">
+        <v>12.27</v>
+      </c>
+      <c r="M15">
+        <v>1.9626854</v>
+      </c>
+      <c r="N15">
+        <v>10.3073146</v>
+      </c>
+      <c r="O15">
+        <v>2.061462919999999</v>
+      </c>
+      <c r="P15">
+        <v>8.245851680000001</v>
+      </c>
+      <c r="Q15">
+        <v>11.07585168</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1858197643703174</v>
+      </c>
+      <c r="T15">
+        <v>1.074414637835783</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.251638698693126</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1671725518912887</v>
+      </c>
+      <c r="C16">
+        <v>252.143540532242</v>
+      </c>
+      <c r="D16">
+        <v>257.9239405322419</v>
+      </c>
+      <c r="E16">
+        <v>32.02040000000001</v>
+      </c>
+      <c r="F16">
+        <v>39.88040000000001</v>
+      </c>
+      <c r="G16">
+        <v>34.1</v>
+      </c>
+      <c r="H16">
+        <v>277</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>15.1</v>
+      </c>
+      <c r="K16">
+        <v>2.83</v>
+      </c>
+      <c r="L16">
+        <v>12.27</v>
+      </c>
+      <c r="M16">
+        <v>2.193422</v>
+      </c>
+      <c r="N16">
+        <v>10.076578</v>
+      </c>
+      <c r="O16">
+        <v>2.0153156</v>
+      </c>
+      <c r="P16">
+        <v>8.0612624</v>
+      </c>
+      <c r="Q16">
+        <v>10.8912624</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1872238975480101</v>
+      </c>
+      <c r="T16">
+        <v>1.084675987702893</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.044</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.593998783635797</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1669619087804012</v>
+      </c>
+      <c r="C17">
+        <v>249.7188566686594</v>
+      </c>
+      <c r="D17">
+        <v>258.3478566686593</v>
+      </c>
+      <c r="E17">
+        <v>34.869</v>
+      </c>
+      <c r="F17">
+        <v>42.729</v>
+      </c>
+      <c r="G17">
+        <v>34.1</v>
+      </c>
+      <c r="H17">
+        <v>277</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>15.1</v>
+      </c>
+      <c r="K17">
+        <v>2.83</v>
+      </c>
+      <c r="L17">
+        <v>12.27</v>
+      </c>
+      <c r="M17">
+        <v>2.350095</v>
+      </c>
+      <c r="N17">
+        <v>9.919905</v>
+      </c>
+      <c r="O17">
+        <v>1.983981</v>
+      </c>
+      <c r="P17">
+        <v>7.935924</v>
+      </c>
+      <c r="Q17">
+        <v>10.765924</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1886610691534132</v>
+      </c>
+      <c r="T17">
+        <v>1.095178781096288</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.044</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.221065531393411</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1667512656695138</v>
+      </c>
+      <c r="C18">
+        <v>247.2955685710858</v>
+      </c>
+      <c r="D18">
+        <v>258.7731685710858</v>
+      </c>
+      <c r="E18">
+        <v>37.7176</v>
+      </c>
+      <c r="F18">
+        <v>45.5776</v>
+      </c>
+      <c r="G18">
+        <v>34.1</v>
+      </c>
+      <c r="H18">
+        <v>277</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>15.1</v>
+      </c>
+      <c r="K18">
+        <v>2.83</v>
+      </c>
+      <c r="L18">
+        <v>12.27</v>
+      </c>
+      <c r="M18">
+        <v>2.506768</v>
+      </c>
+      <c r="N18">
+        <v>9.763231999999999</v>
+      </c>
+      <c r="O18">
+        <v>1.952646399999999</v>
+      </c>
+      <c r="P18">
+        <v>7.8105856</v>
+      </c>
+      <c r="Q18">
+        <v>10.6405856</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1901324591303736</v>
+      </c>
+      <c r="T18">
+        <v>1.10593164099905</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.044</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.894748935681323</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1665406225586264</v>
+      </c>
+      <c r="C19">
+        <v>244.8736831443375</v>
+      </c>
+      <c r="D19">
+        <v>259.1998831443375</v>
+      </c>
+      <c r="E19">
+        <v>40.56620000000001</v>
+      </c>
+      <c r="F19">
+        <v>48.42620000000001</v>
+      </c>
+      <c r="G19">
+        <v>34.1</v>
+      </c>
+      <c r="H19">
+        <v>277</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>15.1</v>
+      </c>
+      <c r="K19">
+        <v>2.83</v>
+      </c>
+      <c r="L19">
+        <v>12.27</v>
+      </c>
+      <c r="M19">
+        <v>2.663441000000001</v>
+      </c>
+      <c r="N19">
+        <v>9.606558999999999</v>
+      </c>
+      <c r="O19">
+        <v>1.921311799999999</v>
+      </c>
+      <c r="P19">
+        <v>7.685247199999999</v>
+      </c>
+      <c r="Q19">
+        <v>10.5152472</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1916393042875017</v>
+      </c>
+      <c r="T19">
+        <v>1.11694360595971</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.044</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.606822527700068</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.166877179447739</v>
+      </c>
+      <c r="C20">
+        <v>241.343966440288</v>
+      </c>
+      <c r="D20">
+        <v>258.5187664402879</v>
+      </c>
+      <c r="E20">
+        <v>43.4148</v>
+      </c>
+      <c r="F20">
+        <v>51.2748</v>
+      </c>
+      <c r="G20">
+        <v>34.1</v>
+      </c>
+      <c r="H20">
+        <v>277</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>15.1</v>
+      </c>
+      <c r="K20">
+        <v>2.83</v>
+      </c>
+      <c r="L20">
+        <v>12.27</v>
+      </c>
+      <c r="M20">
+        <v>3.01495824</v>
+      </c>
+      <c r="N20">
+        <v>9.255041759999999</v>
+      </c>
+      <c r="O20">
+        <v>1.851008351999999</v>
+      </c>
+      <c r="P20">
+        <v>7.404033408</v>
+      </c>
+      <c r="Q20">
+        <v>10.234033408</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1931829017655353</v>
+      </c>
+      <c r="T20">
+        <v>1.128224155431605</v>
+      </c>
+      <c r="U20">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.069708109787948</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1673353363368516</v>
+      </c>
+      <c r="C21">
+        <v>237.5738910142689</v>
+      </c>
+      <c r="D21">
+        <v>257.5972910142689</v>
+      </c>
+      <c r="E21">
+        <v>46.2634</v>
+      </c>
+      <c r="F21">
+        <v>54.1234</v>
+      </c>
+      <c r="G21">
+        <v>34.1</v>
+      </c>
+      <c r="H21">
+        <v>277</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>15.1</v>
+      </c>
+      <c r="K21">
+        <v>2.83</v>
+      </c>
+      <c r="L21">
+        <v>12.27</v>
+      </c>
+      <c r="M21">
+        <v>3.4097742</v>
+      </c>
+      <c r="N21">
+        <v>8.860225799999998</v>
+      </c>
+      <c r="O21">
+        <v>1.772045159999999</v>
+      </c>
+      <c r="P21">
+        <v>7.088180639999999</v>
+      </c>
+      <c r="Q21">
+        <v>9.918180639999999</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1947646127615451</v>
+      </c>
+      <c r="T21">
+        <v>1.139783236989226</v>
+      </c>
+      <c r="U21">
+        <v>0.063</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.0504</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.598478749707238</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1683246932259641</v>
+      </c>
+      <c r="C22">
+        <v>232.7576688710758</v>
+      </c>
+      <c r="D22">
+        <v>255.6296688710758</v>
+      </c>
+      <c r="E22">
+        <v>49.11200000000001</v>
+      </c>
+      <c r="F22">
+        <v>56.97200000000001</v>
+      </c>
+      <c r="G22">
+        <v>34.1</v>
+      </c>
+      <c r="H22">
+        <v>277</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>15.1</v>
+      </c>
+      <c r="K22">
+        <v>2.83</v>
+      </c>
+      <c r="L22">
+        <v>12.27</v>
+      </c>
+      <c r="M22">
+        <v>3.9937372</v>
+      </c>
+      <c r="N22">
+        <v>8.2762628</v>
+      </c>
+      <c r="O22">
+        <v>1.65525256</v>
+      </c>
+      <c r="P22">
+        <v>6.62101024</v>
+      </c>
+      <c r="Q22">
+        <v>9.45101024</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1963858665324552</v>
+      </c>
+      <c r="T22">
+        <v>1.151631295585788</v>
+      </c>
+      <c r="U22">
+        <v>0.0701</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.05608</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.072310316262171</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1718132501150767</v>
+      </c>
+      <c r="C23">
+        <v>223.2046342254278</v>
+      </c>
+      <c r="D23">
+        <v>248.9252342254278</v>
+      </c>
+      <c r="E23">
+        <v>51.9606</v>
+      </c>
+      <c r="F23">
+        <v>59.8206</v>
+      </c>
+      <c r="G23">
+        <v>34.1</v>
+      </c>
+      <c r="H23">
+        <v>277</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>15.1</v>
+      </c>
+      <c r="K23">
+        <v>2.83</v>
+      </c>
+      <c r="L23">
+        <v>12.27</v>
+      </c>
+      <c r="M23">
+        <v>5.467602840000001</v>
+      </c>
+      <c r="N23">
+        <v>6.802397159999999</v>
+      </c>
+      <c r="O23">
+        <v>1.360479432</v>
+      </c>
+      <c r="P23">
+        <v>5.441917728</v>
+      </c>
+      <c r="Q23">
+        <v>8.271917728</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1980481647026288</v>
+      </c>
+      <c r="T23">
+        <v>1.163779305032895</v>
+      </c>
+      <c r="U23">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.07312</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.24412788548482</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1718938070041893</v>
+      </c>
+      <c r="C24">
+        <v>220.2053687441242</v>
+      </c>
+      <c r="D24">
+        <v>248.7745687441242</v>
+      </c>
+      <c r="E24">
+        <v>54.8092</v>
+      </c>
+      <c r="F24">
+        <v>62.6692</v>
+      </c>
+      <c r="G24">
+        <v>34.1</v>
+      </c>
+      <c r="H24">
+        <v>277</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>15.1</v>
+      </c>
+      <c r="K24">
+        <v>2.83</v>
+      </c>
+      <c r="L24">
+        <v>12.27</v>
+      </c>
+      <c r="M24">
+        <v>5.727964880000001</v>
+      </c>
+      <c r="N24">
+        <v>6.542035119999999</v>
+      </c>
+      <c r="O24">
+        <v>1.308407023999999</v>
+      </c>
+      <c r="P24">
+        <v>5.233628095999999</v>
+      </c>
+      <c r="Q24">
+        <v>8.063628095999999</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1997530859028068</v>
+      </c>
+      <c r="T24">
+        <v>1.176238801901724</v>
+      </c>
+      <c r="U24">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.07312</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.142122072508237</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1719743638933019</v>
+      </c>
+      <c r="C25">
+        <v>217.2062855372781</v>
+      </c>
+      <c r="D25">
+        <v>248.6240855372781</v>
+      </c>
+      <c r="E25">
+        <v>57.65780000000001</v>
+      </c>
+      <c r="F25">
+        <v>65.51780000000001</v>
+      </c>
+      <c r="G25">
+        <v>34.1</v>
+      </c>
+      <c r="H25">
+        <v>277</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>15.1</v>
+      </c>
+      <c r="K25">
+        <v>2.83</v>
+      </c>
+      <c r="L25">
+        <v>12.27</v>
+      </c>
+      <c r="M25">
+        <v>5.988326920000001</v>
+      </c>
+      <c r="N25">
+        <v>6.281673079999998</v>
+      </c>
+      <c r="O25">
+        <v>1.256334615999999</v>
+      </c>
+      <c r="P25">
+        <v>5.025338463999999</v>
+      </c>
+      <c r="Q25">
+        <v>7.855338463999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2015022907705219</v>
+      </c>
+      <c r="T25">
+        <v>1.189021922065846</v>
+      </c>
+      <c r="U25">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.07312</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.04898633022527</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1761061207824144</v>
+      </c>
+      <c r="C26">
+        <v>206.8761962026124</v>
+      </c>
+      <c r="D26">
+        <v>241.1425962026124</v>
+      </c>
+      <c r="E26">
+        <v>60.5064</v>
+      </c>
+      <c r="F26">
+        <v>68.3664</v>
+      </c>
+      <c r="G26">
+        <v>34.1</v>
+      </c>
+      <c r="H26">
+        <v>277</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>15.1</v>
+      </c>
+      <c r="K26">
+        <v>2.83</v>
+      </c>
+      <c r="L26">
+        <v>12.27</v>
+      </c>
+      <c r="M26">
+        <v>7.69122</v>
+      </c>
+      <c r="N26">
+        <v>4.578779999999999</v>
+      </c>
+      <c r="O26">
+        <v>0.9157559999999997</v>
+      </c>
+      <c r="P26">
+        <v>3.663024</v>
+      </c>
+      <c r="Q26">
+        <v>6.493024</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2032975273452821</v>
+      </c>
+      <c r="T26">
+        <v>1.202141440129024</v>
+      </c>
+      <c r="U26">
+        <v>0.1125</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>1.595325579036876</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.176355477671527</v>
+      </c>
+      <c r="C27">
+        <v>203.5904593568868</v>
+      </c>
+      <c r="D27">
+        <v>240.7054593568868</v>
+      </c>
+      <c r="E27">
+        <v>63.355</v>
+      </c>
+      <c r="F27">
+        <v>71.215</v>
+      </c>
+      <c r="G27">
+        <v>34.1</v>
+      </c>
+      <c r="H27">
+        <v>277</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>15.1</v>
+      </c>
+      <c r="K27">
+        <v>2.83</v>
+      </c>
+      <c r="L27">
+        <v>12.27</v>
+      </c>
+      <c r="M27">
+        <v>8.011687500000001</v>
+      </c>
+      <c r="N27">
+        <v>4.258312499999999</v>
+      </c>
+      <c r="O27">
+        <v>0.8516624999999995</v>
+      </c>
+      <c r="P27">
+        <v>3.406649999999999</v>
+      </c>
+      <c r="Q27">
+        <v>6.236649999999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2051406368953693</v>
+      </c>
+      <c r="T27">
+        <v>1.21561081200722</v>
+      </c>
+      <c r="U27">
+        <v>0.1125</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.531512555875401</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1967804563353132</v>
+      </c>
+      <c r="C28">
+        <v>169.6215297562037</v>
+      </c>
+      <c r="D28">
+        <v>209.5851297562037</v>
+      </c>
+      <c r="E28">
+        <v>66.20360000000001</v>
+      </c>
+      <c r="F28">
+        <v>74.06360000000001</v>
+      </c>
+      <c r="G28">
+        <v>34.1</v>
+      </c>
+      <c r="H28">
+        <v>277</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>15.1</v>
+      </c>
+      <c r="K28">
+        <v>2.83</v>
+      </c>
+      <c r="L28">
+        <v>12.27</v>
+      </c>
+      <c r="M28">
+        <v>14.56090376</v>
+      </c>
+      <c r="N28">
+        <v>-2.290903760000003</v>
+      </c>
+      <c r="O28">
+        <v>-0.4581807520000004</v>
+      </c>
+      <c r="P28">
+        <v>-1.832723008000002</v>
+      </c>
+      <c r="Q28">
+        <v>0.997276991999998</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2084854249488004</v>
+      </c>
+      <c r="T28">
+        <v>1.240054391144055</v>
+      </c>
+      <c r="U28">
+        <v>0.1966</v>
+      </c>
+      <c r="V28">
+        <v>0.1685334949291636</v>
+      </c>
+      <c r="W28">
+        <v>0.1634663148969264</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.8426674746458181</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1983584563353132</v>
+      </c>
+      <c r="C29">
+        <v>164.7001763443741</v>
+      </c>
+      <c r="D29">
+        <v>207.5123763443741</v>
+      </c>
+      <c r="E29">
+        <v>69.05220000000001</v>
+      </c>
+      <c r="F29">
+        <v>76.91220000000001</v>
+      </c>
+      <c r="G29">
+        <v>34.1</v>
+      </c>
+      <c r="H29">
+        <v>277</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>15.1</v>
+      </c>
+      <c r="K29">
+        <v>2.83</v>
+      </c>
+      <c r="L29">
+        <v>12.27</v>
+      </c>
+      <c r="M29">
+        <v>15.12093852</v>
+      </c>
+      <c r="N29">
+        <v>-2.850938520000003</v>
+      </c>
+      <c r="O29">
+        <v>-0.5701877040000005</v>
+      </c>
+      <c r="P29">
+        <v>-2.280750816000003</v>
+      </c>
+      <c r="Q29">
+        <v>0.5492491839999971</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2108098828248114</v>
+      </c>
+      <c r="T29">
+        <v>1.257041437598083</v>
+      </c>
+      <c r="U29">
+        <v>0.1966</v>
+      </c>
+      <c r="V29">
+        <v>0.1622915136354909</v>
+      </c>
+      <c r="W29">
+        <v>0.1646934884192625</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.8114575681774545</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2052153874152174</v>
+      </c>
+      <c r="C30">
+        <v>153.3012969205712</v>
+      </c>
+      <c r="D30">
+        <v>198.9620969205712</v>
+      </c>
+      <c r="E30">
+        <v>71.90080000000002</v>
+      </c>
+      <c r="F30">
+        <v>79.76080000000002</v>
+      </c>
+      <c r="G30">
+        <v>34.1</v>
+      </c>
+      <c r="H30">
+        <v>277</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>15.1</v>
+      </c>
+      <c r="K30">
+        <v>2.83</v>
+      </c>
+      <c r="L30">
+        <v>12.27</v>
+      </c>
+      <c r="M30">
+        <v>17.05285904</v>
+      </c>
+      <c r="N30">
+        <v>-4.782859040000002</v>
+      </c>
+      <c r="O30">
+        <v>-0.9565718080000001</v>
+      </c>
+      <c r="P30">
+        <v>-3.826287232000002</v>
+      </c>
+      <c r="Q30">
+        <v>-0.9962872320000016</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2138418688083563</v>
+      </c>
+      <c r="T30">
+        <v>1.279199071548769</v>
+      </c>
+      <c r="U30">
+        <v>0.2138</v>
+      </c>
+      <c r="V30">
+        <v>0.1439054878858601</v>
+      </c>
+      <c r="W30">
+        <v>0.1830330066900031</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.7195274394293005</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2069653874152174</v>
+      </c>
+      <c r="C31">
+        <v>148.3822133629096</v>
+      </c>
+      <c r="D31">
+        <v>196.8916133629096</v>
+      </c>
+      <c r="E31">
+        <v>74.74939999999999</v>
+      </c>
+      <c r="F31">
+        <v>82.60939999999999</v>
+      </c>
+      <c r="G31">
+        <v>34.1</v>
+      </c>
+      <c r="H31">
+        <v>277</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>15.1</v>
+      </c>
+      <c r="K31">
+        <v>2.83</v>
+      </c>
+      <c r="L31">
+        <v>12.27</v>
+      </c>
+      <c r="M31">
+        <v>17.66188972</v>
+      </c>
+      <c r="N31">
+        <v>-5.391889719999998</v>
+      </c>
+      <c r="O31">
+        <v>-1.078377943999999</v>
+      </c>
+      <c r="P31">
+        <v>-4.313511775999999</v>
+      </c>
+      <c r="Q31">
+        <v>-1.483511775999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2163072472422768</v>
+      </c>
+      <c r="T31">
+        <v>1.297215959880442</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1389432296828994</v>
+      </c>
+      <c r="W31">
+        <v>0.1840939374937961</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.6947161484144971</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2087153874152174</v>
+      </c>
+      <c r="C32">
+        <v>143.5057786351277</v>
+      </c>
+      <c r="D32">
+        <v>194.8637786351277</v>
+      </c>
+      <c r="E32">
+        <v>77.598</v>
+      </c>
+      <c r="F32">
+        <v>85.458</v>
+      </c>
+      <c r="G32">
+        <v>34.1</v>
+      </c>
+      <c r="H32">
+        <v>277</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>15.1</v>
+      </c>
+      <c r="K32">
+        <v>2.83</v>
+      </c>
+      <c r="L32">
+        <v>12.27</v>
+      </c>
+      <c r="M32">
+        <v>18.2709204</v>
+      </c>
+      <c r="N32">
+        <v>-6.000920399999998</v>
+      </c>
+      <c r="O32">
+        <v>-1.200184079999999</v>
+      </c>
+      <c r="P32">
+        <v>-4.800736319999999</v>
+      </c>
+      <c r="Q32">
+        <v>-1.970736319999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2188430650600237</v>
+      </c>
+      <c r="T32">
+        <v>1.315747616450162</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1343117886934694</v>
+      </c>
+      <c r="W32">
+        <v>0.1850841395773362</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.6715589434673472</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2104653874152174</v>
+      </c>
+      <c r="C33">
+        <v>138.6706884186308</v>
+      </c>
+      <c r="D33">
+        <v>192.8772884186308</v>
+      </c>
+      <c r="E33">
+        <v>80.4466</v>
+      </c>
+      <c r="F33">
+        <v>88.3066</v>
+      </c>
+      <c r="G33">
+        <v>34.1</v>
+      </c>
+      <c r="H33">
+        <v>277</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>15.1</v>
+      </c>
+      <c r="K33">
+        <v>2.83</v>
+      </c>
+      <c r="L33">
+        <v>12.27</v>
+      </c>
+      <c r="M33">
+        <v>18.87995108</v>
+      </c>
+      <c r="N33">
+        <v>-6.609951080000002</v>
+      </c>
+      <c r="O33">
+        <v>-1.321990216</v>
+      </c>
+      <c r="P33">
+        <v>-5.287960864000002</v>
+      </c>
+      <c r="Q33">
+        <v>-2.457960864000002</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2214523848435022</v>
+      </c>
+      <c r="T33">
+        <v>1.334816422485672</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1299791503485188</v>
+      </c>
+      <c r="W33">
+        <v>0.1860104576554867</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.649895751742594</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2122153874152174</v>
+      </c>
+      <c r="C34">
+        <v>133.8756910443054</v>
+      </c>
+      <c r="D34">
+        <v>190.9308910443054</v>
+      </c>
+      <c r="E34">
+        <v>83.29520000000001</v>
+      </c>
+      <c r="F34">
+        <v>91.15520000000001</v>
+      </c>
+      <c r="G34">
+        <v>34.1</v>
+      </c>
+      <c r="H34">
+        <v>277</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>15.1</v>
+      </c>
+      <c r="K34">
+        <v>2.83</v>
+      </c>
+      <c r="L34">
+        <v>12.27</v>
+      </c>
+      <c r="M34">
+        <v>19.48898176</v>
+      </c>
+      <c r="N34">
+        <v>-7.218981760000002</v>
+      </c>
+      <c r="O34">
+        <v>-1.443796352</v>
+      </c>
+      <c r="P34">
+        <v>-5.775185408000002</v>
+      </c>
+      <c r="Q34">
+        <v>-2.945185408000002</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2241384493264949</v>
+      </c>
+      <c r="T34">
+        <v>1.35444607575752</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.1259173019001275</v>
+      </c>
+      <c r="W34">
+        <v>0.1868788808537527</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.6295865095006379</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2139653874152174</v>
+      </c>
+      <c r="C35">
+        <v>129.1195848625304</v>
+      </c>
+      <c r="D35">
+        <v>189.0233848625304</v>
+      </c>
+      <c r="E35">
+        <v>86.14380000000001</v>
+      </c>
+      <c r="F35">
+        <v>94.00380000000001</v>
+      </c>
+      <c r="G35">
+        <v>34.1</v>
+      </c>
+      <c r="H35">
+        <v>277</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>15.1</v>
+      </c>
+      <c r="K35">
+        <v>2.83</v>
+      </c>
+      <c r="L35">
+        <v>12.27</v>
+      </c>
+      <c r="M35">
+        <v>20.09801244</v>
+      </c>
+      <c r="N35">
+        <v>-7.828012440000002</v>
+      </c>
+      <c r="O35">
+        <v>-1.565602488</v>
+      </c>
+      <c r="P35">
+        <v>-6.262409952000002</v>
+      </c>
+      <c r="Q35">
+        <v>-3.432409952000002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2269046948388307</v>
+      </c>
+      <c r="T35">
+        <v>1.374661688828528</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1221016260849722</v>
+      </c>
+      <c r="W35">
+        <v>0.1876946723430329</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.610508130424861</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2157153874152174</v>
+      </c>
+      <c r="C36">
+        <v>124.4012157692798</v>
+      </c>
+      <c r="D36">
+        <v>187.1536157692799</v>
+      </c>
+      <c r="E36">
+        <v>88.99240000000002</v>
+      </c>
+      <c r="F36">
+        <v>96.85240000000002</v>
+      </c>
+      <c r="G36">
+        <v>34.1</v>
+      </c>
+      <c r="H36">
+        <v>277</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>15.1</v>
+      </c>
+      <c r="K36">
+        <v>2.83</v>
+      </c>
+      <c r="L36">
+        <v>12.27</v>
+      </c>
+      <c r="M36">
+        <v>20.70704312</v>
+      </c>
+      <c r="N36">
+        <v>-8.437043120000002</v>
+      </c>
+      <c r="O36">
+        <v>-1.687408624</v>
+      </c>
+      <c r="P36">
+        <v>-6.749634496000002</v>
+      </c>
+      <c r="Q36">
+        <v>-3.919634496000002</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2297547659727523</v>
+      </c>
+      <c r="T36">
+        <v>1.395489896235021</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1185104017883553</v>
+      </c>
+      <c r="W36">
+        <v>0.1884624760976496</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5925520089417768</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2174653874152174</v>
+      </c>
+      <c r="C37">
+        <v>119.7194748776135</v>
+      </c>
+      <c r="D37">
+        <v>185.3204748776135</v>
+      </c>
+      <c r="E37">
+        <v>91.84100000000001</v>
+      </c>
+      <c r="F37">
+        <v>99.70100000000001</v>
+      </c>
+      <c r="G37">
+        <v>34.1</v>
+      </c>
+      <c r="H37">
+        <v>277</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>15.1</v>
+      </c>
+      <c r="K37">
+        <v>2.83</v>
+      </c>
+      <c r="L37">
+        <v>12.27</v>
+      </c>
+      <c r="M37">
+        <v>21.3160738</v>
+      </c>
+      <c r="N37">
+        <v>-9.046073800000002</v>
+      </c>
+      <c r="O37">
+        <v>-1.80921476</v>
+      </c>
+      <c r="P37">
+        <v>-7.236859040000002</v>
+      </c>
+      <c r="Q37">
+        <v>-4.406859040000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2326925316031024</v>
+      </c>
+      <c r="T37">
+        <v>1.416958971561713</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.115124390308688</v>
+      </c>
+      <c r="W37">
+        <v>0.1891864053520025</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5756219515434404</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2192153874152174</v>
+      </c>
+      <c r="C38">
+        <v>115.0732963246854</v>
+      </c>
+      <c r="D38">
+        <v>183.5228963246854</v>
+      </c>
+      <c r="E38">
+        <v>94.6896</v>
+      </c>
+      <c r="F38">
+        <v>102.5496</v>
+      </c>
+      <c r="G38">
+        <v>34.1</v>
+      </c>
+      <c r="H38">
+        <v>277</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>15.1</v>
+      </c>
+      <c r="K38">
+        <v>2.83</v>
+      </c>
+      <c r="L38">
+        <v>12.27</v>
+      </c>
+      <c r="M38">
+        <v>21.92510448</v>
+      </c>
+      <c r="N38">
+        <v>-9.655104479999999</v>
+      </c>
+      <c r="O38">
+        <v>-1.931020895999999</v>
+      </c>
+      <c r="P38">
+        <v>-7.724083583999999</v>
+      </c>
+      <c r="Q38">
+        <v>-4.894083583999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2357221024094009</v>
+      </c>
+      <c r="T38">
+        <v>1.439098955492365</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1119264905778912</v>
+      </c>
+      <c r="W38">
+        <v>0.1898701163144469</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5596324528894561</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2209653874152174</v>
+      </c>
+      <c r="C39">
+        <v>110.461655205155</v>
+      </c>
+      <c r="D39">
+        <v>181.759855205155</v>
+      </c>
+      <c r="E39">
+        <v>97.5382</v>
+      </c>
+      <c r="F39">
+        <v>105.3982</v>
+      </c>
+      <c r="G39">
+        <v>34.1</v>
+      </c>
+      <c r="H39">
+        <v>277</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>15.1</v>
+      </c>
+      <c r="K39">
+        <v>2.83</v>
+      </c>
+      <c r="L39">
+        <v>12.27</v>
+      </c>
+      <c r="M39">
+        <v>22.53413516</v>
+      </c>
+      <c r="N39">
+        <v>-10.26413516</v>
+      </c>
+      <c r="O39">
+        <v>-2.052827031999999</v>
+      </c>
+      <c r="P39">
+        <v>-8.211308127999999</v>
+      </c>
+      <c r="Q39">
+        <v>-5.381308127999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2388478500666929</v>
+      </c>
+      <c r="T39">
+        <v>1.461941796055736</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1089014502920022</v>
+      </c>
+      <c r="W39">
+        <v>0.1905168699275699</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5445072514600112</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2227153874152174</v>
+      </c>
+      <c r="C40">
+        <v>105.8835656225846</v>
+      </c>
+      <c r="D40">
+        <v>180.0303656225846</v>
+      </c>
+      <c r="E40">
+        <v>100.3868</v>
+      </c>
+      <c r="F40">
+        <v>108.2468</v>
+      </c>
+      <c r="G40">
+        <v>34.1</v>
+      </c>
+      <c r="H40">
+        <v>277</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>15.1</v>
+      </c>
+      <c r="K40">
+        <v>2.83</v>
+      </c>
+      <c r="L40">
+        <v>12.27</v>
+      </c>
+      <c r="M40">
+        <v>23.14316584</v>
+      </c>
+      <c r="N40">
+        <v>-10.87316584</v>
+      </c>
+      <c r="O40">
+        <v>-2.174633168</v>
+      </c>
+      <c r="P40">
+        <v>-8.698532672000002</v>
+      </c>
+      <c r="Q40">
+        <v>-5.868532672000002</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2420744282935751</v>
+      </c>
+      <c r="T40">
+        <v>1.485521502443732</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.106035622652739</v>
+      </c>
+      <c r="W40">
+        <v>0.1911295838768444</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5301781132636951</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2244653874152174</v>
+      </c>
+      <c r="C41">
+        <v>101.3380788510349</v>
+      </c>
+      <c r="D41">
+        <v>178.333478851035</v>
+      </c>
+      <c r="E41">
+        <v>103.2354</v>
+      </c>
+      <c r="F41">
+        <v>111.0954</v>
+      </c>
+      <c r="G41">
+        <v>34.1</v>
+      </c>
+      <c r="H41">
+        <v>277</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>15.1</v>
+      </c>
+      <c r="K41">
+        <v>2.83</v>
+      </c>
+      <c r="L41">
+        <v>12.27</v>
+      </c>
+      <c r="M41">
+        <v>23.75219652</v>
+      </c>
+      <c r="N41">
+        <v>-11.48219652</v>
+      </c>
+      <c r="O41">
+        <v>-2.296439304</v>
+      </c>
+      <c r="P41">
+        <v>-9.185757216000003</v>
+      </c>
+      <c r="Q41">
+        <v>-6.355757216000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2454067959705189</v>
+      </c>
+      <c r="T41">
+        <v>1.509874313959203</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.103316760533438</v>
+      </c>
+      <c r="W41">
+        <v>0.1917108765979509</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5165838026671901</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2262153874152174</v>
+      </c>
+      <c r="C42">
+        <v>96.82428159965934</v>
+      </c>
+      <c r="D42">
+        <v>176.6682815996594</v>
+      </c>
+      <c r="E42">
+        <v>106.084</v>
+      </c>
+      <c r="F42">
+        <v>113.944</v>
+      </c>
+      <c r="G42">
+        <v>34.1</v>
+      </c>
+      <c r="H42">
+        <v>277</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>15.1</v>
+      </c>
+      <c r="K42">
+        <v>2.83</v>
+      </c>
+      <c r="L42">
+        <v>12.27</v>
+      </c>
+      <c r="M42">
+        <v>24.3612272</v>
+      </c>
+      <c r="N42">
+        <v>-12.0912272</v>
+      </c>
+      <c r="O42">
+        <v>-2.41824544</v>
+      </c>
+      <c r="P42">
+        <v>-9.672981760000003</v>
+      </c>
+      <c r="Q42">
+        <v>-6.842981760000002</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2488502425700276</v>
+      </c>
+      <c r="T42">
+        <v>1.535038885858523</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.100733841520102</v>
+      </c>
+      <c r="W42">
+        <v>0.1922631046830022</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5036692076005103</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2387693457382593</v>
+      </c>
+      <c r="C43">
+        <v>82.88455042644165</v>
+      </c>
+      <c r="D43">
+        <v>165.5771504264417</v>
+      </c>
+      <c r="E43">
+        <v>108.9326</v>
+      </c>
+      <c r="F43">
+        <v>116.7926</v>
+      </c>
+      <c r="G43">
+        <v>34.1</v>
+      </c>
+      <c r="H43">
+        <v>277</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>15.1</v>
+      </c>
+      <c r="K43">
+        <v>2.83</v>
+      </c>
+      <c r="L43">
+        <v>12.27</v>
+      </c>
+      <c r="M43">
+        <v>27.89007288000001</v>
+      </c>
+      <c r="N43">
+        <v>-15.62007288000001</v>
+      </c>
+      <c r="O43">
+        <v>-3.124014576</v>
+      </c>
+      <c r="P43">
+        <v>-12.49605830400001</v>
+      </c>
+      <c r="Q43">
+        <v>-9.666058304000005</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2533493285848448</v>
+      </c>
+      <c r="T43">
+        <v>1.567918028958128</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.08798829642929205</v>
+      </c>
+      <c r="W43">
+        <v>0.2177883948126851</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.4399414821464603</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2407693457382593</v>
+      </c>
+      <c r="C44">
+        <v>78.39632387993575</v>
+      </c>
+      <c r="D44">
+        <v>163.9375238799358</v>
+      </c>
+      <c r="E44">
+        <v>111.7812</v>
+      </c>
+      <c r="F44">
+        <v>119.6412</v>
+      </c>
+      <c r="G44">
+        <v>34.1</v>
+      </c>
+      <c r="H44">
+        <v>277</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>15.1</v>
+      </c>
+      <c r="K44">
+        <v>2.83</v>
+      </c>
+      <c r="L44">
+        <v>12.27</v>
+      </c>
+      <c r="M44">
+        <v>28.57031856</v>
+      </c>
+      <c r="N44">
+        <v>-16.30031856</v>
+      </c>
+      <c r="O44">
+        <v>-3.260063712</v>
+      </c>
+      <c r="P44">
+        <v>-13.040254848</v>
+      </c>
+      <c r="Q44">
+        <v>-10.210254848</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2570484549397559</v>
+      </c>
+      <c r="T44">
+        <v>1.594951098422923</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.08589333699049939</v>
+      </c>
+      <c r="W44">
+        <v>0.2182886711266687</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.4294666849524971</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2427693457382593</v>
+      </c>
+      <c r="C45">
+        <v>73.94025170526587</v>
+      </c>
+      <c r="D45">
+        <v>162.3300517052659</v>
+      </c>
+      <c r="E45">
+        <v>114.6298</v>
+      </c>
+      <c r="F45">
+        <v>122.4898</v>
+      </c>
+      <c r="G45">
+        <v>34.1</v>
+      </c>
+      <c r="H45">
+        <v>277</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>15.1</v>
+      </c>
+      <c r="K45">
+        <v>2.83</v>
+      </c>
+      <c r="L45">
+        <v>12.27</v>
+      </c>
+      <c r="M45">
+        <v>29.25056424</v>
+      </c>
+      <c r="N45">
+        <v>-16.98056424</v>
+      </c>
+      <c r="O45">
+        <v>-3.396112848</v>
+      </c>
+      <c r="P45">
+        <v>-13.584451392</v>
+      </c>
+      <c r="Q45">
+        <v>-10.754451392</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2608773752018569</v>
+      </c>
+      <c r="T45">
+        <v>1.622932696640869</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.08389581752560404</v>
+      </c>
+      <c r="W45">
+        <v>0.2187656787748858</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4194790876280203</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2447693457382593</v>
+      </c>
+      <c r="C46">
+        <v>69.51539722794621</v>
+      </c>
+      <c r="D46">
+        <v>160.7537972279462</v>
+      </c>
+      <c r="E46">
+        <v>117.4784</v>
+      </c>
+      <c r="F46">
+        <v>125.3384</v>
+      </c>
+      <c r="G46">
+        <v>34.1</v>
+      </c>
+      <c r="H46">
+        <v>277</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>15.1</v>
+      </c>
+      <c r="K46">
+        <v>2.83</v>
+      </c>
+      <c r="L46">
+        <v>12.27</v>
+      </c>
+      <c r="M46">
+        <v>29.93080992</v>
+      </c>
+      <c r="N46">
+        <v>-17.66080992</v>
+      </c>
+      <c r="O46">
+        <v>-3.532161984</v>
+      </c>
+      <c r="P46">
+        <v>-14.128647936</v>
+      </c>
+      <c r="Q46">
+        <v>-11.298647936</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2648430426161758</v>
+      </c>
+      <c r="T46">
+        <v>1.651913637652313</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.08198909440002215</v>
+      </c>
+      <c r="W46">
+        <v>0.2192210042572747</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4099454720001108</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2467693457382593</v>
+      </c>
+      <c r="C47">
+        <v>65.12085980474282</v>
+      </c>
+      <c r="D47">
+        <v>159.2078598047428</v>
+      </c>
+      <c r="E47">
+        <v>120.327</v>
+      </c>
+      <c r="F47">
+        <v>128.187</v>
+      </c>
+      <c r="G47">
+        <v>34.1</v>
+      </c>
+      <c r="H47">
+        <v>277</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>15.1</v>
+      </c>
+      <c r="K47">
+        <v>2.83</v>
+      </c>
+      <c r="L47">
+        <v>12.27</v>
+      </c>
+      <c r="M47">
+        <v>30.6110556</v>
+      </c>
+      <c r="N47">
+        <v>-18.3410556</v>
+      </c>
+      <c r="O47">
+        <v>-3.66821112</v>
+      </c>
+      <c r="P47">
+        <v>-14.67284448</v>
+      </c>
+      <c r="Q47">
+        <v>-11.84284448</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2689529161182881</v>
+      </c>
+      <c r="T47">
+        <v>1.681948431064173</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.08016711452446609</v>
+      </c>
+      <c r="W47">
+        <v>0.2196560930515575</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.4008355726223305</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2487693457382593</v>
+      </c>
+      <c r="C48">
+        <v>60.75577310764939</v>
+      </c>
+      <c r="D48">
+        <v>157.6913731076494</v>
+      </c>
+      <c r="E48">
+        <v>123.1756</v>
+      </c>
+      <c r="F48">
+        <v>131.0356</v>
+      </c>
+      <c r="G48">
+        <v>34.1</v>
+      </c>
+      <c r="H48">
+        <v>277</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>15.1</v>
+      </c>
+      <c r="K48">
+        <v>2.83</v>
+      </c>
+      <c r="L48">
+        <v>12.27</v>
+      </c>
+      <c r="M48">
+        <v>31.29130128000001</v>
+      </c>
+      <c r="N48">
+        <v>-19.02130128000001</v>
+      </c>
+      <c r="O48">
+        <v>-3.804260256000001</v>
+      </c>
+      <c r="P48">
+        <v>-15.21704102400001</v>
+      </c>
+      <c r="Q48">
+        <v>-12.38704102400001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2732150071575156</v>
+      </c>
+      <c r="T48">
+        <v>1.713095624232029</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.07842435116523856</v>
+      </c>
+      <c r="W48">
+        <v>0.220072264941741</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3921217558261929</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2507693457382593</v>
+      </c>
+      <c r="C49">
+        <v>56.41930350501011</v>
+      </c>
+      <c r="D49">
+        <v>156.2035035050101</v>
+      </c>
+      <c r="E49">
+        <v>126.0242</v>
+      </c>
+      <c r="F49">
+        <v>133.8842</v>
+      </c>
+      <c r="G49">
+        <v>34.1</v>
+      </c>
+      <c r="H49">
+        <v>277</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>15.1</v>
+      </c>
+      <c r="K49">
+        <v>2.83</v>
+      </c>
+      <c r="L49">
+        <v>12.27</v>
+      </c>
+      <c r="M49">
+        <v>31.97154696000001</v>
+      </c>
+      <c r="N49">
+        <v>-19.70154696000001</v>
+      </c>
+      <c r="O49">
+        <v>-3.940309392000001</v>
+      </c>
+      <c r="P49">
+        <v>-15.76123756800001</v>
+      </c>
+      <c r="Q49">
+        <v>-12.93123756800001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2776379318208649</v>
+      </c>
+      <c r="T49">
+        <v>1.745418183179803</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.07675574794895688</v>
+      </c>
+      <c r="W49">
+        <v>0.2204707273897891</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3837787397447845</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2527693457382593</v>
+      </c>
+      <c r="C50">
+        <v>52.11064853343404</v>
+      </c>
+      <c r="D50">
+        <v>154.743448533434</v>
+      </c>
+      <c r="E50">
+        <v>128.8728</v>
+      </c>
+      <c r="F50">
+        <v>136.7328</v>
+      </c>
+      <c r="G50">
+        <v>34.1</v>
+      </c>
+      <c r="H50">
+        <v>277</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>15.1</v>
+      </c>
+      <c r="K50">
+        <v>2.83</v>
+      </c>
+      <c r="L50">
+        <v>12.27</v>
+      </c>
+      <c r="M50">
+        <v>32.65179264</v>
+      </c>
+      <c r="N50">
+        <v>-20.38179264</v>
+      </c>
+      <c r="O50">
+        <v>-4.076358528</v>
+      </c>
+      <c r="P50">
+        <v>-16.305434112</v>
+      </c>
+      <c r="Q50">
+        <v>-13.475434112</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2822309689712662</v>
+      </c>
+      <c r="T50">
+        <v>1.778983917471722</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.07515666986668695</v>
+      </c>
+      <c r="W50">
+        <v>0.2208525872358351</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3757833493334349</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2547693457382593</v>
+      </c>
+      <c r="C51">
+        <v>47.82903545461528</v>
+      </c>
+      <c r="D51">
+        <v>153.3104354546153</v>
+      </c>
+      <c r="E51">
+        <v>131.7214</v>
+      </c>
+      <c r="F51">
+        <v>139.5814</v>
+      </c>
+      <c r="G51">
+        <v>34.1</v>
+      </c>
+      <c r="H51">
+        <v>277</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>15.1</v>
+      </c>
+      <c r="K51">
+        <v>2.83</v>
+      </c>
+      <c r="L51">
+        <v>12.27</v>
+      </c>
+      <c r="M51">
+        <v>33.33203832</v>
+      </c>
+      <c r="N51">
+        <v>-21.06203832</v>
+      </c>
+      <c r="O51">
+        <v>-4.212407664</v>
+      </c>
+      <c r="P51">
+        <v>-16.849630656</v>
+      </c>
+      <c r="Q51">
+        <v>-14.019630656</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2870041252256048</v>
+      </c>
+      <c r="T51">
+        <v>1.813865955069207</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.07362286027757091</v>
+      </c>
+      <c r="W51">
+        <v>0.2212188609657161</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3681143013878546</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2567693457382593</v>
+      </c>
+      <c r="C52">
+        <v>43.57371989160472</v>
+      </c>
+      <c r="D52">
+        <v>151.9037198916047</v>
+      </c>
+      <c r="E52">
+        <v>134.57</v>
+      </c>
+      <c r="F52">
+        <v>142.43</v>
+      </c>
+      <c r="G52">
+        <v>34.1</v>
+      </c>
+      <c r="H52">
+        <v>277</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>15.1</v>
+      </c>
+      <c r="K52">
+        <v>2.83</v>
+      </c>
+      <c r="L52">
+        <v>12.27</v>
+      </c>
+      <c r="M52">
+        <v>34.012284</v>
+      </c>
+      <c r="N52">
+        <v>-21.742284</v>
+      </c>
+      <c r="O52">
+        <v>-4.348456799999999</v>
+      </c>
+      <c r="P52">
+        <v>-17.3938272</v>
+      </c>
+      <c r="Q52">
+        <v>-14.5638272</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2919682077301168</v>
+      </c>
+      <c r="T52">
+        <v>1.850143274170591</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.07215040307201949</v>
+      </c>
+      <c r="W52">
+        <v>0.2215704837464018</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3607520153600975</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2587693457382593</v>
+      </c>
+      <c r="C53">
+        <v>39.34398453947836</v>
+      </c>
+      <c r="D53">
+        <v>150.5225845394784</v>
+      </c>
+      <c r="E53">
+        <v>137.4186</v>
+      </c>
+      <c r="F53">
+        <v>145.2786</v>
+      </c>
+      <c r="G53">
+        <v>34.1</v>
+      </c>
+      <c r="H53">
+        <v>277</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>15.1</v>
+      </c>
+      <c r="K53">
+        <v>2.83</v>
+      </c>
+      <c r="L53">
+        <v>12.27</v>
+      </c>
+      <c r="M53">
+        <v>34.69252968000001</v>
+      </c>
+      <c r="N53">
+        <v>-22.42252968000001</v>
+      </c>
+      <c r="O53">
+        <v>-4.484505936000001</v>
+      </c>
+      <c r="P53">
+        <v>-17.93802374400001</v>
+      </c>
+      <c r="Q53">
+        <v>-15.10802374400001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.297134905847058</v>
+      </c>
+      <c r="T53">
+        <v>1.887901300174072</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.0707356892862936</v>
+      </c>
+      <c r="W53">
+        <v>0.2219083173984331</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3536784464314681</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2607693457382593</v>
+      </c>
+      <c r="C54">
+        <v>35.13913794570797</v>
+      </c>
+      <c r="D54">
+        <v>149.166337945708</v>
+      </c>
+      <c r="E54">
+        <v>140.2672</v>
+      </c>
+      <c r="F54">
+        <v>148.1272</v>
+      </c>
+      <c r="G54">
+        <v>34.1</v>
+      </c>
+      <c r="H54">
+        <v>277</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>15.1</v>
+      </c>
+      <c r="K54">
+        <v>2.83</v>
+      </c>
+      <c r="L54">
+        <v>12.27</v>
+      </c>
+      <c r="M54">
+        <v>35.37277536000001</v>
+      </c>
+      <c r="N54">
+        <v>-23.10277536000001</v>
+      </c>
+      <c r="O54">
+        <v>-4.620555072</v>
+      </c>
+      <c r="P54">
+        <v>-18.48222028800001</v>
+      </c>
+      <c r="Q54">
+        <v>-15.65222028800001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3025168830522051</v>
+      </c>
+      <c r="T54">
+        <v>1.927232577261032</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.06937538756924949</v>
+      </c>
+      <c r="W54">
+        <v>0.2222331574484632</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3468769378462476</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2627693457382593</v>
+      </c>
+      <c r="C55">
+        <v>30.95851335587835</v>
+      </c>
+      <c r="D55">
+        <v>147.8343133558784</v>
+      </c>
+      <c r="E55">
+        <v>143.1158</v>
+      </c>
+      <c r="F55">
+        <v>150.9758</v>
+      </c>
+      <c r="G55">
+        <v>34.1</v>
+      </c>
+      <c r="H55">
+        <v>277</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>15.1</v>
+      </c>
+      <c r="K55">
+        <v>2.83</v>
+      </c>
+      <c r="L55">
+        <v>12.27</v>
+      </c>
+      <c r="M55">
+        <v>36.05302104</v>
+      </c>
+      <c r="N55">
+        <v>-23.78302104</v>
+      </c>
+      <c r="O55">
+        <v>-4.756604208</v>
+      </c>
+      <c r="P55">
+        <v>-19.02641683200001</v>
+      </c>
+      <c r="Q55">
+        <v>-16.196416832</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3081278805639541</v>
+      </c>
+      <c r="T55">
+        <v>1.968237525713395</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06806641799247122</v>
+      </c>
+      <c r="W55">
+        <v>0.2225457393833979</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3403320899623561</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2647693457382593</v>
+      </c>
+      <c r="C56">
+        <v>26.80146762070223</v>
+      </c>
+      <c r="D56">
+        <v>146.5258676207023</v>
+      </c>
+      <c r="E56">
+        <v>145.9644</v>
+      </c>
+      <c r="F56">
+        <v>153.8244</v>
+      </c>
+      <c r="G56">
+        <v>34.1</v>
+      </c>
+      <c r="H56">
+        <v>277</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>15.1</v>
+      </c>
+      <c r="K56">
+        <v>2.83</v>
+      </c>
+      <c r="L56">
+        <v>12.27</v>
+      </c>
+      <c r="M56">
+        <v>36.73326672000001</v>
+      </c>
+      <c r="N56">
+        <v>-24.46326672000001</v>
+      </c>
+      <c r="O56">
+        <v>-4.892653344000001</v>
+      </c>
+      <c r="P56">
+        <v>-19.57061337600001</v>
+      </c>
+      <c r="Q56">
+        <v>-16.74061337600001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3139828344892575</v>
+      </c>
+      <c r="T56">
+        <v>2.011025298011512</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06680592877038839</v>
+      </c>
+      <c r="W56">
+        <v>0.2228467442096313</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3340296438519421</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2667693457382593</v>
+      </c>
+      <c r="C57">
+        <v>22.66738016056863</v>
+      </c>
+      <c r="D57">
+        <v>145.2403801605687</v>
+      </c>
+      <c r="E57">
+        <v>148.813</v>
+      </c>
+      <c r="F57">
+        <v>156.673</v>
+      </c>
+      <c r="G57">
+        <v>34.1</v>
+      </c>
+      <c r="H57">
+        <v>277</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>15.1</v>
+      </c>
+      <c r="K57">
+        <v>2.83</v>
+      </c>
+      <c r="L57">
+        <v>12.27</v>
+      </c>
+      <c r="M57">
+        <v>37.41351240000001</v>
+      </c>
+      <c r="N57">
+        <v>-25.14351240000001</v>
+      </c>
+      <c r="O57">
+        <v>-5.028702480000001</v>
+      </c>
+      <c r="P57">
+        <v>-20.11480992000001</v>
+      </c>
+      <c r="Q57">
+        <v>-17.28480992000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3200980085890188</v>
+      </c>
+      <c r="T57">
+        <v>2.055714749078434</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.06559127552001771</v>
+      </c>
+      <c r="W57">
+        <v>0.2231368034058198</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3279563776000886</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2687693457382593</v>
+      </c>
+      <c r="C58">
+        <v>18.55565198412134</v>
+      </c>
+      <c r="D58">
+        <v>143.9772519841214</v>
+      </c>
+      <c r="E58">
+        <v>151.6616</v>
+      </c>
+      <c r="F58">
+        <v>159.5216</v>
+      </c>
+      <c r="G58">
+        <v>34.1</v>
+      </c>
+      <c r="H58">
+        <v>277</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>15.1</v>
+      </c>
+      <c r="K58">
+        <v>2.83</v>
+      </c>
+      <c r="L58">
+        <v>12.27</v>
+      </c>
+      <c r="M58">
+        <v>38.09375808000001</v>
+      </c>
+      <c r="N58">
+        <v>-25.82375808000001</v>
+      </c>
+      <c r="O58">
+        <v>-5.164751616</v>
+      </c>
+      <c r="P58">
+        <v>-20.65900646400001</v>
+      </c>
+      <c r="Q58">
+        <v>-17.82900646400001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3264911451478601</v>
+      </c>
+      <c r="T58">
+        <v>2.102435538830217</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.06442000274287453</v>
+      </c>
+      <c r="W58">
+        <v>0.2234165033450016</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3221000137143727</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2707693457382594</v>
+      </c>
+      <c r="C59">
+        <v>14.46570475760819</v>
+      </c>
+      <c r="D59">
+        <v>142.7359047576082</v>
+      </c>
+      <c r="E59">
+        <v>154.5102</v>
+      </c>
+      <c r="F59">
+        <v>162.3702</v>
+      </c>
+      <c r="G59">
+        <v>34.1</v>
+      </c>
+      <c r="H59">
+        <v>277</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>15.1</v>
+      </c>
+      <c r="K59">
+        <v>2.83</v>
+      </c>
+      <c r="L59">
+        <v>12.27</v>
+      </c>
+      <c r="M59">
+        <v>38.77400376000001</v>
+      </c>
+      <c r="N59">
+        <v>-26.50400376000001</v>
+      </c>
+      <c r="O59">
+        <v>-5.300800752000002</v>
+      </c>
+      <c r="P59">
+        <v>-21.20320300800001</v>
+      </c>
+      <c r="Q59">
+        <v>-18.37320300800001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3331816368954848</v>
+      </c>
+      <c r="T59">
+        <v>2.151329388570455</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.06328982725615742</v>
+      </c>
+      <c r="W59">
+        <v>0.2236863892512296</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3164491362807872</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2727693457382593</v>
+      </c>
+      <c r="C60">
+        <v>10.39697992196179</v>
+      </c>
+      <c r="D60">
+        <v>141.5157799219618</v>
+      </c>
+      <c r="E60">
+        <v>157.3588</v>
+      </c>
+      <c r="F60">
+        <v>165.2188</v>
+      </c>
+      <c r="G60">
+        <v>34.1</v>
+      </c>
+      <c r="H60">
+        <v>277</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>15.1</v>
+      </c>
+      <c r="K60">
+        <v>2.83</v>
+      </c>
+      <c r="L60">
+        <v>12.27</v>
+      </c>
+      <c r="M60">
+        <v>39.45424944</v>
+      </c>
+      <c r="N60">
+        <v>-27.18424944</v>
+      </c>
+      <c r="O60">
+        <v>-5.436849887999998</v>
+      </c>
+      <c r="P60">
+        <v>-21.747399552</v>
+      </c>
+      <c r="Q60">
+        <v>-18.917399552</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3401907234882343</v>
+      </c>
+      <c r="T60">
+        <v>2.202551516869751</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.06219862333794784</v>
+      </c>
+      <c r="W60">
+        <v>0.223946968746898</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3109931166897393</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2747693457382593</v>
+      </c>
+      <c r="C61">
+        <v>6.348937854779592</v>
+      </c>
+      <c r="D61">
+        <v>140.3163378547796</v>
+      </c>
+      <c r="E61">
+        <v>160.2074</v>
+      </c>
+      <c r="F61">
+        <v>168.0674</v>
+      </c>
+      <c r="G61">
+        <v>34.1</v>
+      </c>
+      <c r="H61">
+        <v>277</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>15.1</v>
+      </c>
+      <c r="K61">
+        <v>2.83</v>
+      </c>
+      <c r="L61">
+        <v>12.27</v>
+      </c>
+      <c r="M61">
+        <v>40.13449512</v>
+      </c>
+      <c r="N61">
+        <v>-27.86449512</v>
+      </c>
+      <c r="O61">
+        <v>-5.572899023999998</v>
+      </c>
+      <c r="P61">
+        <v>-22.291596096</v>
+      </c>
+      <c r="Q61">
+        <v>-19.461596096</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3475417167440449</v>
+      </c>
+      <c r="T61">
+        <v>2.256272285573891</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.06114440938306737</v>
+      </c>
+      <c r="W61">
+        <v>0.2241987150393235</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3057220469153369</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2767693457382593</v>
+      </c>
+      <c r="C62">
+        <v>2.321057074564237</v>
+      </c>
+      <c r="D62">
+        <v>139.1370570745642</v>
+      </c>
+      <c r="E62">
+        <v>163.056</v>
+      </c>
+      <c r="F62">
+        <v>170.916</v>
+      </c>
+      <c r="G62">
+        <v>34.1</v>
+      </c>
+      <c r="H62">
+        <v>277</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>15.1</v>
+      </c>
+      <c r="K62">
+        <v>2.83</v>
+      </c>
+      <c r="L62">
+        <v>12.27</v>
+      </c>
+      <c r="M62">
+        <v>40.8147408</v>
+      </c>
+      <c r="N62">
+        <v>-28.5447408</v>
+      </c>
+      <c r="O62">
+        <v>-5.708948159999999</v>
+      </c>
+      <c r="P62">
+        <v>-22.83579264</v>
+      </c>
+      <c r="Q62">
+        <v>-20.00579264</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.355260259662646</v>
+      </c>
+      <c r="T62">
+        <v>2.312679092713238</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.06012533589334957</v>
+      </c>
+      <c r="W62">
+        <v>0.2244420697886681</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3006266794667479</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2787693457382593</v>
+      </c>
+      <c r="C63">
+        <v>-1.687166515244826</v>
+      </c>
+      <c r="D63">
+        <v>137.9774334847552</v>
+      </c>
+      <c r="E63">
+        <v>165.9046</v>
+      </c>
+      <c r="F63">
+        <v>173.7646</v>
+      </c>
+      <c r="G63">
+        <v>34.1</v>
+      </c>
+      <c r="H63">
+        <v>277</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>15.1</v>
+      </c>
+      <c r="K63">
+        <v>2.83</v>
+      </c>
+      <c r="L63">
+        <v>12.27</v>
+      </c>
+      <c r="M63">
+        <v>41.49498648</v>
+      </c>
+      <c r="N63">
+        <v>-29.22498648</v>
+      </c>
+      <c r="O63">
+        <v>-5.844997295999999</v>
+      </c>
+      <c r="P63">
+        <v>-23.379989184</v>
+      </c>
+      <c r="Q63">
+        <v>-20.549989184</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3633746252950216</v>
+      </c>
+      <c r="T63">
+        <v>2.371978556628962</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.0591396746491963</v>
+      </c>
+      <c r="W63">
+        <v>0.2246774456937719</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2956983732459816</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2807693457382593</v>
+      </c>
+      <c r="C64">
+        <v>-5.676220344747776</v>
+      </c>
+      <c r="D64">
+        <v>136.8369796552522</v>
+      </c>
+      <c r="E64">
+        <v>168.7532</v>
+      </c>
+      <c r="F64">
+        <v>176.6132</v>
+      </c>
+      <c r="G64">
+        <v>34.1</v>
+      </c>
+      <c r="H64">
+        <v>277</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>15.1</v>
+      </c>
+      <c r="K64">
+        <v>2.83</v>
+      </c>
+      <c r="L64">
+        <v>12.27</v>
+      </c>
+      <c r="M64">
+        <v>42.17523216</v>
+      </c>
+      <c r="N64">
+        <v>-29.90523216</v>
+      </c>
+      <c r="O64">
+        <v>-5.981046431999999</v>
+      </c>
+      <c r="P64">
+        <v>-23.924185728</v>
+      </c>
+      <c r="Q64">
+        <v>-21.094185728</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3719160628027853</v>
+      </c>
+      <c r="T64">
+        <v>2.434399044961304</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05818580892904798</v>
+      </c>
+      <c r="W64">
+        <v>0.2249052288277434</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2909290446452399</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2827693457382593</v>
+      </c>
+      <c r="C65">
+        <v>-9.646575860721953</v>
+      </c>
+      <c r="D65">
+        <v>135.7152241392781</v>
+      </c>
+      <c r="E65">
+        <v>171.6018</v>
+      </c>
+      <c r="F65">
+        <v>179.4618</v>
+      </c>
+      <c r="G65">
+        <v>34.1</v>
+      </c>
+      <c r="H65">
+        <v>277</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>15.1</v>
+      </c>
+      <c r="K65">
+        <v>2.83</v>
+      </c>
+      <c r="L65">
+        <v>12.27</v>
+      </c>
+      <c r="M65">
+        <v>42.85547784000001</v>
+      </c>
+      <c r="N65">
+        <v>-30.58547784000001</v>
+      </c>
+      <c r="O65">
+        <v>-6.117095568</v>
+      </c>
+      <c r="P65">
+        <v>-24.46838227200001</v>
+      </c>
+      <c r="Q65">
+        <v>-21.63838227200001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.380919199635293</v>
+      </c>
+      <c r="T65">
+        <v>2.500193613744041</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05726222466033293</v>
+      </c>
+      <c r="W65">
+        <v>0.2251257807511125</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2863111233016646</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2847693457382593</v>
+      </c>
+      <c r="C66">
+        <v>-13.59868917643158</v>
+      </c>
+      <c r="D66">
+        <v>134.6117108235684</v>
+      </c>
+      <c r="E66">
+        <v>174.4504</v>
+      </c>
+      <c r="F66">
+        <v>182.3104</v>
+      </c>
+      <c r="G66">
+        <v>34.1</v>
+      </c>
+      <c r="H66">
+        <v>277</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>15.1</v>
+      </c>
+      <c r="K66">
+        <v>2.83</v>
+      </c>
+      <c r="L66">
+        <v>12.27</v>
+      </c>
+      <c r="M66">
+        <v>43.53572352</v>
+      </c>
+      <c r="N66">
+        <v>-31.26572352000001</v>
+      </c>
+      <c r="O66">
+        <v>-6.253144703999999</v>
+      </c>
+      <c r="P66">
+        <v>-25.012578816</v>
+      </c>
+      <c r="Q66">
+        <v>-22.182578816</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3904225107362734</v>
+      </c>
+      <c r="T66">
+        <v>2.569643436348043</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05636750240001522</v>
+      </c>
+      <c r="W66">
+        <v>0.2253394404268764</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2818375120000761</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2867693457382593</v>
+      </c>
+      <c r="C67">
+        <v>-17.53300168999087</v>
+      </c>
+      <c r="D67">
+        <v>133.5259983100092</v>
+      </c>
+      <c r="E67">
+        <v>177.299</v>
+      </c>
+      <c r="F67">
+        <v>185.159</v>
+      </c>
+      <c r="G67">
+        <v>34.1</v>
+      </c>
+      <c r="H67">
+        <v>277</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>15.1</v>
+      </c>
+      <c r="K67">
+        <v>2.83</v>
+      </c>
+      <c r="L67">
+        <v>12.27</v>
+      </c>
+      <c r="M67">
+        <v>44.21596920000001</v>
+      </c>
+      <c r="N67">
+        <v>-31.94596920000001</v>
+      </c>
+      <c r="O67">
+        <v>-6.389193840000001</v>
+      </c>
+      <c r="P67">
+        <v>-25.55677536000001</v>
+      </c>
+      <c r="Q67">
+        <v>-22.72677536000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4004688681858812</v>
+      </c>
+      <c r="T67">
+        <v>2.643061820243701</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.05550031005539959</v>
+      </c>
+      <c r="W67">
+        <v>0.2255465259587706</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2775015502769981</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2887693457382593</v>
+      </c>
+      <c r="C68">
+        <v>-21.44994067304219</v>
+      </c>
+      <c r="D68">
+        <v>132.4576593269578</v>
+      </c>
+      <c r="E68">
+        <v>180.1476</v>
+      </c>
+      <c r="F68">
+        <v>188.0076</v>
+      </c>
+      <c r="G68">
+        <v>34.1</v>
+      </c>
+      <c r="H68">
+        <v>277</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>15.1</v>
+      </c>
+      <c r="K68">
+        <v>2.83</v>
+      </c>
+      <c r="L68">
+        <v>12.27</v>
+      </c>
+      <c r="M68">
+        <v>44.89621488000001</v>
+      </c>
+      <c r="N68">
+        <v>-32.62621488000001</v>
+      </c>
+      <c r="O68">
+        <v>-6.525242975999999</v>
+      </c>
+      <c r="P68">
+        <v>-26.100971904</v>
+      </c>
+      <c r="Q68">
+        <v>-23.27097190400001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4111061878384072</v>
+      </c>
+      <c r="T68">
+        <v>2.72079893260381</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.05465939626668143</v>
+      </c>
+      <c r="W68">
+        <v>0.2257473361715165</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2732969813334073</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2907693457382593</v>
+      </c>
+      <c r="C69">
+        <v>-25.34991983139867</v>
+      </c>
+      <c r="D69">
+        <v>131.4062801686014</v>
+      </c>
+      <c r="E69">
+        <v>182.9962</v>
+      </c>
+      <c r="F69">
+        <v>190.8562</v>
+      </c>
+      <c r="G69">
+        <v>34.1</v>
+      </c>
+      <c r="H69">
+        <v>277</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>15.1</v>
+      </c>
+      <c r="K69">
+        <v>2.83</v>
+      </c>
+      <c r="L69">
+        <v>12.27</v>
+      </c>
+      <c r="M69">
+        <v>45.57646056000001</v>
+      </c>
+      <c r="N69">
+        <v>-33.30646056</v>
+      </c>
+      <c r="O69">
+        <v>-6.661292112</v>
+      </c>
+      <c r="P69">
+        <v>-26.64516844800001</v>
+      </c>
+      <c r="Q69">
+        <v>-23.81516844800001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4223881935304801</v>
+      </c>
+      <c r="T69">
+        <v>2.803247385106956</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.05384358438210409</v>
+      </c>
+      <c r="W69">
+        <v>0.2259421520495535</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2692179219105206</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2927693457382593</v>
+      </c>
+      <c r="C70">
+        <v>-29.23333983919622</v>
+      </c>
+      <c r="D70">
+        <v>130.3714601608038</v>
+      </c>
+      <c r="E70">
+        <v>185.8448</v>
+      </c>
+      <c r="F70">
+        <v>193.7048</v>
+      </c>
+      <c r="G70">
+        <v>34.1</v>
+      </c>
+      <c r="H70">
+        <v>277</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>15.1</v>
+      </c>
+      <c r="K70">
+        <v>2.83</v>
+      </c>
+      <c r="L70">
+        <v>12.27</v>
+      </c>
+      <c r="M70">
+        <v>46.25670624000001</v>
+      </c>
+      <c r="N70">
+        <v>-33.98670624000002</v>
+      </c>
+      <c r="O70">
+        <v>-6.797341248000002</v>
+      </c>
+      <c r="P70">
+        <v>-27.18936499200002</v>
+      </c>
+      <c r="Q70">
+        <v>-24.35936499200002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4343753245783077</v>
+      </c>
+      <c r="T70">
+        <v>2.890848865891549</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.05305176696472021</v>
+      </c>
+      <c r="W70">
+        <v>0.2261312380488248</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.265258834823601</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2947693457382593</v>
+      </c>
+      <c r="C71">
+        <v>-33.10058884800461</v>
+      </c>
+      <c r="D71">
+        <v>129.3528111519954</v>
+      </c>
+      <c r="E71">
+        <v>188.6934</v>
+      </c>
+      <c r="F71">
+        <v>196.5534</v>
+      </c>
+      <c r="G71">
+        <v>34.1</v>
+      </c>
+      <c r="H71">
+        <v>277</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>15.1</v>
+      </c>
+      <c r="K71">
+        <v>2.83</v>
+      </c>
+      <c r="L71">
+        <v>12.27</v>
+      </c>
+      <c r="M71">
+        <v>46.93695192000001</v>
+      </c>
+      <c r="N71">
+        <v>-34.66695192000002</v>
+      </c>
+      <c r="O71">
+        <v>-6.933390384000002</v>
+      </c>
+      <c r="P71">
+        <v>-27.73356153600001</v>
+      </c>
+      <c r="Q71">
+        <v>-24.90356153600001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4471358189195434</v>
+      </c>
+      <c r="T71">
+        <v>2.984102055113857</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0522829007768257</v>
+      </c>
+      <c r="W71">
+        <v>0.226314843294494</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2614145038841285</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2967693457382593</v>
+      </c>
+      <c r="C72">
+        <v>-36.95204297225573</v>
+      </c>
+      <c r="D72">
+        <v>128.3499570277443</v>
+      </c>
+      <c r="E72">
+        <v>191.542</v>
+      </c>
+      <c r="F72">
+        <v>199.402</v>
+      </c>
+      <c r="G72">
+        <v>34.1</v>
+      </c>
+      <c r="H72">
+        <v>277</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>15.1</v>
+      </c>
+      <c r="K72">
+        <v>2.83</v>
+      </c>
+      <c r="L72">
+        <v>12.27</v>
+      </c>
+      <c r="M72">
+        <v>47.6171976</v>
+      </c>
+      <c r="N72">
+        <v>-35.3471976</v>
+      </c>
+      <c r="O72">
+        <v>-7.069439519999999</v>
+      </c>
+      <c r="P72">
+        <v>-28.27775808</v>
+      </c>
+      <c r="Q72">
+        <v>-25.44775808</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4607470128835282</v>
+      </c>
+      <c r="T72">
+        <v>3.083572123617652</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.05153600219429964</v>
+      </c>
+      <c r="W72">
+        <v>0.2264932026760013</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2576800109714983</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2987693457382593</v>
+      </c>
+      <c r="C73">
+        <v>-40.78806675226531</v>
+      </c>
+      <c r="D73">
+        <v>127.3625332477347</v>
+      </c>
+      <c r="E73">
+        <v>194.3906</v>
+      </c>
+      <c r="F73">
+        <v>202.2506</v>
+      </c>
+      <c r="G73">
+        <v>34.1</v>
+      </c>
+      <c r="H73">
+        <v>277</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>15.1</v>
+      </c>
+      <c r="K73">
+        <v>2.83</v>
+      </c>
+      <c r="L73">
+        <v>12.27</v>
+      </c>
+      <c r="M73">
+        <v>48.29744328</v>
+      </c>
+      <c r="N73">
+        <v>-36.02744328</v>
+      </c>
+      <c r="O73">
+        <v>-7.205488655999998</v>
+      </c>
+      <c r="P73">
+        <v>-28.821954624</v>
+      </c>
+      <c r="Q73">
+        <v>-25.991954624</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4752969098795118</v>
+      </c>
+      <c r="T73">
+        <v>3.189902196845846</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.05081014300846443</v>
+      </c>
+      <c r="W73">
+        <v>0.2266665378495787</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2540507150423222</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3007693457382593</v>
+      </c>
+      <c r="C74">
+        <v>-44.60901359604441</v>
+      </c>
+      <c r="D74">
+        <v>126.3901864039556</v>
+      </c>
+      <c r="E74">
+        <v>197.2392</v>
+      </c>
+      <c r="F74">
+        <v>205.0992</v>
+      </c>
+      <c r="G74">
+        <v>34.1</v>
+      </c>
+      <c r="H74">
+        <v>277</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>15.1</v>
+      </c>
+      <c r="K74">
+        <v>2.83</v>
+      </c>
+      <c r="L74">
+        <v>12.27</v>
+      </c>
+      <c r="M74">
+        <v>48.97768896</v>
+      </c>
+      <c r="N74">
+        <v>-36.70768896</v>
+      </c>
+      <c r="O74">
+        <v>-7.341537791999998</v>
+      </c>
+      <c r="P74">
+        <v>-29.366151168</v>
+      </c>
+      <c r="Q74">
+        <v>-26.536151168</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4908860852323515</v>
+      </c>
+      <c r="T74">
+        <v>3.303827275304626</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0501044465777913</v>
+      </c>
+      <c r="W74">
+        <v>0.2268350581572234</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2505222328889567</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3027693457382593</v>
+      </c>
+      <c r="C75">
+        <v>-48.41522620102677</v>
+      </c>
+      <c r="D75">
+        <v>125.4325737989732</v>
+      </c>
+      <c r="E75">
+        <v>200.0878</v>
+      </c>
+      <c r="F75">
+        <v>207.9478</v>
+      </c>
+      <c r="G75">
+        <v>34.1</v>
+      </c>
+      <c r="H75">
+        <v>277</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>15.1</v>
+      </c>
+      <c r="K75">
+        <v>2.83</v>
+      </c>
+      <c r="L75">
+        <v>12.27</v>
+      </c>
+      <c r="M75">
+        <v>49.65793464</v>
+      </c>
+      <c r="N75">
+        <v>-37.38793464</v>
+      </c>
+      <c r="O75">
+        <v>-7.477586927999998</v>
+      </c>
+      <c r="P75">
+        <v>-29.910347712</v>
+      </c>
+      <c r="Q75">
+        <v>-27.080347712</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.5076300143150312</v>
+      </c>
+      <c r="T75">
+        <v>3.426191248464057</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04941808429590376</v>
+      </c>
+      <c r="W75">
+        <v>0.2269989614701382</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2470904214795189</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3047693457382593</v>
+      </c>
+      <c r="C76">
+        <v>-52.20703695676863</v>
+      </c>
+      <c r="D76">
+        <v>124.4893630432314</v>
+      </c>
+      <c r="E76">
+        <v>202.9364</v>
+      </c>
+      <c r="F76">
+        <v>210.7964</v>
+      </c>
+      <c r="G76">
+        <v>34.1</v>
+      </c>
+      <c r="H76">
+        <v>277</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>15.1</v>
+      </c>
+      <c r="K76">
+        <v>2.83</v>
+      </c>
+      <c r="L76">
+        <v>12.27</v>
+      </c>
+      <c r="M76">
+        <v>50.33818032000001</v>
+      </c>
+      <c r="N76">
+        <v>-38.06818032000001</v>
+      </c>
+      <c r="O76">
+        <v>-7.613636064</v>
+      </c>
+      <c r="P76">
+        <v>-30.45454425600001</v>
+      </c>
+      <c r="Q76">
+        <v>-27.62454425600001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5256619379425324</v>
+      </c>
+      <c r="T76">
+        <v>3.557967834943443</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04875027234595911</v>
+      </c>
+      <c r="W76">
+        <v>0.227158434963785</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2437513617297955</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3067693457382593</v>
+      </c>
+      <c r="C77">
+        <v>-55.98476832961472</v>
+      </c>
+      <c r="D77">
+        <v>123.5602316703853</v>
+      </c>
+      <c r="E77">
+        <v>205.785</v>
+      </c>
+      <c r="F77">
+        <v>213.645</v>
+      </c>
+      <c r="G77">
+        <v>34.1</v>
+      </c>
+      <c r="H77">
+        <v>277</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>15.1</v>
+      </c>
+      <c r="K77">
+        <v>2.83</v>
+      </c>
+      <c r="L77">
+        <v>12.27</v>
+      </c>
+      <c r="M77">
+        <v>51.01842600000001</v>
+      </c>
+      <c r="N77">
+        <v>-38.74842600000001</v>
+      </c>
+      <c r="O77">
+        <v>-7.7496852</v>
+      </c>
+      <c r="P77">
+        <v>-30.99874080000001</v>
+      </c>
+      <c r="Q77">
+        <v>-28.16874080000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5451364154602336</v>
+      </c>
+      <c r="T77">
+        <v>3.700286548341182</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04810026871467966</v>
+      </c>
+      <c r="W77">
+        <v>0.2273136558309345</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2405013435733983</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3087693457382593</v>
+      </c>
+      <c r="C78">
+        <v>-59.74873323026668</v>
+      </c>
+      <c r="D78">
+        <v>122.6448667697333</v>
+      </c>
+      <c r="E78">
+        <v>208.6336</v>
+      </c>
+      <c r="F78">
+        <v>216.4936</v>
+      </c>
+      <c r="G78">
+        <v>34.1</v>
+      </c>
+      <c r="H78">
+        <v>277</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>15.1</v>
+      </c>
+      <c r="K78">
+        <v>2.83</v>
+      </c>
+      <c r="L78">
+        <v>12.27</v>
+      </c>
+      <c r="M78">
+        <v>51.69867168</v>
+      </c>
+      <c r="N78">
+        <v>-39.42867168000001</v>
+      </c>
+      <c r="O78">
+        <v>-7.885734336</v>
+      </c>
+      <c r="P78">
+        <v>-31.54293734400001</v>
+      </c>
+      <c r="Q78">
+        <v>-28.71293734400001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5662337661044101</v>
+      </c>
+      <c r="T78">
+        <v>3.854465154522065</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04746737044211809</v>
+      </c>
+      <c r="W78">
+        <v>0.2274647919384222</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2373368522105904</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3107693457382593</v>
+      </c>
+      <c r="C79">
+        <v>-63.49923536513279</v>
+      </c>
+      <c r="D79">
+        <v>121.7429646348672</v>
+      </c>
+      <c r="E79">
+        <v>211.4822</v>
+      </c>
+      <c r="F79">
+        <v>219.3422</v>
+      </c>
+      <c r="G79">
+        <v>34.1</v>
+      </c>
+      <c r="H79">
+        <v>277</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>15.1</v>
+      </c>
+      <c r="K79">
+        <v>2.83</v>
+      </c>
+      <c r="L79">
+        <v>12.27</v>
+      </c>
+      <c r="M79">
+        <v>52.37891736000001</v>
+      </c>
+      <c r="N79">
+        <v>-40.10891736000001</v>
+      </c>
+      <c r="O79">
+        <v>-8.021783471999999</v>
+      </c>
+      <c r="P79">
+        <v>-32.08713388800001</v>
+      </c>
+      <c r="Q79">
+        <v>-29.25713388800001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.589165668978515</v>
+      </c>
+      <c r="T79">
+        <v>4.022050596023024</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04685091108572693</v>
+      </c>
+      <c r="W79">
+        <v>0.2276120024327284</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2342545554286348</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3127693457382593</v>
+      </c>
+      <c r="C80">
+        <v>-67.23656957228874</v>
+      </c>
+      <c r="D80">
+        <v>120.8542304277113</v>
+      </c>
+      <c r="E80">
+        <v>214.3308</v>
+      </c>
+      <c r="F80">
+        <v>222.1908</v>
+      </c>
+      <c r="G80">
+        <v>34.1</v>
+      </c>
+      <c r="H80">
+        <v>277</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>15.1</v>
+      </c>
+      <c r="K80">
+        <v>2.83</v>
+      </c>
+      <c r="L80">
+        <v>12.27</v>
+      </c>
+      <c r="M80">
+        <v>53.05916304000001</v>
+      </c>
+      <c r="N80">
+        <v>-40.78916304000001</v>
+      </c>
+      <c r="O80">
+        <v>-8.157832608</v>
+      </c>
+      <c r="P80">
+        <v>-32.63133043200001</v>
+      </c>
+      <c r="Q80">
+        <v>-29.80133043200001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6141822902957201</v>
+      </c>
+      <c r="T80">
+        <v>4.204871077660434</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04625025837949966</v>
+      </c>
+      <c r="W80">
+        <v>0.2277554382989755</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2312512918974985</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3147693457382593</v>
+      </c>
+      <c r="C81">
+        <v>-70.96102214282993</v>
+      </c>
+      <c r="D81">
+        <v>119.9783778571701</v>
+      </c>
+      <c r="E81">
+        <v>217.1794</v>
+      </c>
+      <c r="F81">
+        <v>225.0394</v>
+      </c>
+      <c r="G81">
+        <v>34.1</v>
+      </c>
+      <c r="H81">
+        <v>277</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>15.1</v>
+      </c>
+      <c r="K81">
+        <v>2.83</v>
+      </c>
+      <c r="L81">
+        <v>12.27</v>
+      </c>
+      <c r="M81">
+        <v>53.73940872000001</v>
+      </c>
+      <c r="N81">
+        <v>-41.46940872</v>
+      </c>
+      <c r="O81">
+        <v>-8.293881743999998</v>
+      </c>
+      <c r="P81">
+        <v>-33.17552697600001</v>
+      </c>
+      <c r="Q81">
+        <v>-30.34552697600001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6415814469764687</v>
+      </c>
+      <c r="T81">
+        <v>4.405103033739502</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.0456648120708984</v>
+      </c>
+      <c r="W81">
+        <v>0.2278952428774695</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2283240603544922</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3167693457382593</v>
+      </c>
+      <c r="C82">
+        <v>-74.67287112835044</v>
+      </c>
+      <c r="D82">
+        <v>119.1151288716496</v>
+      </c>
+      <c r="E82">
+        <v>220.028</v>
+      </c>
+      <c r="F82">
+        <v>227.888</v>
+      </c>
+      <c r="G82">
+        <v>34.1</v>
+      </c>
+      <c r="H82">
+        <v>277</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>15.1</v>
+      </c>
+      <c r="K82">
+        <v>2.83</v>
+      </c>
+      <c r="L82">
+        <v>12.27</v>
+      </c>
+      <c r="M82">
+        <v>54.41965440000001</v>
+      </c>
+      <c r="N82">
+        <v>-42.14965440000002</v>
+      </c>
+      <c r="O82">
+        <v>-8.429930880000002</v>
+      </c>
+      <c r="P82">
+        <v>-33.71972352000002</v>
+      </c>
+      <c r="Q82">
+        <v>-30.88972352000002</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6717205193252922</v>
+      </c>
+      <c r="T82">
+        <v>4.625358185426478</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04509400192001217</v>
+      </c>
+      <c r="W82">
+        <v>0.2280315523415011</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2254700096000608</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3187693457382593</v>
+      </c>
+      <c r="C83">
+        <v>-78.37238663524317</v>
+      </c>
+      <c r="D83">
+        <v>118.2642133647569</v>
+      </c>
+      <c r="E83">
+        <v>222.8766</v>
+      </c>
+      <c r="F83">
+        <v>230.7366</v>
+      </c>
+      <c r="G83">
+        <v>34.1</v>
+      </c>
+      <c r="H83">
+        <v>277</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>15.1</v>
+      </c>
+      <c r="K83">
+        <v>2.83</v>
+      </c>
+      <c r="L83">
+        <v>12.27</v>
+      </c>
+      <c r="M83">
+        <v>55.09990008000001</v>
+      </c>
+      <c r="N83">
+        <v>-42.82990008000002</v>
+      </c>
+      <c r="O83">
+        <v>-8.565980016000001</v>
+      </c>
+      <c r="P83">
+        <v>-34.26392006400002</v>
+      </c>
+      <c r="Q83">
+        <v>-31.43392006400002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.7050321256055709</v>
+      </c>
+      <c r="T83">
+        <v>4.868798089922609</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0445372858469256</v>
+      </c>
+      <c r="W83">
+        <v>0.2281644961397542</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.222686429234628</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3207693457382593</v>
+      </c>
+      <c r="C84">
+        <v>-82.05983110647543</v>
+      </c>
+      <c r="D84">
+        <v>117.4253688935246</v>
+      </c>
+      <c r="E84">
+        <v>225.7252</v>
+      </c>
+      <c r="F84">
+        <v>233.5852</v>
+      </c>
+      <c r="G84">
+        <v>34.1</v>
+      </c>
+      <c r="H84">
+        <v>277</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>15.1</v>
+      </c>
+      <c r="K84">
+        <v>2.83</v>
+      </c>
+      <c r="L84">
+        <v>12.27</v>
+      </c>
+      <c r="M84">
+        <v>55.78014576000001</v>
+      </c>
+      <c r="N84">
+        <v>-43.51014576000001</v>
+      </c>
+      <c r="O84">
+        <v>-8.702029152000001</v>
+      </c>
+      <c r="P84">
+        <v>-34.80811660800001</v>
+      </c>
+      <c r="Q84">
+        <v>-31.97811660800001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7420450214725471</v>
+      </c>
+      <c r="T84">
+        <v>5.139286872696087</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.04399414821464603</v>
+      </c>
+      <c r="W84">
+        <v>0.2282941974063425</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2199707410732301</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3227693457382593</v>
+      </c>
+      <c r="C85">
+        <v>-85.7354595914567</v>
+      </c>
+      <c r="D85">
+        <v>116.5983404085433</v>
+      </c>
+      <c r="E85">
+        <v>228.5738</v>
+      </c>
+      <c r="F85">
+        <v>236.4338</v>
+      </c>
+      <c r="G85">
+        <v>34.1</v>
+      </c>
+      <c r="H85">
+        <v>277</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>15.1</v>
+      </c>
+      <c r="K85">
+        <v>2.83</v>
+      </c>
+      <c r="L85">
+        <v>12.27</v>
+      </c>
+      <c r="M85">
+        <v>56.46039144000001</v>
+      </c>
+      <c r="N85">
+        <v>-44.19039144000001</v>
+      </c>
+      <c r="O85">
+        <v>-8.838078288</v>
+      </c>
+      <c r="P85">
+        <v>-35.35231315200001</v>
+      </c>
+      <c r="Q85">
+        <v>-32.52231315200002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7834123756768145</v>
+      </c>
+      <c r="T85">
+        <v>5.441597865207623</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.04346409823615632</v>
+      </c>
+      <c r="W85">
+        <v>0.2284207733412059</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2173204911807816</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3247693457382593</v>
+      </c>
+      <c r="C86">
+        <v>-89.39952000458266</v>
+      </c>
+      <c r="D86">
+        <v>115.7828799954173</v>
+      </c>
+      <c r="E86">
+        <v>231.4224</v>
+      </c>
+      <c r="F86">
+        <v>239.2824</v>
+      </c>
+      <c r="G86">
+        <v>34.1</v>
+      </c>
+      <c r="H86">
+        <v>277</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>15.1</v>
+      </c>
+      <c r="K86">
+        <v>2.83</v>
+      </c>
+      <c r="L86">
+        <v>12.27</v>
+      </c>
+      <c r="M86">
+        <v>57.14063712</v>
+      </c>
+      <c r="N86">
+        <v>-44.87063712</v>
+      </c>
+      <c r="O86">
+        <v>-8.974127423999997</v>
+      </c>
+      <c r="P86">
+        <v>-35.896509696</v>
+      </c>
+      <c r="Q86">
+        <v>-33.066509696</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8299506491566151</v>
+      </c>
+      <c r="T86">
+        <v>5.781697731783096</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.0429466684952497</v>
+      </c>
+      <c r="W86">
+        <v>0.2285443355633344</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2147333424762486</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3267693457382593</v>
+      </c>
+      <c r="C87">
+        <v>-93.05225337300485</v>
+      </c>
+      <c r="D87">
+        <v>114.9787466269952</v>
+      </c>
+      <c r="E87">
+        <v>234.271</v>
+      </c>
+      <c r="F87">
+        <v>242.131</v>
+      </c>
+      <c r="G87">
+        <v>34.1</v>
+      </c>
+      <c r="H87">
+        <v>277</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>15.1</v>
+      </c>
+      <c r="K87">
+        <v>2.83</v>
+      </c>
+      <c r="L87">
+        <v>12.27</v>
+      </c>
+      <c r="M87">
+        <v>57.8208828</v>
+      </c>
+      <c r="N87">
+        <v>-45.5508828</v>
+      </c>
+      <c r="O87">
+        <v>-9.110176559999998</v>
+      </c>
+      <c r="P87">
+        <v>-36.44070624</v>
+      </c>
+      <c r="Q87">
+        <v>-33.61070624</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8826940257670561</v>
+      </c>
+      <c r="T87">
+        <v>6.167144247235302</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.04244141357177617</v>
+      </c>
+      <c r="W87">
+        <v>0.2286649904390599</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.212207067858881</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3287693457382593</v>
+      </c>
+      <c r="C88">
+        <v>-96.69389407414695</v>
+      </c>
+      <c r="D88">
+        <v>114.185705925853</v>
+      </c>
+      <c r="E88">
+        <v>237.1196</v>
+      </c>
+      <c r="F88">
+        <v>244.9796</v>
+      </c>
+      <c r="G88">
+        <v>34.1</v>
+      </c>
+      <c r="H88">
+        <v>277</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>15.1</v>
+      </c>
+      <c r="K88">
+        <v>2.83</v>
+      </c>
+      <c r="L88">
+        <v>12.27</v>
+      </c>
+      <c r="M88">
+        <v>58.50112848000001</v>
+      </c>
+      <c r="N88">
+        <v>-46.23112848000001</v>
+      </c>
+      <c r="O88">
+        <v>-9.246225696</v>
+      </c>
+      <c r="P88">
+        <v>-36.98490278400001</v>
+      </c>
+      <c r="Q88">
+        <v>-34.15490278400002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9429721704647029</v>
+      </c>
+      <c r="T88">
+        <v>6.607654550609253</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.04194790876280202</v>
+      </c>
+      <c r="W88">
+        <v>0.2287828393874429</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2097395438140102</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3307693457382593</v>
+      </c>
+      <c r="C89">
+        <v>-100.3246700634593</v>
+      </c>
+      <c r="D89">
+        <v>113.4035299365407</v>
+      </c>
+      <c r="E89">
+        <v>239.9682</v>
+      </c>
+      <c r="F89">
+        <v>247.8282</v>
+      </c>
+      <c r="G89">
+        <v>34.1</v>
+      </c>
+      <c r="H89">
+        <v>277</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>15.1</v>
+      </c>
+      <c r="K89">
+        <v>2.83</v>
+      </c>
+      <c r="L89">
+        <v>12.27</v>
+      </c>
+      <c r="M89">
+        <v>59.18137416</v>
+      </c>
+      <c r="N89">
+        <v>-46.91137416000001</v>
+      </c>
+      <c r="O89">
+        <v>-9.382274832</v>
+      </c>
+      <c r="P89">
+        <v>-37.52909932800001</v>
+      </c>
+      <c r="Q89">
+        <v>-34.69909932800001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.012523875885065</v>
+      </c>
+      <c r="T89">
+        <v>7.115935669886887</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04146574889196522</v>
+      </c>
+      <c r="W89">
+        <v>0.2288979791645987</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2073287444598261</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3327693457382593</v>
+      </c>
+      <c r="C90">
+        <v>-103.944803092876</v>
+      </c>
+      <c r="D90">
+        <v>112.631996907124</v>
+      </c>
+      <c r="E90">
+        <v>242.8168</v>
+      </c>
+      <c r="F90">
+        <v>250.6768</v>
+      </c>
+      <c r="G90">
+        <v>34.1</v>
+      </c>
+      <c r="H90">
+        <v>277</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>15.1</v>
+      </c>
+      <c r="K90">
+        <v>2.83</v>
+      </c>
+      <c r="L90">
+        <v>12.27</v>
+      </c>
+      <c r="M90">
+        <v>59.86161984</v>
+      </c>
+      <c r="N90">
+        <v>-47.59161984000001</v>
+      </c>
+      <c r="O90">
+        <v>-9.518323967999999</v>
+      </c>
+      <c r="P90">
+        <v>-38.07329587200001</v>
+      </c>
+      <c r="Q90">
+        <v>-35.24329587200001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.09366753220882</v>
+      </c>
+      <c r="T90">
+        <v>7.708930309044129</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04099454720001108</v>
+      </c>
+      <c r="W90">
+        <v>0.2290105021286374</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2049727360000554</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3347693457382593</v>
+      </c>
+      <c r="C91">
+        <v>-107.5545089204149</v>
+      </c>
+      <c r="D91">
+        <v>111.8708910795851</v>
+      </c>
+      <c r="E91">
+        <v>245.6654</v>
+      </c>
+      <c r="F91">
+        <v>253.5254</v>
+      </c>
+      <c r="G91">
+        <v>34.1</v>
+      </c>
+      <c r="H91">
+        <v>277</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>15.1</v>
+      </c>
+      <c r="K91">
+        <v>2.83</v>
+      </c>
+      <c r="L91">
+        <v>12.27</v>
+      </c>
+      <c r="M91">
+        <v>60.54186552000001</v>
+      </c>
+      <c r="N91">
+        <v>-48.27186552000001</v>
+      </c>
+      <c r="O91">
+        <v>-9.654373103999999</v>
+      </c>
+      <c r="P91">
+        <v>-38.617492416</v>
+      </c>
+      <c r="Q91">
+        <v>-35.78749241600001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.18956458059144</v>
+      </c>
+      <c r="T91">
+        <v>8.409742155320869</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04053393431012331</v>
+      </c>
+      <c r="W91">
+        <v>0.2291204964867426</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2026696715506167</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3367693457382593</v>
+      </c>
+      <c r="C92">
+        <v>-111.1539975113363</v>
+      </c>
+      <c r="D92">
+        <v>111.1200024886637</v>
+      </c>
+      <c r="E92">
+        <v>248.514</v>
+      </c>
+      <c r="F92">
+        <v>256.374</v>
+      </c>
+      <c r="G92">
+        <v>34.1</v>
+      </c>
+      <c r="H92">
+        <v>277</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>15.1</v>
+      </c>
+      <c r="K92">
+        <v>2.83</v>
+      </c>
+      <c r="L92">
+        <v>12.27</v>
+      </c>
+      <c r="M92">
+        <v>61.22211120000001</v>
+      </c>
+      <c r="N92">
+        <v>-48.9521112</v>
+      </c>
+      <c r="O92">
+        <v>-9.790422239999998</v>
+      </c>
+      <c r="P92">
+        <v>-39.16168896000001</v>
+      </c>
+      <c r="Q92">
+        <v>-36.33168896000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.304641038650584</v>
+      </c>
+      <c r="T92">
+        <v>9.250716370852956</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04008355726223305</v>
+      </c>
+      <c r="W92">
+        <v>0.2292280465257788</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2004177863111654</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3387693457382593</v>
+      </c>
+      <c r="C93">
+        <v>-114.7434732312548</v>
+      </c>
+      <c r="D93">
+        <v>110.3791267687452</v>
+      </c>
+      <c r="E93">
+        <v>251.3626</v>
+      </c>
+      <c r="F93">
+        <v>259.2226</v>
+      </c>
+      <c r="G93">
+        <v>34.1</v>
+      </c>
+      <c r="H93">
+        <v>277</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>15.1</v>
+      </c>
+      <c r="K93">
+        <v>2.83</v>
+      </c>
+      <c r="L93">
+        <v>12.27</v>
+      </c>
+      <c r="M93">
+        <v>61.90235688000001</v>
+      </c>
+      <c r="N93">
+        <v>-49.63235688</v>
+      </c>
+      <c r="O93">
+        <v>-9.926471375999999</v>
+      </c>
+      <c r="P93">
+        <v>-39.70588550400001</v>
+      </c>
+      <c r="Q93">
+        <v>-36.87588550400001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.445290042945094</v>
+      </c>
+      <c r="T93">
+        <v>10.27857374539217</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03964307861099972</v>
+      </c>
+      <c r="W93">
+        <v>0.2293332328276933</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1982153930549987</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3407693457382593</v>
+      </c>
+      <c r="C94">
+        <v>-118.3231350315769</v>
+      </c>
+      <c r="D94">
+        <v>109.6480649684231</v>
+      </c>
+      <c r="E94">
+        <v>254.2112</v>
+      </c>
+      <c r="F94">
+        <v>262.0712</v>
+      </c>
+      <c r="G94">
+        <v>34.1</v>
+      </c>
+      <c r="H94">
+        <v>277</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>15.1</v>
+      </c>
+      <c r="K94">
+        <v>2.83</v>
+      </c>
+      <c r="L94">
+        <v>12.27</v>
+      </c>
+      <c r="M94">
+        <v>62.58260256000001</v>
+      </c>
+      <c r="N94">
+        <v>-50.31260256000002</v>
+      </c>
+      <c r="O94">
+        <v>-10.062520512</v>
+      </c>
+      <c r="P94">
+        <v>-40.25008204800002</v>
+      </c>
+      <c r="Q94">
+        <v>-37.42008204800002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.621101298313231</v>
+      </c>
+      <c r="T94">
+        <v>11.5633954635662</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03921217558261928</v>
+      </c>
+      <c r="W94">
+        <v>0.2294361324708705</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1960608779130963</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3427693457382593</v>
+      </c>
+      <c r="C95">
+        <v>-121.8931766276175</v>
+      </c>
+      <c r="D95">
+        <v>108.9266233723825</v>
+      </c>
+      <c r="E95">
+        <v>257.0598</v>
+      </c>
+      <c r="F95">
+        <v>264.9198</v>
+      </c>
+      <c r="G95">
+        <v>34.1</v>
+      </c>
+      <c r="H95">
+        <v>277</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>15.1</v>
+      </c>
+      <c r="K95">
+        <v>2.83</v>
+      </c>
+      <c r="L95">
+        <v>12.27</v>
+      </c>
+      <c r="M95">
+        <v>63.26284824</v>
+      </c>
+      <c r="N95">
+        <v>-50.99284824</v>
+      </c>
+      <c r="O95">
+        <v>-10.198569648</v>
+      </c>
+      <c r="P95">
+        <v>-40.794278592</v>
+      </c>
+      <c r="Q95">
+        <v>-37.96427859200001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.847144340929407</v>
+      </c>
+      <c r="T95">
+        <v>13.21530910121852</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03879053928603198</v>
+      </c>
+      <c r="W95">
+        <v>0.2295368192184956</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.19395269643016</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3447693457382593</v>
+      </c>
+      <c r="C96">
+        <v>-125.4537866697318</v>
+      </c>
+      <c r="D96">
+        <v>108.2146133302682</v>
+      </c>
+      <c r="E96">
+        <v>259.9084</v>
+      </c>
+      <c r="F96">
+        <v>267.7684</v>
+      </c>
+      <c r="G96">
+        <v>34.1</v>
+      </c>
+      <c r="H96">
+        <v>277</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>15.1</v>
+      </c>
+      <c r="K96">
+        <v>2.83</v>
+      </c>
+      <c r="L96">
+        <v>12.27</v>
+      </c>
+      <c r="M96">
+        <v>63.94309392000002</v>
+      </c>
+      <c r="N96">
+        <v>-51.67309392000001</v>
+      </c>
+      <c r="O96">
+        <v>-10.334618784</v>
+      </c>
+      <c r="P96">
+        <v>-41.33847513600001</v>
+      </c>
+      <c r="Q96">
+        <v>-38.50847513600002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.148535064417643</v>
+      </c>
+      <c r="T96">
+        <v>15.41786061808827</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.03837787397447844</v>
+      </c>
+      <c r="W96">
+        <v>0.2296353636948946</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1918893698723924</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3467693457382593</v>
+      </c>
+      <c r="C97">
+        <v>-129.0051489077777</v>
+      </c>
+      <c r="D97">
+        <v>107.5118510922224</v>
+      </c>
+      <c r="E97">
+        <v>262.757</v>
+      </c>
+      <c r="F97">
+        <v>270.617</v>
+      </c>
+      <c r="G97">
+        <v>34.1</v>
+      </c>
+      <c r="H97">
+        <v>277</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>15.1</v>
+      </c>
+      <c r="K97">
+        <v>2.83</v>
+      </c>
+      <c r="L97">
+        <v>12.27</v>
+      </c>
+      <c r="M97">
+        <v>64.62333960000001</v>
+      </c>
+      <c r="N97">
+        <v>-52.35333960000001</v>
+      </c>
+      <c r="O97">
+        <v>-10.47066792</v>
+      </c>
+      <c r="P97">
+        <v>-41.88267168000002</v>
+      </c>
+      <c r="Q97">
+        <v>-39.05267168000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.570482077301173</v>
+      </c>
+      <c r="T97">
+        <v>18.50143274170594</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03797389635369446</v>
+      </c>
+      <c r="W97">
+        <v>0.2297318335507378</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1898694817684723</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3487693457382594</v>
+      </c>
+      <c r="C98">
+        <v>-132.5474423492124</v>
+      </c>
+      <c r="D98">
+        <v>106.8181576507876</v>
+      </c>
+      <c r="E98">
+        <v>265.6056</v>
+      </c>
+      <c r="F98">
+        <v>273.4656</v>
+      </c>
+      <c r="G98">
+        <v>34.1</v>
+      </c>
+      <c r="H98">
+        <v>277</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>15.1</v>
+      </c>
+      <c r="K98">
+        <v>2.83</v>
+      </c>
+      <c r="L98">
+        <v>12.27</v>
+      </c>
+      <c r="M98">
+        <v>65.30358528000001</v>
+      </c>
+      <c r="N98">
+        <v>-53.03358528000001</v>
+      </c>
+      <c r="O98">
+        <v>-10.606717056</v>
+      </c>
+      <c r="P98">
+        <v>-42.42686822400001</v>
+      </c>
+      <c r="Q98">
+        <v>-39.59686822400001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.203402596626458</v>
+      </c>
+      <c r="T98">
+        <v>23.12679092713237</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03757833493334348</v>
+      </c>
+      <c r="W98">
+        <v>0.2298262936179176</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1878916746667174</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3507693457382594</v>
+      </c>
+      <c r="C99">
+        <v>-136.0808414111074</v>
+      </c>
+      <c r="D99">
+        <v>106.1333585888926</v>
+      </c>
+      <c r="E99">
+        <v>268.4542</v>
+      </c>
+      <c r="F99">
+        <v>276.3142</v>
+      </c>
+      <c r="G99">
+        <v>34.1</v>
+      </c>
+      <c r="H99">
+        <v>277</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>15.1</v>
+      </c>
+      <c r="K99">
+        <v>2.83</v>
+      </c>
+      <c r="L99">
+        <v>12.27</v>
+      </c>
+      <c r="M99">
+        <v>65.98383096000001</v>
+      </c>
+      <c r="N99">
+        <v>-53.71383096000001</v>
+      </c>
+      <c r="O99">
+        <v>-10.742766192</v>
+      </c>
+      <c r="P99">
+        <v>-42.97106476800001</v>
+      </c>
+      <c r="Q99">
+        <v>-40.14106476800001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.258270128835278</v>
+      </c>
+      <c r="T99">
+        <v>30.83572123617649</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03719092941856675</v>
+      </c>
+      <c r="W99">
+        <v>0.2299188060548463</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1859546470928337</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3527693457382594</v>
+      </c>
+      <c r="C100">
+        <v>-139.6055160663534</v>
+      </c>
+      <c r="D100">
+        <v>105.4572839336466</v>
+      </c>
+      <c r="E100">
+        <v>271.3028</v>
+      </c>
+      <c r="F100">
+        <v>279.1628</v>
+      </c>
+      <c r="G100">
+        <v>34.1</v>
+      </c>
+      <c r="H100">
+        <v>277</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>15.1</v>
+      </c>
+      <c r="K100">
+        <v>2.83</v>
+      </c>
+      <c r="L100">
+        <v>12.27</v>
+      </c>
+      <c r="M100">
+        <v>66.66407664</v>
+      </c>
+      <c r="N100">
+        <v>-54.39407664000001</v>
+      </c>
+      <c r="O100">
+        <v>-10.878815328</v>
+      </c>
+      <c r="P100">
+        <v>-43.51526131200001</v>
+      </c>
+      <c r="Q100">
+        <v>-40.68526131200001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.368005193252916</v>
+      </c>
+      <c r="T100">
+        <v>46.25358185426473</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03681143013878545</v>
+      </c>
+      <c r="W100">
+        <v>0.230009430482858</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1840571506939273</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3547693457382594</v>
+      </c>
+      <c r="C101">
+        <v>-143.1216319843121</v>
+      </c>
+      <c r="D101">
+        <v>104.7897680156879</v>
+      </c>
+      <c r="E101">
+        <v>274.1514</v>
+      </c>
+      <c r="F101">
+        <v>282.0114</v>
+      </c>
+      <c r="G101">
+        <v>34.1</v>
+      </c>
+      <c r="H101">
+        <v>277</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>15.1</v>
+      </c>
+      <c r="K101">
+        <v>2.83</v>
+      </c>
+      <c r="L101">
+        <v>12.27</v>
+      </c>
+      <c r="M101">
+        <v>67.34432232000002</v>
+      </c>
+      <c r="N101">
+        <v>-55.07432232000002</v>
+      </c>
+      <c r="O101">
+        <v>-11.014864464</v>
+      </c>
+      <c r="P101">
+        <v>-44.05945785600002</v>
+      </c>
+      <c r="Q101">
+        <v>-41.22945785600002</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.69721038650583</v>
+      </c>
+      <c r="T101">
+        <v>92.50716370852946</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03643959751112094</v>
+      </c>
+      <c r="W101">
+        <v>0.2300982241143443</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1821979875556047</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_retail_special_lines.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_retail_special_lines.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1350344024970945</v>
+        <v>0.1348003336921003</v>
       </c>
       <c r="C2">
-        <v>225.1543633765046</v>
+        <v>223.4808201734944</v>
       </c>
       <c r="D2">
-        <v>218.0843633765046</v>
+        <v>218.6579201734944</v>
       </c>
       <c r="E2">
-        <v>-6.51</v>
+        <v>-4.2629</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.2471</v>
       </c>
       <c r="G2">
         <v>7.07</v>
@@ -1451,28 +1451,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.11302913</v>
       </c>
       <c r="N2">
-        <v>9.559999999999999</v>
+        <v>9.446970869999999</v>
       </c>
       <c r="O2">
-        <v>1.912</v>
+        <v>1.889394174</v>
       </c>
       <c r="P2">
-        <v>7.647999999999999</v>
+        <v>7.557576696</v>
       </c>
       <c r="Q2">
-        <v>13.088</v>
+        <v>12.997576696</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1350344024970945</v>
+        <v>0.1357554885778791</v>
       </c>
       <c r="T2">
-        <v>0.9771532823765235</v>
+        <v>0.9850494705169399</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>84.57996624410009</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1348003336921003</v>
+        <v>0.1345662648871061</v>
       </c>
       <c r="C3">
-        <v>223.4808201734944</v>
+        <v>221.8103018077741</v>
       </c>
       <c r="D3">
-        <v>218.6579201734944</v>
+        <v>219.2345018077741</v>
       </c>
       <c r="E3">
-        <v>-4.2629</v>
+        <v>-2.0158</v>
       </c>
       <c r="F3">
-        <v>2.2471</v>
+        <v>4.494199999999999</v>
       </c>
       <c r="G3">
         <v>7.07</v>
@@ -1533,28 +1533,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M3">
-        <v>0.11302913</v>
+        <v>0.22605826</v>
       </c>
       <c r="N3">
-        <v>9.446970869999999</v>
+        <v>9.333941739999998</v>
       </c>
       <c r="O3">
-        <v>1.889394174</v>
+        <v>1.866788348</v>
       </c>
       <c r="P3">
-        <v>7.557576696</v>
+        <v>7.467153391999998</v>
       </c>
       <c r="Q3">
-        <v>12.997576696</v>
+        <v>12.907153392</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1357554885778791</v>
+        <v>0.1364912907011287</v>
       </c>
       <c r="T3">
-        <v>0.9850494705169399</v>
+        <v>0.9931068053540995</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>84.57996624410009</v>
+        <v>42.28998312205005</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1345662648871061</v>
+        <v>0.1343321960821119</v>
       </c>
       <c r="C4">
-        <v>221.8103018077741</v>
+        <v>220.1428322712956</v>
       </c>
       <c r="D4">
-        <v>219.2345018077741</v>
+        <v>219.8141322712956</v>
       </c>
       <c r="E4">
-        <v>-2.0158</v>
+        <v>0.2312999999999992</v>
       </c>
       <c r="F4">
-        <v>4.494199999999999</v>
+        <v>6.741299999999999</v>
       </c>
       <c r="G4">
         <v>7.07</v>
@@ -1615,28 +1615,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M4">
-        <v>0.22605826</v>
+        <v>0.3390873899999999</v>
       </c>
       <c r="N4">
-        <v>9.333941739999998</v>
+        <v>9.220912609999999</v>
       </c>
       <c r="O4">
-        <v>1.866788348</v>
+        <v>1.844182522</v>
       </c>
       <c r="P4">
-        <v>7.467153391999998</v>
+        <v>7.376730088</v>
       </c>
       <c r="Q4">
-        <v>12.907153392</v>
+        <v>12.816730088</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1364912907011287</v>
+        <v>0.1372422640021772</v>
       </c>
       <c r="T4">
-        <v>0.9931068053540995</v>
+        <v>1.001330270806458</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.28998312205005</v>
+        <v>28.1933220813667</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1343321960821119</v>
+        <v>0.1340981272771177</v>
       </c>
       <c r="C5">
-        <v>220.1428322712956</v>
+        <v>218.4784358104103</v>
       </c>
       <c r="D5">
-        <v>219.8141322712956</v>
+        <v>220.3968358104103</v>
       </c>
       <c r="E5">
-        <v>0.2312999999999992</v>
+        <v>2.478399999999999</v>
       </c>
       <c r="F5">
-        <v>6.741299999999999</v>
+        <v>8.988399999999999</v>
       </c>
       <c r="G5">
         <v>7.07</v>
@@ -1697,28 +1697,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M5">
-        <v>0.3390873899999999</v>
+        <v>0.4521165199999999</v>
       </c>
       <c r="N5">
-        <v>9.220912609999999</v>
+        <v>9.107883479999998</v>
       </c>
       <c r="O5">
-        <v>1.844182522</v>
+        <v>1.821576696</v>
       </c>
       <c r="P5">
-        <v>7.376730088</v>
+        <v>7.286306783999999</v>
       </c>
       <c r="Q5">
-        <v>12.816730088</v>
+        <v>12.726306784</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1372422640021772</v>
+        <v>0.1380088825803309</v>
       </c>
       <c r="T5">
-        <v>1.001330270806458</v>
+        <v>1.009725058455741</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.1933220813667</v>
+        <v>21.14499156102502</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1340981272771177</v>
+        <v>0.1338640584721235</v>
       </c>
       <c r="C6">
-        <v>218.4784358104103</v>
+        <v>216.8171369292512</v>
       </c>
       <c r="D6">
-        <v>220.3968358104103</v>
+        <v>220.9826369292512</v>
       </c>
       <c r="E6">
-        <v>2.478399999999999</v>
+        <v>4.7255</v>
       </c>
       <c r="F6">
-        <v>8.988399999999999</v>
+        <v>11.2355</v>
       </c>
       <c r="G6">
         <v>7.07</v>
@@ -1779,28 +1779,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M6">
-        <v>0.4521165199999999</v>
+        <v>0.5651456499999999</v>
       </c>
       <c r="N6">
-        <v>9.107883479999998</v>
+        <v>8.994854349999999</v>
       </c>
       <c r="O6">
-        <v>1.821576696</v>
+        <v>1.79897087</v>
       </c>
       <c r="P6">
-        <v>7.286306783999999</v>
+        <v>7.195883479999999</v>
       </c>
       <c r="Q6">
-        <v>12.726306784</v>
+        <v>12.63588348</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1380088825803309</v>
+        <v>0.1387916404969721</v>
       </c>
       <c r="T6">
-        <v>1.009725058455741</v>
+        <v>1.018296578476588</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.14499156102502</v>
+        <v>16.91599324882002</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1338640584721235</v>
+        <v>0.1336299896671294</v>
       </c>
       <c r="C7">
-        <v>216.8171369292512</v>
+        <v>215.1589603931674</v>
       </c>
       <c r="D7">
-        <v>220.9826369292512</v>
+        <v>221.5715603931674</v>
       </c>
       <c r="E7">
-        <v>4.7255</v>
+        <v>6.9726</v>
       </c>
       <c r="F7">
-        <v>11.2355</v>
+        <v>13.4826</v>
       </c>
       <c r="G7">
         <v>7.07</v>
@@ -1861,28 +1861,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M7">
-        <v>0.5651456499999999</v>
+        <v>0.67817478</v>
       </c>
       <c r="N7">
-        <v>8.994854349999999</v>
+        <v>8.88182522</v>
       </c>
       <c r="O7">
-        <v>1.79897087</v>
+        <v>1.776365044</v>
       </c>
       <c r="P7">
-        <v>7.195883479999999</v>
+        <v>7.105460175999999</v>
       </c>
       <c r="Q7">
-        <v>12.63588348</v>
+        <v>12.545460176</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1387916404969721</v>
+        <v>0.1395910528373716</v>
       </c>
       <c r="T7">
-        <v>1.018296578476588</v>
+        <v>1.027050471263836</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.91599324882002</v>
+        <v>14.09666104068335</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1336299896671294</v>
+        <v>0.1334799208621352</v>
       </c>
       <c r="C8">
-        <v>215.1589603931674</v>
+        <v>213.2910917948606</v>
       </c>
       <c r="D8">
-        <v>221.5715603931674</v>
+        <v>221.9507917948607</v>
       </c>
       <c r="E8">
-        <v>6.972599999999998</v>
+        <v>9.219699999999998</v>
       </c>
       <c r="F8">
-        <v>13.4826</v>
+        <v>15.7297</v>
       </c>
       <c r="G8">
         <v>7.07</v>
@@ -1943,45 +1943,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M8">
-        <v>0.6781747799999999</v>
+        <v>0.8147984599999999</v>
       </c>
       <c r="N8">
-        <v>8.88182522</v>
+        <v>8.745201539999998</v>
       </c>
       <c r="O8">
-        <v>1.776365044</v>
+        <v>1.749040308</v>
       </c>
       <c r="P8">
-        <v>7.105460175999999</v>
+        <v>6.996161231999999</v>
       </c>
       <c r="Q8">
-        <v>12.545460176</v>
+        <v>12.436161232</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1395910528373716</v>
+        <v>0.1404076568410055</v>
       </c>
       <c r="T8">
-        <v>1.027050471263836</v>
+        <v>1.035992619809949</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.09666104068335</v>
+        <v>11.73296277462282</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1334799208621351</v>
+        <v>0.1332578520571409</v>
       </c>
       <c r="C9">
-        <v>213.2910917948607</v>
+        <v>211.6075586552633</v>
       </c>
       <c r="D9">
-        <v>221.9507917948607</v>
+        <v>222.5143586552634</v>
       </c>
       <c r="E9">
-        <v>9.2197</v>
+        <v>11.4668</v>
       </c>
       <c r="F9">
-        <v>15.7297</v>
+        <v>17.9768</v>
       </c>
       <c r="G9">
         <v>7.07</v>
@@ -2025,28 +2025,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M9">
-        <v>0.81479846</v>
+        <v>0.9311982399999998</v>
       </c>
       <c r="N9">
-        <v>8.745201539999998</v>
+        <v>8.628801759999998</v>
       </c>
       <c r="O9">
-        <v>1.749040308</v>
+        <v>1.725760352</v>
       </c>
       <c r="P9">
-        <v>6.996161231999999</v>
+        <v>6.903041407999998</v>
       </c>
       <c r="Q9">
-        <v>12.436161232</v>
+        <v>12.343041408</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1404076568410055</v>
+        <v>0.141242013105588</v>
       </c>
       <c r="T9">
-        <v>1.035992619809949</v>
+        <v>1.045129162889673</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.73296277462282</v>
+        <v>10.26634242779497</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1332578520571409</v>
+        <v>0.1331581832521468</v>
       </c>
       <c r="C10">
-        <v>211.6075586552633</v>
+        <v>209.6143300087599</v>
       </c>
       <c r="D10">
-        <v>222.5143586552634</v>
+        <v>222.7682300087598</v>
       </c>
       <c r="E10">
-        <v>11.4668</v>
+        <v>13.7139</v>
       </c>
       <c r="F10">
-        <v>17.9768</v>
+        <v>20.2239</v>
       </c>
       <c r="G10">
         <v>7.07</v>
@@ -2107,45 +2107,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M10">
-        <v>0.9311982399999998</v>
+        <v>1.08197865</v>
       </c>
       <c r="N10">
-        <v>8.628801759999998</v>
+        <v>8.478021349999999</v>
       </c>
       <c r="O10">
-        <v>1.725760352</v>
+        <v>1.69560427</v>
       </c>
       <c r="P10">
-        <v>6.903041407999998</v>
+        <v>6.782417079999999</v>
       </c>
       <c r="Q10">
-        <v>12.343041408</v>
+        <v>12.22241708</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.141242013105588</v>
+        <v>0.1420947068704909</v>
       </c>
       <c r="T10">
-        <v>1.045129162889673</v>
+        <v>1.054466509114007</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.26634242779497</v>
+        <v>8.835664178770996</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1331581832521468</v>
+        <v>0.1329497144471526</v>
       </c>
       <c r="C11">
-        <v>209.6143300087599</v>
+        <v>207.9001087106029</v>
       </c>
       <c r="D11">
-        <v>222.7682300087598</v>
+        <v>223.3011087106029</v>
       </c>
       <c r="E11">
-        <v>13.7139</v>
+        <v>15.961</v>
       </c>
       <c r="F11">
-        <v>20.2239</v>
+        <v>22.471</v>
       </c>
       <c r="G11">
         <v>7.07</v>
@@ -2189,28 +2189,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M11">
-        <v>1.08197865</v>
+        <v>1.2021985</v>
       </c>
       <c r="N11">
-        <v>8.478021349999999</v>
+        <v>8.357801499999999</v>
       </c>
       <c r="O11">
-        <v>1.69560427</v>
+        <v>1.6715603</v>
       </c>
       <c r="P11">
-        <v>6.782417079999999</v>
+        <v>6.6862412</v>
       </c>
       <c r="Q11">
-        <v>12.22241708</v>
+        <v>12.1262412</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1420947068704909</v>
+        <v>0.1429663493857251</v>
       </c>
       <c r="T11">
-        <v>1.054466509114007</v>
+        <v>1.064011351921103</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.835664178770996</v>
+        <v>7.952097760893897</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1329497144471526</v>
+        <v>0.1328116456421584</v>
       </c>
       <c r="C12">
-        <v>207.9001087106028</v>
+        <v>206.0073396395954</v>
       </c>
       <c r="D12">
-        <v>223.3011087106028</v>
+        <v>223.6554396395954</v>
       </c>
       <c r="E12">
-        <v>15.961</v>
+        <v>18.20809999999999</v>
       </c>
       <c r="F12">
-        <v>22.471</v>
+        <v>24.7181</v>
       </c>
       <c r="G12">
         <v>7.07</v>
@@ -2271,45 +2271,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M12">
-        <v>1.2021985</v>
+        <v>1.34219283</v>
       </c>
       <c r="N12">
-        <v>8.357801499999999</v>
+        <v>8.217807169999999</v>
       </c>
       <c r="O12">
-        <v>1.6715603</v>
+        <v>1.643561434</v>
       </c>
       <c r="P12">
-        <v>6.6862412</v>
+        <v>6.574245735999999</v>
       </c>
       <c r="Q12">
-        <v>12.1262412</v>
+        <v>12.014245736</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1429663493857251</v>
+        <v>0.1438575793732117</v>
       </c>
       <c r="T12">
-        <v>1.064011351921104</v>
+        <v>1.073770685577798</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.952097760893895</v>
+        <v>7.122672529848039</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1328116456421584</v>
+        <v>0.1326095768371642</v>
       </c>
       <c r="C13">
-        <v>206.0073396395954</v>
+        <v>204.2808479533902</v>
       </c>
       <c r="D13">
-        <v>223.6554396395954</v>
+        <v>224.1760479533901</v>
       </c>
       <c r="E13">
-        <v>18.20809999999999</v>
+        <v>20.4552</v>
       </c>
       <c r="F13">
-        <v>24.7181</v>
+        <v>26.9652</v>
       </c>
       <c r="G13">
         <v>7.07</v>
@@ -2353,28 +2353,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M13">
-        <v>1.34219283</v>
+        <v>1.46421036</v>
       </c>
       <c r="N13">
-        <v>8.217807169999999</v>
+        <v>8.09578964</v>
       </c>
       <c r="O13">
-        <v>1.643561434</v>
+        <v>1.619157928</v>
       </c>
       <c r="P13">
-        <v>6.574245735999999</v>
+        <v>6.476631712</v>
       </c>
       <c r="Q13">
-        <v>12.014245736</v>
+        <v>11.916631712</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1438575793732117</v>
+        <v>0.1447690645876866</v>
       </c>
       <c r="T13">
-        <v>1.073770685577798</v>
+        <v>1.083751822272144</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.122672529848039</v>
+        <v>6.529116485694037</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1326095768371642</v>
+        <v>0.13251150803217</v>
       </c>
       <c r="C14">
-        <v>204.2808479533902</v>
+        <v>202.2872861241592</v>
       </c>
       <c r="D14">
-        <v>224.1760479533901</v>
+        <v>224.4295861241592</v>
       </c>
       <c r="E14">
-        <v>20.4552</v>
+        <v>22.7023</v>
       </c>
       <c r="F14">
-        <v>26.9652</v>
+        <v>29.2123</v>
       </c>
       <c r="G14">
         <v>7.07</v>
@@ -2435,45 +2435,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M14">
-        <v>1.46421036</v>
+        <v>1.61544019</v>
       </c>
       <c r="N14">
-        <v>8.09578964</v>
+        <v>7.944559809999999</v>
       </c>
       <c r="O14">
-        <v>1.619157928</v>
+        <v>1.588911962</v>
       </c>
       <c r="P14">
-        <v>6.476631712</v>
+        <v>6.355647847999998</v>
       </c>
       <c r="Q14">
-        <v>11.916631712</v>
+        <v>11.795647848</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1447690645876866</v>
+        <v>0.1457015034852529</v>
       </c>
       <c r="T14">
-        <v>1.083751822272144</v>
+        <v>1.093962410384752</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.529116485694037</v>
+        <v>5.917891642896416</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.13251150803217</v>
+        <v>0.1323174392271758</v>
       </c>
       <c r="C15">
-        <v>202.2872861241592</v>
+        <v>200.5436081159971</v>
       </c>
       <c r="D15">
-        <v>224.4295861241592</v>
+        <v>224.9330081159971</v>
       </c>
       <c r="E15">
-        <v>22.7023</v>
+        <v>24.9494</v>
       </c>
       <c r="F15">
-        <v>29.2123</v>
+        <v>31.4594</v>
       </c>
       <c r="G15">
         <v>7.07</v>
@@ -2517,28 +2517,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M15">
-        <v>1.61544019</v>
+        <v>1.73970482</v>
       </c>
       <c r="N15">
-        <v>7.944559809999999</v>
+        <v>7.820295179999999</v>
       </c>
       <c r="O15">
-        <v>1.588911962</v>
+        <v>1.564059036</v>
       </c>
       <c r="P15">
-        <v>6.355647847999998</v>
+        <v>6.256236143999999</v>
       </c>
       <c r="Q15">
-        <v>11.795647848</v>
+        <v>11.696236144</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1457015034852529</v>
+        <v>0.146655627008344</v>
       </c>
       <c r="T15">
-        <v>1.093962410384752</v>
+        <v>1.104410454034862</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.917891642896416</v>
+        <v>5.495185096975243</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1323174392271758</v>
+        <v>0.1321233704221816</v>
       </c>
       <c r="C16">
-        <v>200.5436081159971</v>
+        <v>198.8021936548647</v>
       </c>
       <c r="D16">
-        <v>224.9330081159971</v>
+        <v>225.4386936548647</v>
       </c>
       <c r="E16">
-        <v>24.9494</v>
+        <v>27.19650000000001</v>
       </c>
       <c r="F16">
-        <v>31.4594</v>
+        <v>33.70650000000001</v>
       </c>
       <c r="G16">
         <v>7.07</v>
@@ -2599,28 +2599,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M16">
-        <v>1.73970482</v>
+        <v>1.86396945</v>
       </c>
       <c r="N16">
-        <v>7.820295179999999</v>
+        <v>7.696030549999998</v>
       </c>
       <c r="O16">
-        <v>1.564059036</v>
+        <v>1.53920611</v>
       </c>
       <c r="P16">
-        <v>6.256236143999999</v>
+        <v>6.156824439999999</v>
       </c>
       <c r="Q16">
-        <v>11.696236144</v>
+        <v>11.59682444</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.146655627008344</v>
+        <v>0.1476322004966843</v>
       </c>
       <c r="T16">
-        <v>1.104410454034862</v>
+        <v>1.11510433400615</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.495185096975243</v>
+        <v>5.12883942384356</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1321233704221816</v>
+        <v>0.1319293016171874</v>
       </c>
       <c r="C17">
-        <v>198.8021936548647</v>
+        <v>197.0630580416133</v>
       </c>
       <c r="D17">
-        <v>225.4386936548647</v>
+        <v>225.9466580416133</v>
       </c>
       <c r="E17">
-        <v>27.1965</v>
+        <v>29.4436</v>
       </c>
       <c r="F17">
-        <v>33.7065</v>
+        <v>35.95359999999999</v>
       </c>
       <c r="G17">
         <v>7.07</v>
@@ -2681,28 +2681,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M17">
-        <v>1.86396945</v>
+        <v>1.98823408</v>
       </c>
       <c r="N17">
-        <v>7.696030549999999</v>
+        <v>7.571765919999999</v>
       </c>
       <c r="O17">
-        <v>1.53920611</v>
+        <v>1.514353184</v>
       </c>
       <c r="P17">
-        <v>6.156824439999999</v>
+        <v>6.057412735999999</v>
       </c>
       <c r="Q17">
-        <v>11.59682444</v>
+        <v>11.497412736</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1476322004966843</v>
+        <v>0.148632025734747</v>
       </c>
       <c r="T17">
-        <v>1.11510433400615</v>
+        <v>1.126052830167232</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.128839423843561</v>
+        <v>4.808286959853339</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1319293016171874</v>
+        <v>0.1317352328121932</v>
       </c>
       <c r="C18">
-        <v>197.0630580416133</v>
+        <v>195.32621671531</v>
       </c>
       <c r="D18">
-        <v>225.9466580416133</v>
+        <v>226.45691671531</v>
       </c>
       <c r="E18">
-        <v>29.4436</v>
+        <v>31.6907</v>
       </c>
       <c r="F18">
-        <v>35.95359999999999</v>
+        <v>38.2007</v>
       </c>
       <c r="G18">
         <v>7.07</v>
@@ -2763,28 +2763,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M18">
-        <v>1.98823408</v>
+        <v>2.11249871</v>
       </c>
       <c r="N18">
-        <v>7.571765919999999</v>
+        <v>7.447501289999998</v>
       </c>
       <c r="O18">
-        <v>1.514353184</v>
+        <v>1.489500258</v>
       </c>
       <c r="P18">
-        <v>6.057412735999999</v>
+        <v>5.958001031999999</v>
       </c>
       <c r="Q18">
-        <v>11.497412736</v>
+        <v>11.398001032</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.148632025734747</v>
+        <v>0.1496559431472208</v>
       </c>
       <c r="T18">
-        <v>1.126052830167232</v>
+        <v>1.137265145512918</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.808286959853339</v>
+        <v>4.5254465504502</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1317352328121932</v>
+        <v>0.1319011640071991</v>
       </c>
       <c r="C19">
-        <v>195.32621671531</v>
+        <v>192.6426967523376</v>
       </c>
       <c r="D19">
-        <v>226.45691671531</v>
+        <v>226.0204967523376</v>
       </c>
       <c r="E19">
-        <v>31.6907</v>
+        <v>33.9378</v>
       </c>
       <c r="F19">
-        <v>38.2007</v>
+        <v>40.4478</v>
       </c>
       <c r="G19">
         <v>7.07</v>
@@ -2845,45 +2845,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M19">
-        <v>2.11249871</v>
+        <v>2.33788284</v>
       </c>
       <c r="N19">
-        <v>7.447501289999998</v>
+        <v>7.222117159999998</v>
       </c>
       <c r="O19">
-        <v>1.489500258</v>
+        <v>1.444423432</v>
       </c>
       <c r="P19">
-        <v>5.958001031999999</v>
+        <v>5.777693727999998</v>
       </c>
       <c r="Q19">
-        <v>11.398001032</v>
+        <v>11.217693728</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1496559431472208</v>
+        <v>0.1507048341551208</v>
       </c>
       <c r="T19">
-        <v>1.137265145512918</v>
+        <v>1.148750931964596</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.5254465504502</v>
+        <v>4.089169840521178</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1319011640071991</v>
+        <v>0.1322590952022049</v>
       </c>
       <c r="C20">
-        <v>192.6426967523376</v>
+        <v>189.4598966237488</v>
       </c>
       <c r="D20">
-        <v>226.0204967523376</v>
+        <v>225.0847966237488</v>
       </c>
       <c r="E20">
-        <v>33.9378</v>
+        <v>36.1849</v>
       </c>
       <c r="F20">
-        <v>40.44779999999999</v>
+        <v>42.6949</v>
       </c>
       <c r="G20">
         <v>7.07</v>
@@ -2927,45 +2927,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M20">
-        <v>2.33788284</v>
+        <v>2.61719737</v>
       </c>
       <c r="N20">
-        <v>7.222117159999999</v>
+        <v>6.942802629999999</v>
       </c>
       <c r="O20">
-        <v>1.444423432</v>
+        <v>1.388560526</v>
       </c>
       <c r="P20">
-        <v>5.777693727999999</v>
+        <v>5.554242103999999</v>
       </c>
       <c r="Q20">
-        <v>11.217693728</v>
+        <v>10.994242104</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1507048341551208</v>
+        <v>0.1517796237064258</v>
       </c>
       <c r="T20">
-        <v>1.148750931964596</v>
+        <v>1.160520318081748</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.2</v>
       </c>
       <c r="W20">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.089169840521178</v>
+        <v>3.652762344018403</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1322590952022049</v>
+        <v>0.1325610263972107</v>
       </c>
       <c r="C21">
-        <v>189.4598966237488</v>
+        <v>186.4294942073953</v>
       </c>
       <c r="D21">
-        <v>225.0847966237488</v>
+        <v>224.3014942073953</v>
       </c>
       <c r="E21">
-        <v>36.1849</v>
+        <v>38.432</v>
       </c>
       <c r="F21">
-        <v>42.6949</v>
+        <v>44.942</v>
       </c>
       <c r="G21">
         <v>7.07</v>
@@ -3009,45 +3009,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M21">
-        <v>2.61719737</v>
+        <v>2.8807822</v>
       </c>
       <c r="N21">
-        <v>6.942802629999999</v>
+        <v>6.679217799999998</v>
       </c>
       <c r="O21">
-        <v>1.388560526</v>
+        <v>1.33584356</v>
       </c>
       <c r="P21">
-        <v>5.554242103999999</v>
+        <v>5.343374239999998</v>
       </c>
       <c r="Q21">
-        <v>10.994242104</v>
+        <v>10.78337424</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1517796237064258</v>
+        <v>0.1528812829965134</v>
       </c>
       <c r="T21">
-        <v>1.160520318081748</v>
+        <v>1.172583938851828</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.2</v>
       </c>
       <c r="W21">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.652762344018403</v>
+        <v>3.318543137346516</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1325610263972107</v>
+        <v>0.1324373575922165</v>
       </c>
       <c r="C22">
-        <v>186.4294942073953</v>
+        <v>184.5025689970928</v>
       </c>
       <c r="D22">
-        <v>224.3014942073953</v>
+        <v>224.6216689970928</v>
       </c>
       <c r="E22">
-        <v>38.432</v>
+        <v>40.67910000000001</v>
       </c>
       <c r="F22">
-        <v>44.942</v>
+        <v>47.1891</v>
       </c>
       <c r="G22">
         <v>7.07</v>
@@ -3091,28 +3091,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M22">
-        <v>2.8807822</v>
+        <v>3.024821310000001</v>
       </c>
       <c r="N22">
-        <v>6.679217799999998</v>
+        <v>6.535178689999999</v>
       </c>
       <c r="O22">
-        <v>1.33584356</v>
+        <v>1.307035738</v>
       </c>
       <c r="P22">
-        <v>5.343374239999998</v>
+        <v>5.228142951999999</v>
       </c>
       <c r="Q22">
-        <v>10.78337424</v>
+        <v>10.668142952</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1528812829965134</v>
+        <v>0.1540108323952108</v>
       </c>
       <c r="T22">
-        <v>1.172583938851828</v>
+        <v>1.18495296774267</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.318543137346516</v>
+        <v>3.160517273663348</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1324373575922165</v>
+        <v>0.1323136887872223</v>
       </c>
       <c r="C23">
-        <v>184.5025689970928</v>
+        <v>182.5765591479126</v>
       </c>
       <c r="D23">
-        <v>224.6216689970928</v>
+        <v>224.9427591479126</v>
       </c>
       <c r="E23">
-        <v>40.6791</v>
+        <v>42.92619999999999</v>
       </c>
       <c r="F23">
-        <v>47.1891</v>
+        <v>49.43619999999999</v>
       </c>
       <c r="G23">
         <v>7.07</v>
@@ -3173,28 +3173,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M23">
-        <v>3.02482131</v>
+        <v>3.16886042</v>
       </c>
       <c r="N23">
-        <v>6.535178689999999</v>
+        <v>6.391139579999999</v>
       </c>
       <c r="O23">
-        <v>1.307035738</v>
+        <v>1.278227916</v>
       </c>
       <c r="P23">
-        <v>5.228142951999999</v>
+        <v>5.112911663999999</v>
       </c>
       <c r="Q23">
-        <v>10.668142952</v>
+        <v>10.552911664</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1540108323952108</v>
+        <v>0.155169344599003</v>
       </c>
       <c r="T23">
-        <v>1.18495296774267</v>
+        <v>1.197639151220457</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.160517273663348</v>
+        <v>3.016857397587742</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1323136887872223</v>
+        <v>0.1336252199822281</v>
       </c>
       <c r="C24">
-        <v>182.5765591479126</v>
+        <v>176.9702936852715</v>
       </c>
       <c r="D24">
-        <v>224.9427591479126</v>
+        <v>221.5835936852715</v>
       </c>
       <c r="E24">
-        <v>42.92619999999999</v>
+        <v>45.1733</v>
       </c>
       <c r="F24">
-        <v>49.43619999999999</v>
+        <v>51.6833</v>
       </c>
       <c r="G24">
         <v>7.07</v>
@@ -3255,45 +3255,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M24">
-        <v>3.16886042</v>
+        <v>3.71602927</v>
       </c>
       <c r="N24">
-        <v>6.391139579999999</v>
+        <v>5.843970729999999</v>
       </c>
       <c r="O24">
-        <v>1.278227916</v>
+        <v>1.168794146</v>
       </c>
       <c r="P24">
-        <v>5.112911663999999</v>
+        <v>4.675176583999999</v>
       </c>
       <c r="Q24">
-        <v>10.552911664</v>
+        <v>10.115176584</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.155169344599003</v>
+        <v>0.1563579480288677</v>
       </c>
       <c r="T24">
-        <v>1.197639151220457</v>
+        <v>1.210654845957407</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.2</v>
       </c>
       <c r="W24">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.016857397587742</v>
+        <v>2.57263850884576</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1336252199822281</v>
+        <v>0.1343127511772339</v>
       </c>
       <c r="C25">
-        <v>176.9702936852715</v>
+        <v>173.0020220920954</v>
       </c>
       <c r="D25">
-        <v>221.5835936852715</v>
+        <v>219.8624220920954</v>
       </c>
       <c r="E25">
-        <v>45.1733</v>
+        <v>47.4204</v>
       </c>
       <c r="F25">
-        <v>51.6833</v>
+        <v>53.9304</v>
       </c>
       <c r="G25">
         <v>7.07</v>
@@ -3337,45 +3337,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M25">
-        <v>3.71602927</v>
+        <v>4.08792432</v>
       </c>
       <c r="N25">
-        <v>5.843970729999999</v>
+        <v>5.472075679999999</v>
       </c>
       <c r="O25">
-        <v>1.168794146</v>
+        <v>1.094415136</v>
       </c>
       <c r="P25">
-        <v>4.675176583999999</v>
+        <v>4.377660543999999</v>
       </c>
       <c r="Q25">
-        <v>10.115176584</v>
+        <v>9.817660543999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1563579480288677</v>
+        <v>0.1575778304963604</v>
       </c>
       <c r="T25">
-        <v>1.210654845957407</v>
+        <v>1.224013058976908</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.57263850884576</v>
+        <v>2.338595152857428</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1343127511772339</v>
+        <v>0.1342826823722397</v>
       </c>
       <c r="C26">
-        <v>173.0020220920954</v>
+        <v>170.8296372806295</v>
       </c>
       <c r="D26">
-        <v>219.8624220920954</v>
+        <v>219.9371372806295</v>
       </c>
       <c r="E26">
-        <v>47.42039999999999</v>
+        <v>49.6675</v>
       </c>
       <c r="F26">
-        <v>53.93039999999999</v>
+        <v>56.17749999999999</v>
       </c>
       <c r="G26">
         <v>7.07</v>
@@ -3419,28 +3419,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M26">
-        <v>4.08792432</v>
+        <v>4.2582545</v>
       </c>
       <c r="N26">
-        <v>5.472075679999999</v>
+        <v>5.301745499999999</v>
       </c>
       <c r="O26">
-        <v>1.094415136</v>
+        <v>1.0603491</v>
       </c>
       <c r="P26">
-        <v>4.377660543999999</v>
+        <v>4.241396399999999</v>
       </c>
       <c r="Q26">
-        <v>9.817660543999999</v>
+        <v>9.681396400000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1575778304963604</v>
+        <v>0.1588302431629863</v>
       </c>
       <c r="T26">
-        <v>1.224013058976908</v>
+        <v>1.237727491010263</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.338595152857428</v>
+        <v>2.245051346743131</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1342826823722397</v>
+        <v>0.1342526135672455</v>
       </c>
       <c r="C27">
-        <v>170.8296372806295</v>
+        <v>168.6573032669035</v>
       </c>
       <c r="D27">
-        <v>219.9371372806295</v>
+        <v>220.0119032669035</v>
       </c>
       <c r="E27">
-        <v>49.6675</v>
+        <v>51.9146</v>
       </c>
       <c r="F27">
-        <v>56.17749999999999</v>
+        <v>58.4246</v>
       </c>
       <c r="G27">
         <v>7.07</v>
@@ -3501,28 +3501,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M27">
-        <v>4.2582545</v>
+        <v>4.42858468</v>
       </c>
       <c r="N27">
-        <v>5.301745499999999</v>
+        <v>5.131415319999999</v>
       </c>
       <c r="O27">
-        <v>1.0603491</v>
+        <v>1.026283064</v>
       </c>
       <c r="P27">
-        <v>4.241396399999999</v>
+        <v>4.105132255999999</v>
       </c>
       <c r="Q27">
-        <v>9.681396400000001</v>
+        <v>9.545132255999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1588302431629863</v>
+        <v>0.1601165048206021</v>
       </c>
       <c r="T27">
-        <v>1.237727491010263</v>
+        <v>1.251812583368844</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.245051346743131</v>
+        <v>2.158703218022241</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1342526135672455</v>
+        <v>0.1342225447622513</v>
       </c>
       <c r="C28">
-        <v>168.6573032669035</v>
+        <v>166.4850201027401</v>
       </c>
       <c r="D28">
-        <v>220.0119032669035</v>
+        <v>220.0867201027401</v>
       </c>
       <c r="E28">
-        <v>51.9146</v>
+        <v>54.1617</v>
       </c>
       <c r="F28">
-        <v>58.4246</v>
+        <v>60.6717</v>
       </c>
       <c r="G28">
         <v>7.07</v>
@@ -3583,28 +3583,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M28">
-        <v>4.42858468</v>
+        <v>4.598914860000001</v>
       </c>
       <c r="N28">
-        <v>5.131415319999999</v>
+        <v>4.961085139999998</v>
       </c>
       <c r="O28">
-        <v>1.026283064</v>
+        <v>0.9922170279999997</v>
       </c>
       <c r="P28">
-        <v>4.105132255999999</v>
+        <v>3.968868111999998</v>
       </c>
       <c r="Q28">
-        <v>9.545132255999999</v>
+        <v>9.408868111999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1601165048206021</v>
+        <v>0.161438006523632</v>
       </c>
       <c r="T28">
-        <v>1.251812583368844</v>
+        <v>1.266283568668755</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.158703218022241</v>
+        <v>2.07875124698438</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1342225447622513</v>
+        <v>0.1341924759572572</v>
       </c>
       <c r="C29">
-        <v>166.4850201027401</v>
+        <v>164.3127878400323</v>
       </c>
       <c r="D29">
-        <v>220.0867201027401</v>
+        <v>220.1615878400324</v>
       </c>
       <c r="E29">
-        <v>54.1617</v>
+        <v>56.4088</v>
       </c>
       <c r="F29">
-        <v>60.6717</v>
+        <v>62.9188</v>
       </c>
       <c r="G29">
         <v>7.07</v>
@@ -3665,28 +3665,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M29">
-        <v>4.598914860000001</v>
+        <v>4.76924504</v>
       </c>
       <c r="N29">
-        <v>4.961085139999998</v>
+        <v>4.790754959999998</v>
       </c>
       <c r="O29">
-        <v>0.9922170279999997</v>
+        <v>0.9581509919999998</v>
       </c>
       <c r="P29">
-        <v>3.968868111999998</v>
+        <v>3.832603967999999</v>
       </c>
       <c r="Q29">
-        <v>9.408868111999999</v>
+        <v>9.272603967999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.161438006523632</v>
+        <v>0.1627962166073016</v>
       </c>
       <c r="T29">
-        <v>1.266283568668755</v>
+        <v>1.281156525782553</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.07875124698438</v>
+        <v>2.004510131020653</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1341924759572572</v>
+        <v>0.137456807152263</v>
       </c>
       <c r="C30">
-        <v>164.3127878400323</v>
+        <v>154.2246953217752</v>
       </c>
       <c r="D30">
-        <v>220.1615878400324</v>
+        <v>212.3205953217753</v>
       </c>
       <c r="E30">
-        <v>56.4088</v>
+        <v>58.65590000000001</v>
       </c>
       <c r="F30">
-        <v>62.9188</v>
+        <v>65.16590000000001</v>
       </c>
       <c r="G30">
         <v>7.07</v>
@@ -3747,45 +3747,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M30">
-        <v>4.76924504</v>
+        <v>5.864931</v>
       </c>
       <c r="N30">
-        <v>4.790754959999998</v>
+        <v>3.695068999999998</v>
       </c>
       <c r="O30">
-        <v>0.9581509919999998</v>
+        <v>0.7390137999999997</v>
       </c>
       <c r="P30">
-        <v>3.832603967999999</v>
+        <v>2.956055199999999</v>
       </c>
       <c r="Q30">
-        <v>9.272603967999999</v>
+        <v>8.396055199999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1627962166073016</v>
+        <v>0.1641926861299479</v>
       </c>
       <c r="T30">
-        <v>1.281156525782553</v>
+        <v>1.296448439434768</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.2</v>
       </c>
       <c r="W30">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.004510131020653</v>
+        <v>1.630027701945683</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.137456807152263</v>
+        <v>0.1375403383472688</v>
       </c>
       <c r="C31">
-        <v>154.2246953217753</v>
+        <v>151.7842736775446</v>
       </c>
       <c r="D31">
-        <v>212.3205953217753</v>
+        <v>212.1272736775446</v>
       </c>
       <c r="E31">
-        <v>58.6559</v>
+        <v>60.903</v>
       </c>
       <c r="F31">
-        <v>65.16589999999999</v>
+        <v>67.413</v>
       </c>
       <c r="G31">
         <v>7.07</v>
@@ -3829,28 +3829,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M31">
-        <v>5.864930999999999</v>
+        <v>6.067169999999999</v>
       </c>
       <c r="N31">
-        <v>3.695068999999999</v>
+        <v>3.49283</v>
       </c>
       <c r="O31">
-        <v>0.7390137999999999</v>
+        <v>0.698566</v>
       </c>
       <c r="P31">
-        <v>2.956055199999999</v>
+        <v>2.794264</v>
       </c>
       <c r="Q31">
-        <v>8.396055199999999</v>
+        <v>8.234264</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1641926861299479</v>
+        <v>0.1656290547818126</v>
       </c>
       <c r="T31">
-        <v>1.296448439434768</v>
+        <v>1.312177264905617</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.630027701945683</v>
+        <v>1.575693445214161</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1375403383472688</v>
+        <v>0.1376238695422746</v>
       </c>
       <c r="C32">
-        <v>151.7842736775446</v>
+        <v>149.3442037585907</v>
       </c>
       <c r="D32">
-        <v>212.1272736775446</v>
+        <v>211.9343037585907</v>
       </c>
       <c r="E32">
-        <v>60.903</v>
+        <v>63.1501</v>
       </c>
       <c r="F32">
-        <v>67.413</v>
+        <v>69.6601</v>
       </c>
       <c r="G32">
         <v>7.07</v>
@@ -3911,28 +3911,28 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M32">
-        <v>6.067169999999999</v>
+        <v>6.269409</v>
       </c>
       <c r="N32">
-        <v>3.49283</v>
+        <v>3.290590999999999</v>
       </c>
       <c r="O32">
-        <v>0.698566</v>
+        <v>0.6581181999999999</v>
       </c>
       <c r="P32">
-        <v>2.794264</v>
+        <v>2.6324728</v>
       </c>
       <c r="Q32">
-        <v>8.234264</v>
+        <v>8.0724728</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1656290547818126</v>
+        <v>0.1671070573076443</v>
       </c>
       <c r="T32">
-        <v>1.312177264905617</v>
+        <v>1.328361998361129</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.575693445214161</v>
+        <v>1.524864624400801</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1376238695422746</v>
+        <v>0.1536735002583857</v>
       </c>
       <c r="C33">
-        <v>149.3442037585907</v>
+        <v>115.5651028199535</v>
       </c>
       <c r="D33">
-        <v>211.9343037585907</v>
+        <v>180.4023028199535</v>
       </c>
       <c r="E33">
-        <v>63.1501</v>
+        <v>65.39719999999998</v>
       </c>
       <c r="F33">
-        <v>69.6601</v>
+        <v>71.90719999999999</v>
       </c>
       <c r="G33">
         <v>7.07</v>
@@ -3993,45 +3993,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M33">
-        <v>6.269409</v>
+        <v>10.55597696</v>
       </c>
       <c r="N33">
-        <v>3.290590999999999</v>
+        <v>-0.9959769600000001</v>
       </c>
       <c r="O33">
-        <v>0.6581181999999999</v>
+        <v>-0.199195392</v>
       </c>
       <c r="P33">
-        <v>2.6324728</v>
+        <v>-0.7967815680000001</v>
       </c>
       <c r="Q33">
-        <v>8.0724728</v>
+        <v>4.643218432</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1671070573076443</v>
+        <v>0.1694209483272679</v>
       </c>
       <c r="T33">
-        <v>1.328361998361129</v>
+        <v>1.35370005343423</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2</v>
+        <v>0.1811296109536033</v>
       </c>
       <c r="W33">
-        <v>0.07199999999999999</v>
+        <v>0.120210173112011</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.524864624400801</v>
+        <v>0.9056480547680165</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1536735002583857</v>
+        <v>0.1546835002583857</v>
       </c>
       <c r="C34">
-        <v>115.5651028199535</v>
+        <v>111.6445966067461</v>
       </c>
       <c r="D34">
-        <v>180.4023028199535</v>
+        <v>178.7288966067461</v>
       </c>
       <c r="E34">
-        <v>65.39719999999998</v>
+        <v>67.64429999999999</v>
       </c>
       <c r="F34">
-        <v>71.90719999999999</v>
+        <v>74.15429999999999</v>
       </c>
       <c r="G34">
         <v>7.07</v>
@@ -4075,37 +4075,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M34">
-        <v>10.55597696</v>
+        <v>10.88585124</v>
       </c>
       <c r="N34">
-        <v>-0.9959769600000001</v>
+        <v>-1.32585124</v>
       </c>
       <c r="O34">
-        <v>-0.199195392</v>
+        <v>-0.2651702480000001</v>
       </c>
       <c r="P34">
-        <v>-0.7967815680000001</v>
+        <v>-1.060680992</v>
       </c>
       <c r="Q34">
-        <v>4.643218432</v>
+        <v>4.379319008</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1694209483272679</v>
+        <v>0.1712660371082719</v>
       </c>
       <c r="T34">
-        <v>1.35370005343423</v>
+        <v>1.373904531843697</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.1811296109536033</v>
+        <v>0.1756408348641002</v>
       </c>
       <c r="W34">
-        <v>0.120210173112011</v>
+        <v>0.1210159254419501</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9056480547680165</v>
+        <v>0.8782041743205008</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1546835002583857</v>
+        <v>0.1556935002583857</v>
       </c>
       <c r="C35">
-        <v>111.6445966067461</v>
+        <v>107.7548499975437</v>
       </c>
       <c r="D35">
-        <v>178.7288966067461</v>
+        <v>177.0862499975437</v>
       </c>
       <c r="E35">
-        <v>67.64429999999999</v>
+        <v>69.89139999999999</v>
       </c>
       <c r="F35">
-        <v>74.15429999999999</v>
+        <v>76.4014</v>
       </c>
       <c r="G35">
         <v>7.07</v>
@@ -4157,37 +4157,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M35">
-        <v>10.88585124</v>
+        <v>11.21572552</v>
       </c>
       <c r="N35">
-        <v>-1.32585124</v>
+        <v>-1.655725520000003</v>
       </c>
       <c r="O35">
-        <v>-0.2651702480000001</v>
+        <v>-0.3311451040000005</v>
       </c>
       <c r="P35">
-        <v>-1.060680992</v>
+        <v>-1.324580416000002</v>
       </c>
       <c r="Q35">
-        <v>4.379319008</v>
+        <v>4.115419583999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1712660371082719</v>
+        <v>0.1731670376705184</v>
       </c>
       <c r="T35">
-        <v>1.373904531843697</v>
+        <v>1.394721267174662</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.1756408348641002</v>
+        <v>0.1704749279563325</v>
       </c>
       <c r="W35">
-        <v>0.1210159254419501</v>
+        <v>0.1217742805760104</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8782041743205008</v>
+        <v>0.8523746397816624</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1556935002583857</v>
+        <v>0.1567035002583857</v>
       </c>
       <c r="C36">
-        <v>107.7548499975437</v>
+        <v>103.8950226076884</v>
       </c>
       <c r="D36">
-        <v>177.0862499975437</v>
+        <v>175.4735226076884</v>
       </c>
       <c r="E36">
-        <v>69.89139999999999</v>
+        <v>72.13849999999999</v>
       </c>
       <c r="F36">
-        <v>76.4014</v>
+        <v>78.6485</v>
       </c>
       <c r="G36">
         <v>7.07</v>
@@ -4239,37 +4239,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M36">
-        <v>11.21572552</v>
+        <v>11.5455998</v>
       </c>
       <c r="N36">
-        <v>-1.655725520000003</v>
+        <v>-1.985599800000003</v>
       </c>
       <c r="O36">
-        <v>-0.3311451040000005</v>
+        <v>-0.3971199600000006</v>
       </c>
       <c r="P36">
-        <v>-1.324580416000002</v>
+        <v>-1.588479840000002</v>
       </c>
       <c r="Q36">
-        <v>4.115419583999998</v>
+        <v>3.851520159999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1731670376705184</v>
+        <v>0.1751265305577572</v>
       </c>
       <c r="T36">
-        <v>1.394721267174662</v>
+        <v>1.416178517438887</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1704749279563325</v>
+        <v>0.1656042157290087</v>
       </c>
       <c r="W36">
-        <v>0.1217742805760104</v>
+        <v>0.1224893011309815</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8523746397816624</v>
+        <v>0.8280210786450434</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1567035002583857</v>
+        <v>0.1577135002583857</v>
       </c>
       <c r="C37">
-        <v>103.8950226076884</v>
+        <v>100.0643043898275</v>
       </c>
       <c r="D37">
-        <v>175.4735226076884</v>
+        <v>173.8899043898275</v>
       </c>
       <c r="E37">
-        <v>72.13849999999999</v>
+        <v>74.3856</v>
       </c>
       <c r="F37">
-        <v>78.6485</v>
+        <v>80.8956</v>
       </c>
       <c r="G37">
         <v>7.07</v>
@@ -4321,37 +4321,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M37">
-        <v>11.5455998</v>
+        <v>11.87547408</v>
       </c>
       <c r="N37">
-        <v>-1.985599800000003</v>
+        <v>-2.315474080000003</v>
       </c>
       <c r="O37">
-        <v>-0.3971199600000006</v>
+        <v>-0.4630948160000006</v>
       </c>
       <c r="P37">
-        <v>-1.588479840000002</v>
+        <v>-1.852379264000003</v>
       </c>
       <c r="Q37">
-        <v>3.851520159999998</v>
+        <v>3.587620735999998</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1751265305577572</v>
+        <v>0.1771472575977221</v>
       </c>
       <c r="T37">
-        <v>1.416178517438887</v>
+        <v>1.43830630677387</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1656042157290087</v>
+        <v>0.1610040986254251</v>
       </c>
       <c r="W37">
-        <v>0.1224893011309815</v>
+        <v>0.1231645983217876</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8280210786450434</v>
+        <v>0.8050204931271255</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1577135002583857</v>
+        <v>0.1800944191441717</v>
       </c>
       <c r="C38">
-        <v>100.0643043898275</v>
+        <v>68.83747559687035</v>
       </c>
       <c r="D38">
-        <v>173.8899043898275</v>
+        <v>144.9101755968703</v>
       </c>
       <c r="E38">
-        <v>74.38559999999998</v>
+        <v>76.63269999999999</v>
       </c>
       <c r="F38">
-        <v>80.89559999999999</v>
+        <v>83.14269999999999</v>
       </c>
       <c r="G38">
         <v>7.07</v>
@@ -4403,45 +4403,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M38">
-        <v>11.87547408</v>
+        <v>16.69505416</v>
       </c>
       <c r="N38">
-        <v>-2.315474080000001</v>
+        <v>-7.135054159999999</v>
       </c>
       <c r="O38">
-        <v>-0.4630948160000003</v>
+        <v>-1.427010832</v>
       </c>
       <c r="P38">
-        <v>-1.852379264000001</v>
+        <v>-5.708043328</v>
       </c>
       <c r="Q38">
-        <v>3.587620735999999</v>
+        <v>-0.2680433279999992</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1771472575977221</v>
+        <v>0.1814399424576637</v>
       </c>
       <c r="T38">
-        <v>1.43830630677387</v>
+        <v>1.485312965458412</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1610040986254251</v>
+        <v>0.1145249354495056</v>
       </c>
       <c r="W38">
-        <v>0.1231645983217876</v>
+        <v>0.1778033929617393</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8050204931271256</v>
+        <v>0.5726246772475281</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1800944191441717</v>
+        <v>0.1816444191441717</v>
       </c>
       <c r="C39">
-        <v>68.83747559687035</v>
+        <v>64.93693430285022</v>
       </c>
       <c r="D39">
-        <v>144.9101755968703</v>
+        <v>143.2567343028502</v>
       </c>
       <c r="E39">
-        <v>76.63269999999999</v>
+        <v>78.87979999999999</v>
       </c>
       <c r="F39">
-        <v>83.14269999999999</v>
+        <v>85.38979999999999</v>
       </c>
       <c r="G39">
         <v>7.07</v>
@@ -4485,37 +4485,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M39">
-        <v>16.69505416</v>
+        <v>17.14627184</v>
       </c>
       <c r="N39">
-        <v>-7.135054159999999</v>
+        <v>-7.586271840000002</v>
       </c>
       <c r="O39">
-        <v>-1.427010832</v>
+        <v>-1.517254368000001</v>
       </c>
       <c r="P39">
-        <v>-5.708043328</v>
+        <v>-6.069017472000001</v>
       </c>
       <c r="Q39">
-        <v>-0.2680433279999992</v>
+        <v>-0.629017472000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1814399424576637</v>
+        <v>0.1836276834650454</v>
       </c>
       <c r="T39">
-        <v>1.485312965458412</v>
+        <v>1.509269626191612</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1145249354495056</v>
+        <v>0.1115111213587291</v>
       </c>
       <c r="W39">
-        <v>0.1778033929617393</v>
+        <v>0.1784085668311672</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5726246772475281</v>
+        <v>0.5575556067936456</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1816444191441717</v>
+        <v>0.1831944191441717</v>
       </c>
       <c r="C40">
-        <v>64.93693430285022</v>
+        <v>61.07369924035967</v>
       </c>
       <c r="D40">
-        <v>143.2567343028502</v>
+        <v>141.6405992403597</v>
       </c>
       <c r="E40">
-        <v>78.87979999999999</v>
+        <v>81.12689999999999</v>
       </c>
       <c r="F40">
-        <v>85.38979999999999</v>
+        <v>87.6369</v>
       </c>
       <c r="G40">
         <v>7.07</v>
@@ -4567,37 +4567,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M40">
-        <v>17.14627184</v>
+        <v>17.59748952</v>
       </c>
       <c r="N40">
-        <v>-7.586271840000002</v>
+        <v>-8.037489520000001</v>
       </c>
       <c r="O40">
-        <v>-1.517254368000001</v>
+        <v>-1.607497904</v>
       </c>
       <c r="P40">
-        <v>-6.069017472000001</v>
+        <v>-6.429991616000001</v>
       </c>
       <c r="Q40">
-        <v>-0.629017472000001</v>
+        <v>-0.9899916160000002</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1836276834650454</v>
+        <v>0.1858871536857838</v>
       </c>
       <c r="T40">
-        <v>1.509269626191612</v>
+        <v>1.534011751211146</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1115111213587291</v>
+        <v>0.1086518618367104</v>
       </c>
       <c r="W40">
-        <v>0.1784085668311672</v>
+        <v>0.1789827061431885</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5575556067936456</v>
+        <v>0.5432593091835521</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1831944191441717</v>
+        <v>0.1847444191441717</v>
       </c>
       <c r="C41">
-        <v>61.07369924035967</v>
+        <v>57.24652189594504</v>
       </c>
       <c r="D41">
-        <v>141.6405992403597</v>
+        <v>140.060521895945</v>
       </c>
       <c r="E41">
-        <v>81.12689999999999</v>
+        <v>83.374</v>
       </c>
       <c r="F41">
-        <v>87.6369</v>
+        <v>89.884</v>
       </c>
       <c r="G41">
         <v>7.07</v>
@@ -4649,37 +4649,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M41">
-        <v>17.59748952</v>
+        <v>18.0487072</v>
       </c>
       <c r="N41">
-        <v>-8.037489520000001</v>
+        <v>-8.4887072</v>
       </c>
       <c r="O41">
-        <v>-1.607497904</v>
+        <v>-1.69774144</v>
       </c>
       <c r="P41">
-        <v>-6.429991616000001</v>
+        <v>-6.790965760000001</v>
       </c>
       <c r="Q41">
-        <v>-0.9899916160000002</v>
+        <v>-1.35096576</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1858871536857838</v>
+        <v>0.1882219395805469</v>
       </c>
       <c r="T41">
-        <v>1.534011751211146</v>
+        <v>1.559578613731332</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1086518618367104</v>
+        <v>0.1059355652907927</v>
       </c>
       <c r="W41">
-        <v>0.1789827061431885</v>
+        <v>0.1795281384896088</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5432593091835521</v>
+        <v>0.5296778264539634</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1847444191441717</v>
+        <v>0.1862944191441717</v>
       </c>
       <c r="C42">
-        <v>57.24652189594504</v>
+        <v>53.45420885288502</v>
       </c>
       <c r="D42">
-        <v>140.060521895945</v>
+        <v>138.515308852885</v>
       </c>
       <c r="E42">
-        <v>83.374</v>
+        <v>85.6211</v>
       </c>
       <c r="F42">
-        <v>89.884</v>
+        <v>92.1311</v>
       </c>
       <c r="G42">
         <v>7.07</v>
@@ -4731,37 +4731,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M42">
-        <v>18.0487072</v>
+        <v>18.49992488</v>
       </c>
       <c r="N42">
-        <v>-8.4887072</v>
+        <v>-8.939924880000003</v>
       </c>
       <c r="O42">
-        <v>-1.69774144</v>
+        <v>-1.787984976000001</v>
       </c>
       <c r="P42">
-        <v>-6.790965760000001</v>
+        <v>-7.151939904000002</v>
       </c>
       <c r="Q42">
-        <v>-1.35096576</v>
+        <v>-1.711939904000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1882219395805469</v>
+        <v>0.1906358707598782</v>
       </c>
       <c r="T42">
-        <v>1.559578613731332</v>
+        <v>1.586012149557287</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1059355652907927</v>
+        <v>0.1033517710154075</v>
       </c>
       <c r="W42">
-        <v>0.1795281384896088</v>
+        <v>0.1800469643801062</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5296778264539634</v>
+        <v>0.5167588550770373</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1862944191441717</v>
+        <v>0.1878444191441717</v>
       </c>
       <c r="C43">
-        <v>53.45420885288502</v>
+        <v>49.69561878509107</v>
       </c>
       <c r="D43">
-        <v>138.515308852885</v>
+        <v>137.0038187850911</v>
       </c>
       <c r="E43">
-        <v>85.6211</v>
+        <v>87.8682</v>
       </c>
       <c r="F43">
-        <v>92.1311</v>
+        <v>94.37820000000001</v>
       </c>
       <c r="G43">
         <v>7.07</v>
@@ -4813,37 +4813,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M43">
-        <v>18.49992488</v>
+        <v>18.95114256</v>
       </c>
       <c r="N43">
-        <v>-8.939924880000003</v>
+        <v>-9.391142560000002</v>
       </c>
       <c r="O43">
-        <v>-1.787984976000001</v>
+        <v>-1.878228512000001</v>
       </c>
       <c r="P43">
-        <v>-7.151939904000002</v>
+        <v>-7.512914048000002</v>
       </c>
       <c r="Q43">
-        <v>-1.711939904000002</v>
+        <v>-2.072914048000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1906358707598782</v>
+        <v>0.1931330409453934</v>
       </c>
       <c r="T43">
-        <v>1.586012149557287</v>
+        <v>1.61335718661862</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1033517710154075</v>
+        <v>0.1008910145626597</v>
       </c>
       <c r="W43">
-        <v>0.1800469643801062</v>
+        <v>0.1805410842758179</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5167588550770373</v>
+        <v>0.5044550728132984</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1878444191441717</v>
+        <v>0.2050056717150233</v>
       </c>
       <c r="C44">
-        <v>49.69561878509109</v>
+        <v>32.68046993347299</v>
       </c>
       <c r="D44">
-        <v>137.0038187850911</v>
+        <v>122.235769933473</v>
       </c>
       <c r="E44">
-        <v>87.86819999999999</v>
+        <v>90.11529999999999</v>
       </c>
       <c r="F44">
-        <v>94.37819999999999</v>
+        <v>96.6253</v>
       </c>
       <c r="G44">
         <v>7.07</v>
@@ -4895,45 +4895,45 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M44">
-        <v>18.95114256</v>
+        <v>22.78424574</v>
       </c>
       <c r="N44">
-        <v>-9.391142559999999</v>
+        <v>-13.22424574</v>
       </c>
       <c r="O44">
-        <v>-1.878228512</v>
+        <v>-2.644849148</v>
       </c>
       <c r="P44">
-        <v>-7.512914047999999</v>
+        <v>-10.579396592</v>
       </c>
       <c r="Q44">
-        <v>-2.072914047999999</v>
+        <v>-5.139396592</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1931330409453934</v>
+        <v>0.1967024847704908</v>
       </c>
       <c r="T44">
-        <v>1.61335718661862</v>
+        <v>1.65244405953253</v>
       </c>
       <c r="U44">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1008910145626597</v>
+        <v>0.08391763422053049</v>
       </c>
       <c r="W44">
-        <v>0.1805410842758179</v>
+        <v>0.2160122218507989</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5044550728132985</v>
+        <v>0.4195881711026525</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2050056717150233</v>
+        <v>0.2069056717150233</v>
       </c>
       <c r="C45">
-        <v>32.68046993347299</v>
+        <v>28.99178218301556</v>
       </c>
       <c r="D45">
-        <v>122.235769933473</v>
+        <v>120.7941821830156</v>
       </c>
       <c r="E45">
-        <v>90.11529999999999</v>
+        <v>92.36239999999998</v>
       </c>
       <c r="F45">
-        <v>96.6253</v>
+        <v>98.87239999999998</v>
       </c>
       <c r="G45">
         <v>7.07</v>
@@ -4977,37 +4977,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M45">
-        <v>22.78424574</v>
+        <v>23.31411192</v>
       </c>
       <c r="N45">
-        <v>-13.22424574</v>
+        <v>-13.75411192</v>
       </c>
       <c r="O45">
-        <v>-2.644849148</v>
+        <v>-2.750822384</v>
       </c>
       <c r="P45">
-        <v>-10.579396592</v>
+        <v>-11.003289536</v>
       </c>
       <c r="Q45">
-        <v>-5.139396592</v>
+        <v>-5.563289536</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1967024847704908</v>
+        <v>0.1993971719985353</v>
       </c>
       <c r="T45">
-        <v>1.65244405953253</v>
+        <v>1.681951989167039</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08391763422053049</v>
+        <v>0.08201041526097297</v>
       </c>
       <c r="W45">
-        <v>0.2160122218507989</v>
+        <v>0.2164619440814626</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4195881711026525</v>
+        <v>0.4100520763048648</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2069056717150233</v>
+        <v>0.2088056717150233</v>
       </c>
       <c r="C46">
-        <v>28.99178218301556</v>
+        <v>25.33670083038527</v>
       </c>
       <c r="D46">
-        <v>120.7941821830156</v>
+        <v>119.3862008303852</v>
       </c>
       <c r="E46">
-        <v>92.36239999999998</v>
+        <v>94.60949999999998</v>
       </c>
       <c r="F46">
-        <v>98.87239999999998</v>
+        <v>101.1195</v>
       </c>
       <c r="G46">
         <v>7.07</v>
@@ -5059,37 +5059,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M46">
-        <v>23.31411192</v>
+        <v>23.8439781</v>
       </c>
       <c r="N46">
-        <v>-13.75411192</v>
+        <v>-14.2839781</v>
       </c>
       <c r="O46">
-        <v>-2.750822384</v>
+        <v>-2.85679562</v>
       </c>
       <c r="P46">
-        <v>-11.003289536</v>
+        <v>-11.42718248</v>
       </c>
       <c r="Q46">
-        <v>-5.563289536</v>
+        <v>-5.987182479999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1993971719985353</v>
+        <v>0.2021898478530542</v>
       </c>
       <c r="T46">
-        <v>1.681951989167039</v>
+        <v>1.712532934424622</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08201041526097297</v>
+        <v>0.08018796158850691</v>
       </c>
       <c r="W46">
-        <v>0.2164619440814626</v>
+        <v>0.2168916786574301</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4100520763048648</v>
+        <v>0.4009398079425346</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2088056717150233</v>
+        <v>0.2107056717150234</v>
       </c>
       <c r="C47">
-        <v>25.33670083038527</v>
+        <v>21.71406426321532</v>
       </c>
       <c r="D47">
-        <v>119.3862008303852</v>
+        <v>118.0106642632153</v>
       </c>
       <c r="E47">
-        <v>94.60949999999998</v>
+        <v>96.85659999999999</v>
       </c>
       <c r="F47">
-        <v>101.1195</v>
+        <v>103.3666</v>
       </c>
       <c r="G47">
         <v>7.07</v>
@@ -5141,37 +5141,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M47">
-        <v>23.8439781</v>
+        <v>24.37384428</v>
       </c>
       <c r="N47">
-        <v>-14.2839781</v>
+        <v>-14.81384428</v>
       </c>
       <c r="O47">
-        <v>-2.85679562</v>
+        <v>-2.962768856</v>
       </c>
       <c r="P47">
-        <v>-11.42718248</v>
+        <v>-11.851075424</v>
       </c>
       <c r="Q47">
-        <v>-5.987182479999999</v>
+        <v>-6.411075424000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2021898478530542</v>
+        <v>0.2050859561466293</v>
       </c>
       <c r="T47">
-        <v>1.712532934424622</v>
+        <v>1.744246507284337</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08018796158850691</v>
+        <v>0.07844474503223502</v>
       </c>
       <c r="W47">
-        <v>0.2168916786574301</v>
+        <v>0.217302729121399</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4009398079425346</v>
+        <v>0.3922237251611751</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2107056717150234</v>
+        <v>0.2126056717150233</v>
       </c>
       <c r="C48">
-        <v>21.71406426321532</v>
+        <v>18.12276379452157</v>
       </c>
       <c r="D48">
-        <v>118.0106642632153</v>
+        <v>116.6664637945216</v>
       </c>
       <c r="E48">
-        <v>96.85659999999999</v>
+        <v>99.10369999999999</v>
       </c>
       <c r="F48">
-        <v>103.3666</v>
+        <v>105.6137</v>
       </c>
       <c r="G48">
         <v>7.07</v>
@@ -5223,37 +5223,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M48">
-        <v>24.37384428</v>
+        <v>24.90371046</v>
       </c>
       <c r="N48">
-        <v>-14.81384428</v>
+        <v>-15.34371046</v>
       </c>
       <c r="O48">
-        <v>-2.962768856</v>
+        <v>-3.068742092</v>
       </c>
       <c r="P48">
-        <v>-11.851075424</v>
+        <v>-12.274968368</v>
       </c>
       <c r="Q48">
-        <v>-6.411075424000001</v>
+        <v>-6.834968367999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2050859561466293</v>
+        <v>0.2080913515456222</v>
       </c>
       <c r="T48">
-        <v>1.744246507284337</v>
+        <v>1.777156818742532</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.07844474503223502</v>
+        <v>0.0767757079038896</v>
       </c>
       <c r="W48">
-        <v>0.217302729121399</v>
+        <v>0.2176962880762628</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3922237251611751</v>
+        <v>0.3838785395194479</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2126056717150233</v>
+        <v>0.2145056717150233</v>
       </c>
       <c r="C49">
-        <v>18.12276379452157</v>
+        <v>14.56174068241644</v>
       </c>
       <c r="D49">
-        <v>116.6664637945216</v>
+        <v>115.3525406824164</v>
       </c>
       <c r="E49">
-        <v>99.10369999999999</v>
+        <v>101.3508</v>
       </c>
       <c r="F49">
-        <v>105.6137</v>
+        <v>107.8608</v>
       </c>
       <c r="G49">
         <v>7.07</v>
@@ -5305,37 +5305,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M49">
-        <v>24.90371046</v>
+        <v>25.43357664</v>
       </c>
       <c r="N49">
-        <v>-15.34371046</v>
+        <v>-15.87357664</v>
       </c>
       <c r="O49">
-        <v>-3.068742092</v>
+        <v>-3.174715328000001</v>
       </c>
       <c r="P49">
-        <v>-12.274968368</v>
+        <v>-12.698861312</v>
       </c>
       <c r="Q49">
-        <v>-6.834968367999999</v>
+        <v>-7.258861312000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2080913515456222</v>
+        <v>0.2112123390753458</v>
       </c>
       <c r="T49">
-        <v>1.777156818742532</v>
+        <v>1.811332911410658</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0767757079038896</v>
+        <v>0.07517621398922522</v>
       </c>
       <c r="W49">
-        <v>0.2176962880762628</v>
+        <v>0.2180734487413407</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3838785395194479</v>
+        <v>0.375881069946126</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2145056717150233</v>
+        <v>0.2164056717150233</v>
       </c>
       <c r="C50">
-        <v>14.56174068241648</v>
+        <v>11.02998334896809</v>
       </c>
       <c r="D50">
-        <v>115.3525406824165</v>
+        <v>114.0678833489681</v>
       </c>
       <c r="E50">
-        <v>101.3508</v>
+        <v>103.5979</v>
       </c>
       <c r="F50">
-        <v>107.8608</v>
+        <v>110.1079</v>
       </c>
       <c r="G50">
         <v>7.07</v>
@@ -5387,37 +5387,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M50">
-        <v>25.43357664</v>
+        <v>25.96344282</v>
       </c>
       <c r="N50">
-        <v>-15.87357664</v>
+        <v>-16.40344282</v>
       </c>
       <c r="O50">
-        <v>-3.174715328</v>
+        <v>-3.280688564</v>
       </c>
       <c r="P50">
-        <v>-12.698861312</v>
+        <v>-13.122754256</v>
       </c>
       <c r="Q50">
-        <v>-7.258861312</v>
+        <v>-7.682754255999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2112123390753457</v>
+        <v>0.2144557182729016</v>
       </c>
       <c r="T50">
-        <v>1.811332911410658</v>
+        <v>1.846849243006945</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07517621398922524</v>
+        <v>0.07364200554046553</v>
       </c>
       <c r="W50">
-        <v>0.2180734487413407</v>
+        <v>0.2184352150935582</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3758810699461261</v>
+        <v>0.3682100277023277</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2164056717150233</v>
+        <v>0.2183056717150233</v>
       </c>
       <c r="C51">
-        <v>11.02998334896809</v>
+        <v>7.526524782850458</v>
       </c>
       <c r="D51">
-        <v>114.0678833489681</v>
+        <v>112.8115247828505</v>
       </c>
       <c r="E51">
-        <v>103.5979</v>
+        <v>105.845</v>
       </c>
       <c r="F51">
-        <v>110.1079</v>
+        <v>112.355</v>
       </c>
       <c r="G51">
         <v>7.07</v>
@@ -5469,37 +5469,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M51">
-        <v>25.96344282</v>
+        <v>26.493309</v>
       </c>
       <c r="N51">
-        <v>-16.40344282</v>
+        <v>-16.933309</v>
       </c>
       <c r="O51">
-        <v>-3.280688564</v>
+        <v>-3.386661800000001</v>
       </c>
       <c r="P51">
-        <v>-13.122754256</v>
+        <v>-13.5466472</v>
       </c>
       <c r="Q51">
-        <v>-7.682754255999998</v>
+        <v>-8.106647200000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2144557182729016</v>
+        <v>0.2178288326383596</v>
       </c>
       <c r="T51">
-        <v>1.846849243006945</v>
+        <v>1.883786227867084</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07364200554046553</v>
+        <v>0.07216916542965622</v>
       </c>
       <c r="W51">
-        <v>0.2184352150935582</v>
+        <v>0.2187825107916871</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3682100277023277</v>
+        <v>0.3608458271482811</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2183056717150233</v>
+        <v>0.2202056717150233</v>
       </c>
       <c r="C52">
-        <v>7.526524782850458</v>
+        <v>4.050440111769078</v>
       </c>
       <c r="D52">
-        <v>112.8115247828505</v>
+        <v>111.5825401117691</v>
       </c>
       <c r="E52">
-        <v>105.845</v>
+        <v>108.0921</v>
       </c>
       <c r="F52">
-        <v>112.355</v>
+        <v>114.6021</v>
       </c>
       <c r="G52">
         <v>7.07</v>
@@ -5551,37 +5551,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M52">
-        <v>26.493309</v>
+        <v>27.02317518</v>
       </c>
       <c r="N52">
-        <v>-16.933309</v>
+        <v>-17.46317518</v>
       </c>
       <c r="O52">
-        <v>-3.386661800000001</v>
+        <v>-3.492635036</v>
       </c>
       <c r="P52">
-        <v>-13.5466472</v>
+        <v>-13.970540144</v>
       </c>
       <c r="Q52">
-        <v>-8.106647200000001</v>
+        <v>-8.530540144</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2178288326383596</v>
+        <v>0.2213396251411833</v>
       </c>
       <c r="T52">
-        <v>1.883786227867084</v>
+        <v>1.922230844762331</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07216916542965622</v>
+        <v>0.07075408375456492</v>
       </c>
       <c r="W52">
-        <v>0.2187825107916871</v>
+        <v>0.2191161870506736</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3608458271482811</v>
+        <v>0.3537704187728246</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2202056717150233</v>
+        <v>0.2221056717150234</v>
       </c>
       <c r="C53">
-        <v>4.050440111769078</v>
+        <v>0.6008443318542618</v>
       </c>
       <c r="D53">
-        <v>111.5825401117691</v>
+        <v>110.3800443318543</v>
       </c>
       <c r="E53">
-        <v>108.0921</v>
+        <v>110.3392</v>
       </c>
       <c r="F53">
-        <v>114.6021</v>
+        <v>116.8492</v>
       </c>
       <c r="G53">
         <v>7.07</v>
@@ -5633,37 +5633,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M53">
-        <v>27.02317518</v>
+        <v>27.55304136</v>
       </c>
       <c r="N53">
-        <v>-17.46317518</v>
+        <v>-17.99304136</v>
       </c>
       <c r="O53">
-        <v>-3.492635036</v>
+        <v>-3.598608272000001</v>
       </c>
       <c r="P53">
-        <v>-13.970540144</v>
+        <v>-14.394433088</v>
       </c>
       <c r="Q53">
-        <v>-8.530540144</v>
+        <v>-8.954433088000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2213396251411833</v>
+        <v>0.2249967006649579</v>
       </c>
       <c r="T53">
-        <v>1.922230844762331</v>
+        <v>1.96227732069488</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07075408375456492</v>
+        <v>0.06939342829774635</v>
       </c>
       <c r="W53">
-        <v>0.2191161870506736</v>
+        <v>0.2194370296073914</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3537704187728246</v>
+        <v>0.3469671414887318</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2221056717150234</v>
+        <v>0.2240056717150233</v>
       </c>
       <c r="C54">
-        <v>0.6008443318542618</v>
+        <v>-2.823109817692099</v>
       </c>
       <c r="D54">
-        <v>110.3800443318543</v>
+        <v>109.2031901823079</v>
       </c>
       <c r="E54">
-        <v>110.3392</v>
+        <v>112.5863</v>
       </c>
       <c r="F54">
-        <v>116.8492</v>
+        <v>119.0963</v>
       </c>
       <c r="G54">
         <v>7.07</v>
@@ -5715,37 +5715,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M54">
-        <v>27.55304136</v>
+        <v>28.08290754</v>
       </c>
       <c r="N54">
-        <v>-17.99304136</v>
+        <v>-18.52290754</v>
       </c>
       <c r="O54">
-        <v>-3.598608272000001</v>
+        <v>-3.704581508</v>
       </c>
       <c r="P54">
-        <v>-14.394433088</v>
+        <v>-14.818326032</v>
       </c>
       <c r="Q54">
-        <v>-8.954433088000002</v>
+        <v>-9.378326032</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2249967006649579</v>
+        <v>0.2288093964237868</v>
       </c>
       <c r="T54">
-        <v>1.96227732069488</v>
+        <v>2.00402790198626</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06939342829774635</v>
+        <v>0.06808411832986436</v>
       </c>
       <c r="W54">
-        <v>0.2194370296073914</v>
+        <v>0.219745764897818</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3469671414887318</v>
+        <v>0.3404205916493217</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2240056717150233</v>
+        <v>0.2259056717150233</v>
       </c>
       <c r="C55">
-        <v>-2.823109817692099</v>
+        <v>-6.222233845423375</v>
       </c>
       <c r="D55">
-        <v>109.2031901823079</v>
+        <v>108.0511661545766</v>
       </c>
       <c r="E55">
-        <v>112.5863</v>
+        <v>114.8334</v>
       </c>
       <c r="F55">
-        <v>119.0963</v>
+        <v>121.3434</v>
       </c>
       <c r="G55">
         <v>7.07</v>
@@ -5797,37 +5797,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M55">
-        <v>28.08290754</v>
+        <v>28.61277372</v>
       </c>
       <c r="N55">
-        <v>-18.52290754</v>
+        <v>-19.05277372</v>
       </c>
       <c r="O55">
-        <v>-3.704581508</v>
+        <v>-3.810554744000001</v>
       </c>
       <c r="P55">
-        <v>-14.818326032</v>
+        <v>-15.242218976</v>
       </c>
       <c r="Q55">
-        <v>-9.378326032</v>
+        <v>-9.802218976000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2288093964237868</v>
+        <v>0.2327878615634344</v>
       </c>
       <c r="T55">
-        <v>2.00402790198626</v>
+        <v>2.047593725942483</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06808411832986436</v>
+        <v>0.06682330132375575</v>
       </c>
       <c r="W55">
-        <v>0.219745764897818</v>
+        <v>0.2200430655478584</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3404205916493217</v>
+        <v>0.3341165066187787</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2259056717150233</v>
+        <v>0.2278056717150233</v>
       </c>
       <c r="C56">
-        <v>-6.222233845423375</v>
+        <v>-9.597305373778497</v>
       </c>
       <c r="D56">
-        <v>108.0511661545766</v>
+        <v>106.9231946262215</v>
       </c>
       <c r="E56">
-        <v>114.8334</v>
+        <v>117.0805</v>
       </c>
       <c r="F56">
-        <v>121.3434</v>
+        <v>123.5905</v>
       </c>
       <c r="G56">
         <v>7.07</v>
@@ -5879,37 +5879,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M56">
-        <v>28.61277372</v>
+        <v>29.1426399</v>
       </c>
       <c r="N56">
-        <v>-19.05277372</v>
+        <v>-19.5826399</v>
       </c>
       <c r="O56">
-        <v>-3.810554744000001</v>
+        <v>-3.916527980000001</v>
       </c>
       <c r="P56">
-        <v>-15.242218976</v>
+        <v>-15.66611192</v>
       </c>
       <c r="Q56">
-        <v>-9.802218976000002</v>
+        <v>-10.22611192</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2327878615634344</v>
+        <v>0.2369431473759551</v>
       </c>
       <c r="T56">
-        <v>2.047593725942483</v>
+        <v>2.093095808741205</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06682330132375575</v>
+        <v>0.06560833220877836</v>
       </c>
       <c r="W56">
-        <v>0.2200430655478584</v>
+        <v>0.2203295552651701</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3341165066187787</v>
+        <v>0.3280416610438919</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2278056717150233</v>
+        <v>0.2297056717150233</v>
       </c>
       <c r="C57">
-        <v>-9.597305373778497</v>
+        <v>-12.94906988953427</v>
       </c>
       <c r="D57">
-        <v>106.9231946262215</v>
+        <v>105.8185301104657</v>
       </c>
       <c r="E57">
-        <v>117.0805</v>
+        <v>119.3276</v>
       </c>
       <c r="F57">
-        <v>123.5905</v>
+        <v>125.8376</v>
       </c>
       <c r="G57">
         <v>7.07</v>
@@ -5961,37 +5961,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M57">
-        <v>29.1426399</v>
+        <v>29.67250608</v>
       </c>
       <c r="N57">
-        <v>-19.5826399</v>
+        <v>-20.11250608</v>
       </c>
       <c r="O57">
-        <v>-3.916527980000001</v>
+        <v>-4.022501216000001</v>
       </c>
       <c r="P57">
-        <v>-15.66611192</v>
+        <v>-16.090004864</v>
       </c>
       <c r="Q57">
-        <v>-10.22611192</v>
+        <v>-10.650004864</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2369431473759551</v>
+        <v>0.2412873098163177</v>
       </c>
       <c r="T57">
-        <v>2.093095808741205</v>
+        <v>2.140666168030778</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06560833220877836</v>
+        <v>0.06443675484790733</v>
       </c>
       <c r="W57">
-        <v>0.2203295552651701</v>
+        <v>0.2206058132068635</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3280416610438919</v>
+        <v>0.3221837742395366</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2297056717150233</v>
+        <v>0.2316056717150233</v>
       </c>
       <c r="C58">
-        <v>-12.94906988953427</v>
+        <v>-16.2782423868596</v>
       </c>
       <c r="D58">
-        <v>105.8185301104657</v>
+        <v>104.7364576131404</v>
       </c>
       <c r="E58">
-        <v>119.3276</v>
+        <v>121.5747</v>
       </c>
       <c r="F58">
-        <v>125.8376</v>
+        <v>128.0847</v>
       </c>
       <c r="G58">
         <v>7.07</v>
@@ -6043,37 +6043,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M58">
-        <v>29.67250608</v>
+        <v>30.20237226</v>
       </c>
       <c r="N58">
-        <v>-20.11250608</v>
+        <v>-20.64237226</v>
       </c>
       <c r="O58">
-        <v>-4.022501216000001</v>
+        <v>-4.128474452000001</v>
       </c>
       <c r="P58">
-        <v>-16.090004864</v>
+        <v>-16.513897808</v>
       </c>
       <c r="Q58">
-        <v>-10.650004864</v>
+        <v>-11.073897808</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2412873098163177</v>
+        <v>0.245833526323674</v>
       </c>
       <c r="T58">
-        <v>2.140666168030778</v>
+        <v>2.190449102171029</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06443675484790733</v>
+        <v>0.06330628546461071</v>
       </c>
       <c r="W58">
-        <v>0.2206058132068635</v>
+        <v>0.2208723778874448</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3221837742395366</v>
+        <v>0.3165314273230535</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2316056717150233</v>
+        <v>0.2335056717150233</v>
       </c>
       <c r="C59">
-        <v>-16.2782423868596</v>
+        <v>-19.58550891058135</v>
       </c>
       <c r="D59">
-        <v>104.7364576131404</v>
+        <v>103.6762910894187</v>
       </c>
       <c r="E59">
-        <v>121.5747</v>
+        <v>123.8218</v>
       </c>
       <c r="F59">
-        <v>128.0847</v>
+        <v>130.3318</v>
       </c>
       <c r="G59">
         <v>7.07</v>
@@ -6125,37 +6125,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M59">
-        <v>30.20237226</v>
+        <v>30.73223844</v>
       </c>
       <c r="N59">
-        <v>-20.64237226</v>
+        <v>-21.17223844</v>
       </c>
       <c r="O59">
-        <v>-4.128474452000001</v>
+        <v>-4.234447688000001</v>
       </c>
       <c r="P59">
-        <v>-16.513897808</v>
+        <v>-16.93779075200001</v>
       </c>
       <c r="Q59">
-        <v>-11.073897808</v>
+        <v>-11.497790752</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.245833526323674</v>
+        <v>0.2505962293313805</v>
       </c>
       <c r="T59">
-        <v>2.190449102171029</v>
+        <v>2.24260265222272</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06330628546461071</v>
+        <v>0.06221479778418638</v>
       </c>
       <c r="W59">
-        <v>0.2208723778874448</v>
+        <v>0.2211297506824889</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3165314273230535</v>
+        <v>0.3110739889209319</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2335056717150233</v>
+        <v>0.2354056717150233</v>
       </c>
       <c r="C60">
-        <v>-19.58550891058132</v>
+        <v>-22.87152800666172</v>
       </c>
       <c r="D60">
-        <v>103.6762910894187</v>
+        <v>102.6373719933383</v>
       </c>
       <c r="E60">
-        <v>123.8218</v>
+        <v>126.0689</v>
       </c>
       <c r="F60">
-        <v>130.3318</v>
+        <v>132.5789</v>
       </c>
       <c r="G60">
         <v>7.07</v>
@@ -6207,37 +6207,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M60">
-        <v>30.73223844</v>
+        <v>31.26210462</v>
       </c>
       <c r="N60">
-        <v>-21.17223844</v>
+        <v>-21.70210462</v>
       </c>
       <c r="O60">
-        <v>-4.234447688</v>
+        <v>-4.340420923999999</v>
       </c>
       <c r="P60">
-        <v>-16.937790752</v>
+        <v>-17.361683696</v>
       </c>
       <c r="Q60">
-        <v>-11.497790752</v>
+        <v>-11.921683696</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2505962293313804</v>
+        <v>0.2555912593150726</v>
       </c>
       <c r="T60">
-        <v>2.242602652222719</v>
+        <v>2.297300277886688</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0622147977841864</v>
+        <v>0.06116030968614934</v>
       </c>
       <c r="W60">
-        <v>0.2211297506824889</v>
+        <v>0.221378398976006</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.311073988920932</v>
+        <v>0.3058015484307467</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2354056717150233</v>
+        <v>0.2373056717150233</v>
       </c>
       <c r="C61">
-        <v>-22.87152800666172</v>
+        <v>-26.13693208633168</v>
       </c>
       <c r="D61">
-        <v>102.6373719933383</v>
+        <v>101.6190679136683</v>
       </c>
       <c r="E61">
-        <v>126.0689</v>
+        <v>128.316</v>
       </c>
       <c r="F61">
-        <v>132.5789</v>
+        <v>134.826</v>
       </c>
       <c r="G61">
         <v>7.07</v>
@@ -6289,37 +6289,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M61">
-        <v>31.26210462</v>
+        <v>31.7919708</v>
       </c>
       <c r="N61">
-        <v>-21.70210462</v>
+        <v>-22.2319708</v>
       </c>
       <c r="O61">
-        <v>-4.340420923999999</v>
+        <v>-4.446394160000001</v>
       </c>
       <c r="P61">
-        <v>-17.361683696</v>
+        <v>-17.78557664</v>
       </c>
       <c r="Q61">
-        <v>-11.921683696</v>
+        <v>-12.34557664</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2555912593150726</v>
+        <v>0.2608360407979495</v>
       </c>
       <c r="T61">
-        <v>2.297300277886688</v>
+        <v>2.354732784833855</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06116030968614934</v>
+        <v>0.06014097119138018</v>
       </c>
       <c r="W61">
-        <v>0.221378398976006</v>
+        <v>0.2216187589930726</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3058015484307467</v>
+        <v>0.3007048559569009</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2373056717150233</v>
+        <v>0.2392056717150233</v>
       </c>
       <c r="C62">
-        <v>-26.13693208633168</v>
+        <v>-29.38232870981676</v>
       </c>
       <c r="D62">
-        <v>101.6190679136683</v>
+        <v>100.6207712901832</v>
       </c>
       <c r="E62">
-        <v>128.316</v>
+        <v>130.5631</v>
       </c>
       <c r="F62">
-        <v>134.826</v>
+        <v>137.0731</v>
       </c>
       <c r="G62">
         <v>7.07</v>
@@ -6371,37 +6371,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M62">
-        <v>31.7919708</v>
+        <v>32.32183698</v>
       </c>
       <c r="N62">
-        <v>-22.2319708</v>
+        <v>-22.76183698</v>
       </c>
       <c r="O62">
-        <v>-4.446394160000001</v>
+        <v>-4.552367396</v>
       </c>
       <c r="P62">
-        <v>-17.78557664</v>
+        <v>-18.209469584</v>
       </c>
       <c r="Q62">
-        <v>-12.34557664</v>
+        <v>-12.769469584</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2608360407979495</v>
+        <v>0.2663497854337943</v>
       </c>
       <c r="T62">
-        <v>2.354732784833855</v>
+        <v>2.415110548547544</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06014097119138018</v>
+        <v>0.05915505363086575</v>
       </c>
       <c r="W62">
-        <v>0.2216187589930726</v>
+        <v>0.2218512383538419</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3007048559569009</v>
+        <v>0.2957752681543288</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2392056717150233</v>
+        <v>0.2411056717150233</v>
       </c>
       <c r="C63">
-        <v>-29.38232870981676</v>
+        <v>-32.60830179513252</v>
       </c>
       <c r="D63">
-        <v>100.6207712901832</v>
+        <v>99.64189820486749</v>
       </c>
       <c r="E63">
-        <v>130.5631</v>
+        <v>132.8102</v>
       </c>
       <c r="F63">
-        <v>137.0731</v>
+        <v>139.3202</v>
       </c>
       <c r="G63">
         <v>7.07</v>
@@ -6453,37 +6453,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M63">
-        <v>32.32183698</v>
+        <v>32.85170316</v>
       </c>
       <c r="N63">
-        <v>-22.76183698</v>
+        <v>-23.29170316</v>
       </c>
       <c r="O63">
-        <v>-4.552367396</v>
+        <v>-4.658340632000001</v>
       </c>
       <c r="P63">
-        <v>-18.209469584</v>
+        <v>-18.633362528</v>
       </c>
       <c r="Q63">
-        <v>-12.769469584</v>
+        <v>-13.193362528</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2663497854337943</v>
+        <v>0.2721537271557363</v>
       </c>
       <c r="T63">
-        <v>2.415110548547544</v>
+        <v>2.478666089298795</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05915505363086575</v>
+        <v>0.05820093986262598</v>
       </c>
       <c r="W63">
-        <v>0.2218512383538419</v>
+        <v>0.2220762183803928</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2957752681543288</v>
+        <v>0.2910046993131299</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2411056717150233</v>
+        <v>0.2430056717150233</v>
       </c>
       <c r="C64">
-        <v>-32.60830179513252</v>
+        <v>-35.81541275700192</v>
       </c>
       <c r="D64">
-        <v>99.64189820486749</v>
+        <v>98.68188724299806</v>
       </c>
       <c r="E64">
-        <v>132.8102</v>
+        <v>135.0573</v>
       </c>
       <c r="F64">
-        <v>139.3202</v>
+        <v>141.5673</v>
       </c>
       <c r="G64">
         <v>7.07</v>
@@ -6535,37 +6535,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M64">
-        <v>32.85170316</v>
+        <v>33.38156934</v>
       </c>
       <c r="N64">
-        <v>-23.29170316</v>
+        <v>-23.82156934</v>
       </c>
       <c r="O64">
-        <v>-4.658340632000001</v>
+        <v>-4.764313868</v>
       </c>
       <c r="P64">
-        <v>-18.633362528</v>
+        <v>-19.057255472</v>
       </c>
       <c r="Q64">
-        <v>-13.193362528</v>
+        <v>-13.617255472</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2721537271557363</v>
+        <v>0.2782713954572427</v>
       </c>
       <c r="T64">
-        <v>2.478666089298795</v>
+        <v>2.545657064685249</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05820093986262598</v>
+        <v>0.05727711542036208</v>
       </c>
       <c r="W64">
-        <v>0.2220762183803928</v>
+        <v>0.2222940561838786</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2910046993131299</v>
+        <v>0.2863855771018103</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2430056717150233</v>
+        <v>0.2449056717150234</v>
       </c>
       <c r="C65">
-        <v>-35.81541275700192</v>
+        <v>-39.0042015805632</v>
       </c>
       <c r="D65">
-        <v>98.68188724299806</v>
+        <v>97.74019841943677</v>
       </c>
       <c r="E65">
-        <v>135.0573</v>
+        <v>137.3044</v>
       </c>
       <c r="F65">
-        <v>141.5673</v>
+        <v>143.8144</v>
       </c>
       <c r="G65">
         <v>7.07</v>
@@ -6617,37 +6617,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M65">
-        <v>33.38156934</v>
+        <v>33.91143552</v>
       </c>
       <c r="N65">
-        <v>-23.82156934</v>
+        <v>-24.35143552</v>
       </c>
       <c r="O65">
-        <v>-4.764313868</v>
+        <v>-4.870287104</v>
       </c>
       <c r="P65">
-        <v>-19.057255472</v>
+        <v>-19.481148416</v>
       </c>
       <c r="Q65">
-        <v>-13.617255472</v>
+        <v>-14.041148416</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2782713954572427</v>
+        <v>0.2847289342199439</v>
       </c>
       <c r="T65">
-        <v>2.545657064685249</v>
+        <v>2.616369760926506</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05727711542036208</v>
+        <v>0.05638216049191892</v>
       </c>
       <c r="W65">
-        <v>0.2222940561838786</v>
+        <v>0.2225050865560055</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2863855771018103</v>
+        <v>0.2819108024595945</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2449056717150234</v>
+        <v>0.2468056717150233</v>
       </c>
       <c r="C66">
-        <v>-39.0042015805632</v>
+        <v>-42.17518783418205</v>
       </c>
       <c r="D66">
-        <v>97.74019841943677</v>
+        <v>96.81631216581795</v>
       </c>
       <c r="E66">
-        <v>137.3044</v>
+        <v>139.5515</v>
       </c>
       <c r="F66">
-        <v>143.8144</v>
+        <v>146.0615</v>
       </c>
       <c r="G66">
         <v>7.07</v>
@@ -6699,37 +6699,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M66">
-        <v>33.91143552</v>
+        <v>34.4413017</v>
       </c>
       <c r="N66">
-        <v>-24.35143552</v>
+        <v>-24.8813017</v>
       </c>
       <c r="O66">
-        <v>-4.870287104</v>
+        <v>-4.97626034</v>
       </c>
       <c r="P66">
-        <v>-19.481148416</v>
+        <v>-19.90504136</v>
       </c>
       <c r="Q66">
-        <v>-14.041148416</v>
+        <v>-14.46504136</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2847289342199439</v>
+        <v>0.2915554751976566</v>
       </c>
       <c r="T66">
-        <v>2.616369760926506</v>
+        <v>2.691123182667263</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05638216049191892</v>
+        <v>0.05551474263819709</v>
       </c>
       <c r="W66">
-        <v>0.2225050865560055</v>
+        <v>0.2227096236859131</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2819108024595945</v>
+        <v>0.2775737131909854</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2468056717150233</v>
+        <v>0.2487056717150233</v>
       </c>
       <c r="C67">
-        <v>-42.17518783418205</v>
+        <v>-45.32887162536068</v>
       </c>
       <c r="D67">
-        <v>96.81631216581795</v>
+        <v>95.9097283746393</v>
       </c>
       <c r="E67">
-        <v>139.5515</v>
+        <v>141.7986</v>
       </c>
       <c r="F67">
-        <v>146.0615</v>
+        <v>148.3086</v>
       </c>
       <c r="G67">
         <v>7.07</v>
@@ -6781,37 +6781,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M67">
-        <v>34.4413017</v>
+        <v>34.97116788</v>
       </c>
       <c r="N67">
-        <v>-24.8813017</v>
+        <v>-25.41116788</v>
       </c>
       <c r="O67">
-        <v>-4.97626034</v>
+        <v>-5.082233576</v>
       </c>
       <c r="P67">
-        <v>-19.90504136</v>
+        <v>-20.328934304</v>
       </c>
       <c r="Q67">
-        <v>-14.46504136</v>
+        <v>-14.888934304</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2915554751976566</v>
+        <v>0.2987835774093524</v>
       </c>
       <c r="T67">
-        <v>2.691123182667263</v>
+        <v>2.770273864510418</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05551474263819709</v>
+        <v>0.05467361017398198</v>
       </c>
       <c r="W67">
-        <v>0.2227096236859131</v>
+        <v>0.222907962720975</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2775737131909854</v>
+        <v>0.2733680508699099</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2487056717150233</v>
+        <v>0.2506056717150233</v>
       </c>
       <c r="C68">
-        <v>-45.32887162536068</v>
+        <v>-48.46573450343851</v>
       </c>
       <c r="D68">
-        <v>95.9097283746393</v>
+        <v>95.0199654965615</v>
       </c>
       <c r="E68">
-        <v>141.7986</v>
+        <v>144.0457</v>
       </c>
       <c r="F68">
-        <v>148.3086</v>
+        <v>150.5557</v>
       </c>
       <c r="G68">
         <v>7.07</v>
@@ -6863,37 +6863,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M68">
-        <v>34.97116788</v>
+        <v>35.50103406</v>
       </c>
       <c r="N68">
-        <v>-25.41116788</v>
+        <v>-25.94103406</v>
       </c>
       <c r="O68">
-        <v>-5.082233576</v>
+        <v>-5.188206812000001</v>
       </c>
       <c r="P68">
-        <v>-20.328934304</v>
+        <v>-20.752827248</v>
       </c>
       <c r="Q68">
-        <v>-14.888934304</v>
+        <v>-15.312827248</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2987835774093524</v>
+        <v>0.306449746421757</v>
       </c>
       <c r="T68">
-        <v>2.770273864510418</v>
+        <v>2.854221557374371</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05467361017398198</v>
+        <v>0.05385758614153449</v>
       </c>
       <c r="W68">
-        <v>0.222907962720975</v>
+        <v>0.2231003811878262</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2733680508699099</v>
+        <v>0.2692879307076724</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2506056717150233</v>
+        <v>0.2525056717150234</v>
       </c>
       <c r="C69">
-        <v>-48.46573450343851</v>
+        <v>-51.58624031250775</v>
       </c>
       <c r="D69">
-        <v>95.0199654965615</v>
+        <v>94.14655968749224</v>
       </c>
       <c r="E69">
-        <v>144.0457</v>
+        <v>146.2928</v>
       </c>
       <c r="F69">
-        <v>150.5557</v>
+        <v>152.8028</v>
       </c>
       <c r="G69">
         <v>7.07</v>
@@ -6945,37 +6945,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M69">
-        <v>35.50103406</v>
+        <v>36.03090024</v>
       </c>
       <c r="N69">
-        <v>-25.94103406</v>
+        <v>-26.47090024</v>
       </c>
       <c r="O69">
-        <v>-5.188206812000001</v>
+        <v>-5.294180048000001</v>
       </c>
       <c r="P69">
-        <v>-20.752827248</v>
+        <v>-21.176720192</v>
       </c>
       <c r="Q69">
-        <v>-15.312827248</v>
+        <v>-15.736720192</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.306449746421757</v>
+        <v>0.3145950509974369</v>
       </c>
       <c r="T69">
-        <v>2.854221557374371</v>
+        <v>2.943415981042319</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05385758614153449</v>
+        <v>0.05306556281592369</v>
       </c>
       <c r="W69">
-        <v>0.2231003811878262</v>
+        <v>0.2232871402880052</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2692879307076724</v>
+        <v>0.2653278140796184</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2525056717150234</v>
+        <v>0.2544056717150233</v>
       </c>
       <c r="C70">
-        <v>-51.58624031250775</v>
+        <v>-54.69083599771906</v>
       </c>
       <c r="D70">
-        <v>94.14655968749224</v>
+        <v>93.28906400228095</v>
       </c>
       <c r="E70">
-        <v>146.2928</v>
+        <v>148.5399</v>
       </c>
       <c r="F70">
-        <v>152.8028</v>
+        <v>155.0499</v>
       </c>
       <c r="G70">
         <v>7.07</v>
@@ -7027,37 +7027,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M70">
-        <v>36.03090024</v>
+        <v>36.56076642</v>
       </c>
       <c r="N70">
-        <v>-26.47090024</v>
+        <v>-27.00076642</v>
       </c>
       <c r="O70">
-        <v>-5.294180048000001</v>
+        <v>-5.400153284000001</v>
       </c>
       <c r="P70">
-        <v>-21.176720192</v>
+        <v>-21.600613136</v>
       </c>
       <c r="Q70">
-        <v>-15.736720192</v>
+        <v>-16.160613136</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3145950509974369</v>
+        <v>0.3232658590941284</v>
       </c>
       <c r="T70">
-        <v>2.943415981042319</v>
+        <v>3.038364883656588</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05306556281592369</v>
+        <v>0.05229649668815667</v>
       </c>
       <c r="W70">
-        <v>0.2232871402880052</v>
+        <v>0.2234684860809326</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2653278140796184</v>
+        <v>0.2614824834407834</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2544056717150233</v>
+        <v>0.2563056717150233</v>
       </c>
       <c r="C71">
-        <v>-54.69083599771906</v>
+        <v>-57.77995236792066</v>
       </c>
       <c r="D71">
-        <v>93.28906400228095</v>
+        <v>92.44704763207935</v>
       </c>
       <c r="E71">
-        <v>148.5399</v>
+        <v>150.787</v>
       </c>
       <c r="F71">
-        <v>155.0499</v>
+        <v>157.297</v>
       </c>
       <c r="G71">
         <v>7.07</v>
@@ -7109,37 +7109,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M71">
-        <v>36.56076642</v>
+        <v>37.0906326</v>
       </c>
       <c r="N71">
-        <v>-27.00076642</v>
+        <v>-27.5306326</v>
       </c>
       <c r="O71">
-        <v>-5.400153284000001</v>
+        <v>-5.50612652</v>
       </c>
       <c r="P71">
-        <v>-21.600613136</v>
+        <v>-22.02450608</v>
       </c>
       <c r="Q71">
-        <v>-16.160613136</v>
+        <v>-16.58450608</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3232658590941284</v>
+        <v>0.3325147210639327</v>
       </c>
       <c r="T71">
-        <v>3.038364883656588</v>
+        <v>3.139643713111808</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05229649668815667</v>
+        <v>0.05154940387832586</v>
       </c>
       <c r="W71">
-        <v>0.2234684860809326</v>
+        <v>0.2236446505654908</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2614824834407834</v>
+        <v>0.2577470193916294</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2563056717150233</v>
+        <v>0.2582056717150233</v>
       </c>
       <c r="C72">
-        <v>-57.77995236792066</v>
+        <v>-60.85400481736662</v>
       </c>
       <c r="D72">
-        <v>92.44704763207935</v>
+        <v>91.62009518263341</v>
       </c>
       <c r="E72">
-        <v>150.787</v>
+        <v>153.0341</v>
       </c>
       <c r="F72">
-        <v>157.297</v>
+        <v>159.5441</v>
       </c>
       <c r="G72">
         <v>7.07</v>
@@ -7191,37 +7191,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M72">
-        <v>37.0906326</v>
+        <v>37.62049878000001</v>
       </c>
       <c r="N72">
-        <v>-27.5306326</v>
+        <v>-28.06049878000001</v>
       </c>
       <c r="O72">
-        <v>-5.50612652</v>
+        <v>-5.612099756000002</v>
       </c>
       <c r="P72">
-        <v>-22.02450608</v>
+        <v>-22.448399024</v>
       </c>
       <c r="Q72">
-        <v>-16.58450608</v>
+        <v>-17.008399024</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3325147210639327</v>
+        <v>0.3424014355833787</v>
       </c>
       <c r="T72">
-        <v>3.139643713111808</v>
+        <v>3.247907289426009</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05154940387832586</v>
+        <v>0.0508233559363776</v>
       </c>
       <c r="W72">
-        <v>0.2236446505654908</v>
+        <v>0.2238158526702022</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2577470193916294</v>
+        <v>0.2541167796818881</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2582056717150233</v>
+        <v>0.2601056717150234</v>
       </c>
       <c r="C73">
-        <v>-60.85400481736656</v>
+        <v>-63.91339400903337</v>
       </c>
       <c r="D73">
-        <v>91.62009518263342</v>
+        <v>90.8078059909666</v>
       </c>
       <c r="E73">
-        <v>153.0341</v>
+        <v>155.2812</v>
       </c>
       <c r="F73">
-        <v>159.5441</v>
+        <v>161.7912</v>
       </c>
       <c r="G73">
         <v>7.07</v>
@@ -7273,37 +7273,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M73">
-        <v>37.62049878</v>
+        <v>38.15036496</v>
       </c>
       <c r="N73">
-        <v>-28.06049878</v>
+        <v>-28.59036496</v>
       </c>
       <c r="O73">
-        <v>-5.612099756</v>
+        <v>-5.718072992</v>
       </c>
       <c r="P73">
-        <v>-22.448399024</v>
+        <v>-22.872291968</v>
       </c>
       <c r="Q73">
-        <v>-17.008399024</v>
+        <v>-17.432291968</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3424014355833785</v>
+        <v>0.3529943439970707</v>
       </c>
       <c r="T73">
-        <v>3.247907289426007</v>
+        <v>3.363903978334079</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05082335593637761</v>
+        <v>0.05011747599281682</v>
       </c>
       <c r="W73">
-        <v>0.2238158526702022</v>
+        <v>0.2239822991608938</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2541167796818881</v>
+        <v>0.2505873799640841</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2601056717150234</v>
+        <v>0.2620056717150233</v>
       </c>
       <c r="C74">
-        <v>-63.91339400903337</v>
+        <v>-66.958506521907</v>
       </c>
       <c r="D74">
-        <v>90.8078059909666</v>
+        <v>90.00979347809299</v>
       </c>
       <c r="E74">
-        <v>155.2812</v>
+        <v>157.5283</v>
       </c>
       <c r="F74">
-        <v>161.7912</v>
+        <v>164.0383</v>
       </c>
       <c r="G74">
         <v>7.07</v>
@@ -7355,37 +7355,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M74">
-        <v>38.15036496</v>
+        <v>38.68023114</v>
       </c>
       <c r="N74">
-        <v>-28.59036496</v>
+        <v>-29.12023114</v>
       </c>
       <c r="O74">
-        <v>-5.718072992</v>
+        <v>-5.824046228</v>
       </c>
       <c r="P74">
-        <v>-22.872291968</v>
+        <v>-23.296184912</v>
       </c>
       <c r="Q74">
-        <v>-17.432291968</v>
+        <v>-17.856184912</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3529943439970707</v>
+        <v>0.3643719122932584</v>
       </c>
       <c r="T74">
-        <v>3.363903978334079</v>
+        <v>3.488493014568674</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05011747599281682</v>
+        <v>0.04943093522579193</v>
       </c>
       <c r="W74">
-        <v>0.2239822991608938</v>
+        <v>0.2241441854737583</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2505873799640841</v>
+        <v>0.2471546761289597</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2620056717150233</v>
+        <v>0.2639056717150233</v>
       </c>
       <c r="C75">
-        <v>-66.958506521907</v>
+        <v>-69.98971546443752</v>
       </c>
       <c r="D75">
-        <v>90.00979347809299</v>
+        <v>89.22568453556246</v>
       </c>
       <c r="E75">
-        <v>157.5283</v>
+        <v>159.7754</v>
       </c>
       <c r="F75">
-        <v>164.0383</v>
+        <v>166.2854</v>
       </c>
       <c r="G75">
         <v>7.07</v>
@@ -7437,37 +7437,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M75">
-        <v>38.68023114</v>
+        <v>39.21009732</v>
       </c>
       <c r="N75">
-        <v>-29.12023114</v>
+        <v>-29.65009732</v>
       </c>
       <c r="O75">
-        <v>-5.824046228</v>
+        <v>-5.930019464</v>
       </c>
       <c r="P75">
-        <v>-23.296184912</v>
+        <v>-23.720077856</v>
       </c>
       <c r="Q75">
-        <v>-17.856184912</v>
+        <v>-18.28007785599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3643719122932584</v>
+        <v>0.3766246781506914</v>
       </c>
       <c r="T75">
-        <v>3.488493014568674</v>
+        <v>3.622665822821315</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04943093522579193</v>
+        <v>0.04876294961463258</v>
       </c>
       <c r="W75">
-        <v>0.2241441854737583</v>
+        <v>0.2243016964808696</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2471546761289597</v>
+        <v>0.2438147480731629</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2639056717150233</v>
+        <v>0.2658056717150233</v>
       </c>
       <c r="C76">
-        <v>-69.98971546443752</v>
+        <v>-73.00738105620627</v>
       </c>
       <c r="D76">
-        <v>89.22568453556246</v>
+        <v>88.45511894379371</v>
       </c>
       <c r="E76">
-        <v>159.7754</v>
+        <v>162.0225</v>
       </c>
       <c r="F76">
-        <v>166.2854</v>
+        <v>168.5325</v>
       </c>
       <c r="G76">
         <v>7.07</v>
@@ -7519,37 +7519,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M76">
-        <v>39.21009732</v>
+        <v>39.73996349999999</v>
       </c>
       <c r="N76">
-        <v>-29.65009732</v>
+        <v>-30.1799635</v>
       </c>
       <c r="O76">
-        <v>-5.930019464</v>
+        <v>-6.0359927</v>
       </c>
       <c r="P76">
-        <v>-23.720077856</v>
+        <v>-24.1439708</v>
       </c>
       <c r="Q76">
-        <v>-18.28007785599999</v>
+        <v>-18.7039708</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3766246781506914</v>
+        <v>0.3898576652767192</v>
       </c>
       <c r="T76">
-        <v>3.622665822821315</v>
+        <v>3.767572455734169</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04876294961463258</v>
+        <v>0.04811277695310415</v>
       </c>
       <c r="W76">
-        <v>0.2243016964808696</v>
+        <v>0.224455007194458</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2438147480731629</v>
+        <v>0.2405638847655207</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2658056717150233</v>
+        <v>0.2677056717150233</v>
       </c>
       <c r="C77">
-        <v>-73.00738105620627</v>
+        <v>-76.01185117971099</v>
       </c>
       <c r="D77">
-        <v>88.45511894379371</v>
+        <v>87.69774882028899</v>
       </c>
       <c r="E77">
-        <v>162.0225</v>
+        <v>164.2696</v>
       </c>
       <c r="F77">
-        <v>168.5325</v>
+        <v>170.7796</v>
       </c>
       <c r="G77">
         <v>7.07</v>
@@ -7601,37 +7601,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M77">
-        <v>39.73996349999999</v>
+        <v>40.26982968</v>
       </c>
       <c r="N77">
-        <v>-30.1799635</v>
+        <v>-30.70982968</v>
       </c>
       <c r="O77">
-        <v>-6.0359927</v>
+        <v>-6.141965936000001</v>
       </c>
       <c r="P77">
-        <v>-24.1439708</v>
+        <v>-24.567863744</v>
       </c>
       <c r="Q77">
-        <v>-18.7039708</v>
+        <v>-19.127863744</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3898576652767192</v>
+        <v>0.4041934013299158</v>
       </c>
       <c r="T77">
-        <v>3.767572455734169</v>
+        <v>3.924554641389759</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04811277695310415</v>
+        <v>0.04747971409845803</v>
       </c>
       <c r="W77">
-        <v>0.224455007194458</v>
+        <v>0.2246042834155836</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2405638847655207</v>
+        <v>0.2373985704922902</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2677056717150233</v>
+        <v>0.2696056717150234</v>
       </c>
       <c r="C78">
-        <v>-76.01185117971099</v>
+        <v>-79.00346190404474</v>
       </c>
       <c r="D78">
-        <v>87.69774882028899</v>
+        <v>86.95323809595523</v>
       </c>
       <c r="E78">
-        <v>164.2696</v>
+        <v>166.5167</v>
       </c>
       <c r="F78">
-        <v>170.7796</v>
+        <v>173.0267</v>
       </c>
       <c r="G78">
         <v>7.07</v>
@@ -7683,37 +7683,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M78">
-        <v>40.26982968</v>
+        <v>40.79969585999999</v>
       </c>
       <c r="N78">
-        <v>-30.70982968</v>
+        <v>-31.23969585999999</v>
       </c>
       <c r="O78">
-        <v>-6.141965936000001</v>
+        <v>-6.247939171999999</v>
       </c>
       <c r="P78">
-        <v>-24.567863744</v>
+        <v>-24.991756688</v>
       </c>
       <c r="Q78">
-        <v>-19.127863744</v>
+        <v>-19.55175668799999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4041934013299158</v>
+        <v>0.4197757231268687</v>
       </c>
       <c r="T78">
-        <v>3.924554641389759</v>
+        <v>4.095187451884966</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04747971409845803</v>
+        <v>0.04686309443484171</v>
       </c>
       <c r="W78">
-        <v>0.2246042834155836</v>
+        <v>0.2247496823322643</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2373985704922902</v>
+        <v>0.2343154721742086</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2696056717150234</v>
+        <v>0.2715056717150234</v>
       </c>
       <c r="C79">
-        <v>-79.00346190404474</v>
+        <v>-81.98253798212448</v>
       </c>
       <c r="D79">
-        <v>86.95323809595523</v>
+        <v>86.2212620178755</v>
       </c>
       <c r="E79">
-        <v>166.5167</v>
+        <v>168.7638</v>
       </c>
       <c r="F79">
-        <v>173.0267</v>
+        <v>175.2738</v>
       </c>
       <c r="G79">
         <v>7.07</v>
@@ -7765,37 +7765,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M79">
-        <v>40.79969585999999</v>
+        <v>41.32956204</v>
       </c>
       <c r="N79">
-        <v>-31.23969585999999</v>
+        <v>-31.76956204</v>
       </c>
       <c r="O79">
-        <v>-6.247939171999999</v>
+        <v>-6.353912408</v>
       </c>
       <c r="P79">
-        <v>-24.991756688</v>
+        <v>-25.415649632</v>
       </c>
       <c r="Q79">
-        <v>-19.55175668799999</v>
+        <v>-19.975649632</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4197757231268687</v>
+        <v>0.4367746196326355</v>
       </c>
       <c r="T79">
-        <v>4.095187451884966</v>
+        <v>4.281332336061555</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04686309443484171</v>
+        <v>0.04626228553183091</v>
       </c>
       <c r="W79">
-        <v>0.2247496823322643</v>
+        <v>0.2248913530715943</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2343154721742086</v>
+        <v>0.2313114276591546</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2715056717150234</v>
+        <v>0.2734056717150233</v>
       </c>
       <c r="C80">
-        <v>-81.98253798212448</v>
+        <v>-84.94939332301544</v>
       </c>
       <c r="D80">
-        <v>86.2212620178755</v>
+        <v>85.50150667698455</v>
       </c>
       <c r="E80">
-        <v>168.7638</v>
+        <v>171.0109</v>
       </c>
       <c r="F80">
-        <v>175.2738</v>
+        <v>177.5209</v>
       </c>
       <c r="G80">
         <v>7.07</v>
@@ -7847,37 +7847,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M80">
-        <v>41.32956204</v>
+        <v>41.85942822</v>
       </c>
       <c r="N80">
-        <v>-31.76956204</v>
+        <v>-32.29942822</v>
       </c>
       <c r="O80">
-        <v>-6.353912408</v>
+        <v>-6.459885644</v>
       </c>
       <c r="P80">
-        <v>-25.415649632</v>
+        <v>-25.839542576</v>
       </c>
       <c r="Q80">
-        <v>-19.975649632</v>
+        <v>-20.39954257599999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4367746196326355</v>
+        <v>0.455392458662761</v>
       </c>
       <c r="T80">
-        <v>4.281332336061555</v>
+        <v>4.485205304445439</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04626228553183091</v>
+        <v>0.04567668698079508</v>
       </c>
       <c r="W80">
-        <v>0.2248913530715943</v>
+        <v>0.2250294372099285</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2313114276591546</v>
+        <v>0.2283834349039754</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2734056717150233</v>
+        <v>0.2753056717150233</v>
       </c>
       <c r="C81">
-        <v>-84.94939332301544</v>
+        <v>-87.90433144079404</v>
       </c>
       <c r="D81">
-        <v>85.50150667698455</v>
+        <v>84.79366855920595</v>
       </c>
       <c r="E81">
-        <v>171.0109</v>
+        <v>173.258</v>
       </c>
       <c r="F81">
-        <v>177.5209</v>
+        <v>179.768</v>
       </c>
       <c r="G81">
         <v>7.07</v>
@@ -7929,37 +7929,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M81">
-        <v>41.85942822</v>
+        <v>42.3892944</v>
       </c>
       <c r="N81">
-        <v>-32.29942822</v>
+        <v>-32.82929440000001</v>
       </c>
       <c r="O81">
-        <v>-6.459885644</v>
+        <v>-6.565858880000002</v>
       </c>
       <c r="P81">
-        <v>-25.839542576</v>
+        <v>-26.26343552000001</v>
       </c>
       <c r="Q81">
-        <v>-20.39954257599999</v>
+        <v>-20.82343552000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.455392458662761</v>
+        <v>0.4758720815958991</v>
       </c>
       <c r="T81">
-        <v>4.485205304445439</v>
+        <v>4.709465569667712</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04567668698079508</v>
+        <v>0.04510572839353513</v>
       </c>
       <c r="W81">
-        <v>0.2250294372099285</v>
+        <v>0.2251640692448044</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2283834349039754</v>
+        <v>0.2255286419676755</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2753056717150233</v>
+        <v>0.2772056717150233</v>
       </c>
       <c r="C82">
-        <v>-87.90433144079404</v>
+        <v>-90.84764588129784</v>
       </c>
       <c r="D82">
-        <v>84.79366855920595</v>
+        <v>84.09745411870215</v>
       </c>
       <c r="E82">
-        <v>173.258</v>
+        <v>175.5051</v>
       </c>
       <c r="F82">
-        <v>179.768</v>
+        <v>182.0151</v>
       </c>
       <c r="G82">
         <v>7.07</v>
@@ -8011,37 +8011,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M82">
-        <v>42.3892944</v>
+        <v>42.91916058</v>
       </c>
       <c r="N82">
-        <v>-32.82929440000001</v>
+        <v>-33.35916057999999</v>
       </c>
       <c r="O82">
-        <v>-6.565858880000002</v>
+        <v>-6.671832115999999</v>
       </c>
       <c r="P82">
-        <v>-26.26343552000001</v>
+        <v>-26.687328464</v>
       </c>
       <c r="Q82">
-        <v>-20.82343552000001</v>
+        <v>-21.247328464</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4758720815958991</v>
+        <v>0.4985074543114727</v>
       </c>
       <c r="T82">
-        <v>4.709465569667712</v>
+        <v>4.957332178597591</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04510572839353513</v>
+        <v>0.04454886754917051</v>
       </c>
       <c r="W82">
-        <v>0.2251640692448044</v>
+        <v>0.2252953770319056</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2255286419676755</v>
+        <v>0.2227443377458526</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2772056717150233</v>
+        <v>0.2791056717150233</v>
       </c>
       <c r="C83">
-        <v>-90.84764588129784</v>
+        <v>-93.77962062802374</v>
       </c>
       <c r="D83">
-        <v>84.09745411870215</v>
+        <v>83.41257937197626</v>
       </c>
       <c r="E83">
-        <v>175.5051</v>
+        <v>177.7522</v>
       </c>
       <c r="F83">
-        <v>182.0151</v>
+        <v>184.2622</v>
       </c>
       <c r="G83">
         <v>7.07</v>
@@ -8093,37 +8093,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M83">
-        <v>42.91916058</v>
+        <v>43.44902676</v>
       </c>
       <c r="N83">
-        <v>-33.35916057999999</v>
+        <v>-33.88902676000001</v>
       </c>
       <c r="O83">
-        <v>-6.671832115999999</v>
+        <v>-6.777805352000001</v>
       </c>
       <c r="P83">
-        <v>-26.687328464</v>
+        <v>-27.11122140800001</v>
       </c>
       <c r="Q83">
-        <v>-21.247328464</v>
+        <v>-21.671221408</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4985074543114727</v>
+        <v>0.5236578684398878</v>
       </c>
       <c r="T83">
-        <v>4.957332178597591</v>
+        <v>5.232739521853013</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04454886754917051</v>
+        <v>0.04400558867661964</v>
       </c>
       <c r="W83">
-        <v>0.2252953770319056</v>
+        <v>0.2254234821900531</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2227443377458526</v>
+        <v>0.2200279433830981</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2791056717150233</v>
+        <v>0.2810056717150233</v>
       </c>
       <c r="C84">
-        <v>-93.77962062802374</v>
+        <v>-96.70053048835217</v>
       </c>
       <c r="D84">
-        <v>83.41257937197626</v>
+        <v>82.73876951164783</v>
       </c>
       <c r="E84">
-        <v>177.7522</v>
+        <v>179.9993</v>
       </c>
       <c r="F84">
-        <v>184.2622</v>
+        <v>186.5093</v>
       </c>
       <c r="G84">
         <v>7.07</v>
@@ -8175,37 +8175,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M84">
-        <v>43.44902676</v>
+        <v>43.97889294</v>
       </c>
       <c r="N84">
-        <v>-33.88902676000001</v>
+        <v>-34.41889294000001</v>
       </c>
       <c r="O84">
-        <v>-6.777805352000001</v>
+        <v>-6.883778588000002</v>
       </c>
       <c r="P84">
-        <v>-27.11122140800001</v>
+        <v>-27.535114352</v>
       </c>
       <c r="Q84">
-        <v>-21.671221408</v>
+        <v>-22.095114352</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5236578684398878</v>
+        <v>0.5517671548187048</v>
       </c>
       <c r="T84">
-        <v>5.232739521853013</v>
+        <v>5.540547729020838</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04400558867661964</v>
+        <v>0.04347540086123868</v>
       </c>
       <c r="W84">
-        <v>0.2254234821900531</v>
+        <v>0.2255485004769199</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2200279433830981</v>
+        <v>0.2173770043061933</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2810056717150233</v>
+        <v>0.2829056717150233</v>
       </c>
       <c r="C85">
-        <v>-96.70053048835217</v>
+        <v>-99.61064146120262</v>
       </c>
       <c r="D85">
-        <v>82.73876951164783</v>
+        <v>82.0757585387974</v>
       </c>
       <c r="E85">
-        <v>179.9993</v>
+        <v>182.2464</v>
       </c>
       <c r="F85">
-        <v>186.5093</v>
+        <v>188.7564</v>
       </c>
       <c r="G85">
         <v>7.07</v>
@@ -8257,37 +8257,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M85">
-        <v>43.97889294</v>
+        <v>44.50875912000001</v>
       </c>
       <c r="N85">
-        <v>-34.41889294000001</v>
+        <v>-34.94875912000001</v>
       </c>
       <c r="O85">
-        <v>-6.883778588000002</v>
+        <v>-6.989751824000002</v>
       </c>
       <c r="P85">
-        <v>-27.535114352</v>
+        <v>-27.959007296</v>
       </c>
       <c r="Q85">
-        <v>-22.095114352</v>
+        <v>-22.519007296</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5517671548187048</v>
+        <v>0.583390101994874</v>
       </c>
       <c r="T85">
-        <v>5.540547729020838</v>
+        <v>5.886831962084641</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04347540086123868</v>
+        <v>0.04295783656527155</v>
       </c>
       <c r="W85">
-        <v>0.2255485004769199</v>
+        <v>0.225670542137909</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2173770043061933</v>
+        <v>0.2147891828263578</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2829056717150233</v>
+        <v>0.2848056717150234</v>
       </c>
       <c r="C86">
-        <v>-99.61064146120259</v>
+        <v>-102.5102110871521</v>
       </c>
       <c r="D86">
-        <v>82.0757585387974</v>
+        <v>81.42328891284788</v>
       </c>
       <c r="E86">
-        <v>182.2464</v>
+        <v>184.4935</v>
       </c>
       <c r="F86">
-        <v>188.7564</v>
+        <v>191.0035</v>
       </c>
       <c r="G86">
         <v>7.07</v>
@@ -8339,37 +8339,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M86">
-        <v>44.50875912</v>
+        <v>45.03862529999999</v>
       </c>
       <c r="N86">
-        <v>-34.94875912000001</v>
+        <v>-35.47862529999999</v>
       </c>
       <c r="O86">
-        <v>-6.989751824000002</v>
+        <v>-7.095725059999999</v>
       </c>
       <c r="P86">
-        <v>-27.959007296</v>
+        <v>-28.38290023999999</v>
       </c>
       <c r="Q86">
-        <v>-22.519007296</v>
+        <v>-22.94290023999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5833901019948736</v>
+        <v>0.6192294421278652</v>
       </c>
       <c r="T86">
-        <v>5.886831962084638</v>
+        <v>6.279287426223614</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04295783656527155</v>
+        <v>0.04245245025273896</v>
       </c>
       <c r="W86">
-        <v>0.225670542137909</v>
+        <v>0.2257897122304042</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2147891828263577</v>
+        <v>0.2122622512636948</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2848056717150234</v>
+        <v>0.2867056717150233</v>
       </c>
       <c r="C87">
-        <v>-102.5102110871521</v>
+        <v>-105.3994887819862</v>
       </c>
       <c r="D87">
-        <v>81.42328891284788</v>
+        <v>80.78111121801383</v>
       </c>
       <c r="E87">
-        <v>184.4935</v>
+        <v>186.7406</v>
       </c>
       <c r="F87">
-        <v>191.0035</v>
+        <v>193.2506</v>
       </c>
       <c r="G87">
         <v>7.07</v>
@@ -8421,37 +8421,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M87">
-        <v>45.03862529999999</v>
+        <v>45.56849148</v>
       </c>
       <c r="N87">
-        <v>-35.47862529999999</v>
+        <v>-36.00849148</v>
       </c>
       <c r="O87">
-        <v>-7.095725059999999</v>
+        <v>-7.201698296000001</v>
       </c>
       <c r="P87">
-        <v>-28.38290023999999</v>
+        <v>-28.806793184</v>
       </c>
       <c r="Q87">
-        <v>-22.94290023999999</v>
+        <v>-23.366793184</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6192294421278652</v>
+        <v>0.6601886879941412</v>
       </c>
       <c r="T87">
-        <v>6.279287426223614</v>
+        <v>6.727807956668157</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04245245025273896</v>
+        <v>0.04195881711026524</v>
       </c>
       <c r="W87">
-        <v>0.2257897122304042</v>
+        <v>0.2259061109253994</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2122622512636948</v>
+        <v>0.2097940855513262</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2867056717150233</v>
+        <v>0.2886056717150233</v>
       </c>
       <c r="C88">
-        <v>-105.3994887819862</v>
+        <v>-108.2787161545888</v>
       </c>
       <c r="D88">
-        <v>80.78111121801383</v>
+        <v>80.14898384541121</v>
       </c>
       <c r="E88">
-        <v>186.7406</v>
+        <v>188.9877</v>
       </c>
       <c r="F88">
-        <v>193.2506</v>
+        <v>195.4977</v>
       </c>
       <c r="G88">
         <v>7.07</v>
@@ -8503,37 +8503,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M88">
-        <v>45.56849148</v>
+        <v>46.09835766</v>
       </c>
       <c r="N88">
-        <v>-36.00849148</v>
+        <v>-36.53835766</v>
       </c>
       <c r="O88">
-        <v>-7.201698296000001</v>
+        <v>-7.307671532000001</v>
       </c>
       <c r="P88">
-        <v>-28.806793184</v>
+        <v>-29.230686128</v>
       </c>
       <c r="Q88">
-        <v>-23.366793184</v>
+        <v>-23.790686128</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6601886879941412</v>
+        <v>0.7074493563013828</v>
       </c>
       <c r="T88">
-        <v>6.727807956668157</v>
+        <v>7.24533164564263</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04195881711026524</v>
+        <v>0.04147653185612427</v>
       </c>
       <c r="W88">
-        <v>0.2259061109253994</v>
+        <v>0.2260198337883259</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2097940855513262</v>
+        <v>0.2073826592806213</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2886056717150233</v>
+        <v>0.2905056717150233</v>
       </c>
       <c r="C89">
-        <v>-108.2787161545888</v>
+        <v>-111.148127310023</v>
       </c>
       <c r="D89">
-        <v>80.14898384541121</v>
+        <v>79.52667268997699</v>
       </c>
       <c r="E89">
-        <v>188.9877</v>
+        <v>191.2348</v>
       </c>
       <c r="F89">
-        <v>195.4977</v>
+        <v>197.7448</v>
       </c>
       <c r="G89">
         <v>7.07</v>
@@ -8585,37 +8585,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M89">
-        <v>46.09835766</v>
+        <v>46.62822384</v>
       </c>
       <c r="N89">
-        <v>-36.53835766</v>
+        <v>-37.06822384</v>
       </c>
       <c r="O89">
-        <v>-7.307671532000001</v>
+        <v>-7.413644768000001</v>
       </c>
       <c r="P89">
-        <v>-29.230686128</v>
+        <v>-29.654579072</v>
       </c>
       <c r="Q89">
-        <v>-23.790686128</v>
+        <v>-24.214579072</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7074493563013828</v>
+        <v>0.7625868026598316</v>
       </c>
       <c r="T89">
-        <v>7.24533164564263</v>
+        <v>7.849109282779517</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04147653185612427</v>
+        <v>0.04100520763048648</v>
       </c>
       <c r="W89">
-        <v>0.2260198337883259</v>
+        <v>0.2261309720407313</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2073826592806213</v>
+        <v>0.2050260381524324</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2905056717150233</v>
+        <v>0.2924056717150233</v>
       </c>
       <c r="C90">
-        <v>-111.148127310023</v>
+        <v>-114.0079491386011</v>
       </c>
       <c r="D90">
-        <v>79.52667268997699</v>
+        <v>78.91395086139892</v>
       </c>
       <c r="E90">
-        <v>191.2348</v>
+        <v>193.4819</v>
       </c>
       <c r="F90">
-        <v>197.7448</v>
+        <v>199.9919</v>
       </c>
       <c r="G90">
         <v>7.07</v>
@@ -8667,37 +8667,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M90">
-        <v>46.62822384</v>
+        <v>47.15809002</v>
       </c>
       <c r="N90">
-        <v>-37.06822384</v>
+        <v>-37.59809002</v>
       </c>
       <c r="O90">
-        <v>-7.413644768000001</v>
+        <v>-7.519618004000001</v>
       </c>
       <c r="P90">
-        <v>-29.654579072</v>
+        <v>-30.078472016</v>
       </c>
       <c r="Q90">
-        <v>-24.214579072</v>
+        <v>-24.638472016</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7625868026598316</v>
+        <v>0.8277492392652709</v>
       </c>
       <c r="T90">
-        <v>7.849109282779517</v>
+        <v>8.562664672123111</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04100520763048648</v>
+        <v>0.04054447496048103</v>
       </c>
       <c r="W90">
-        <v>0.2261309720407313</v>
+        <v>0.2262396128043186</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2050260381524324</v>
+        <v>0.2027223748024051</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2924056717150233</v>
+        <v>0.2943056717150234</v>
       </c>
       <c r="C91">
-        <v>-114.0079491386011</v>
+        <v>-116.8584015916936</v>
       </c>
       <c r="D91">
-        <v>78.91395086139892</v>
+        <v>78.3105984083064</v>
       </c>
       <c r="E91">
-        <v>193.4819</v>
+        <v>195.729</v>
       </c>
       <c r="F91">
-        <v>199.9919</v>
+        <v>202.239</v>
       </c>
       <c r="G91">
         <v>7.07</v>
@@ -8749,37 +8749,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M91">
-        <v>47.15809002</v>
+        <v>47.6879562</v>
       </c>
       <c r="N91">
-        <v>-37.59809002</v>
+        <v>-38.1279562</v>
       </c>
       <c r="O91">
-        <v>-7.519618004000001</v>
+        <v>-7.62559124</v>
       </c>
       <c r="P91">
-        <v>-30.078472016</v>
+        <v>-30.50236496</v>
       </c>
       <c r="Q91">
-        <v>-24.638472016</v>
+        <v>-25.06236496</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8277492392652709</v>
+        <v>0.9059441631917982</v>
       </c>
       <c r="T91">
-        <v>8.562664672123111</v>
+        <v>9.418931139335424</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04054447496048103</v>
+        <v>0.04009398079425346</v>
       </c>
       <c r="W91">
-        <v>0.2262396128043186</v>
+        <v>0.226345839328715</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2027223748024051</v>
+        <v>0.2004699039712672</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2943056717150234</v>
+        <v>0.2962056717150233</v>
       </c>
       <c r="C92">
-        <v>-116.8584015916936</v>
+        <v>-119.6996979449819</v>
       </c>
       <c r="D92">
-        <v>78.3105984083064</v>
+        <v>77.71640205501808</v>
       </c>
       <c r="E92">
-        <v>195.729</v>
+        <v>197.9761</v>
       </c>
       <c r="F92">
-        <v>202.239</v>
+        <v>204.4861</v>
       </c>
       <c r="G92">
         <v>7.07</v>
@@ -8831,37 +8831,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M92">
-        <v>47.6879562</v>
+        <v>48.21782238</v>
       </c>
       <c r="N92">
-        <v>-38.1279562</v>
+        <v>-38.65782238</v>
       </c>
       <c r="O92">
-        <v>-7.62559124</v>
+        <v>-7.731564476</v>
       </c>
       <c r="P92">
-        <v>-30.50236496</v>
+        <v>-30.926257904</v>
       </c>
       <c r="Q92">
-        <v>-25.06236496</v>
+        <v>-25.486257904</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9059441631917982</v>
+        <v>1.001515736879776</v>
       </c>
       <c r="T92">
-        <v>9.418931139335424</v>
+        <v>10.46547904370603</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04009398079425346</v>
+        <v>0.0396533875987122</v>
       </c>
       <c r="W92">
-        <v>0.226345839328715</v>
+        <v>0.2264497312042237</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2004699039712672</v>
+        <v>0.1982669379935611</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2962056717150233</v>
+        <v>0.2981056717150233</v>
       </c>
       <c r="C93">
-        <v>-119.6996979449819</v>
+        <v>-122.5320450498164</v>
       </c>
       <c r="D93">
-        <v>77.71640205501808</v>
+        <v>77.13115495018361</v>
       </c>
       <c r="E93">
-        <v>197.9761</v>
+        <v>200.2232</v>
       </c>
       <c r="F93">
-        <v>204.4861</v>
+        <v>206.7332</v>
       </c>
       <c r="G93">
         <v>7.07</v>
@@ -8913,37 +8913,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M93">
-        <v>48.21782238</v>
+        <v>48.74768856</v>
       </c>
       <c r="N93">
-        <v>-38.65782238</v>
+        <v>-39.18768856</v>
       </c>
       <c r="O93">
-        <v>-7.731564476</v>
+        <v>-7.837537712</v>
       </c>
       <c r="P93">
-        <v>-30.926257904</v>
+        <v>-31.350150848</v>
       </c>
       <c r="Q93">
-        <v>-25.486257904</v>
+        <v>-25.910150848</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.001515736879776</v>
+        <v>1.120980203989748</v>
       </c>
       <c r="T93">
-        <v>10.46547904370603</v>
+        <v>11.77366392416928</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0396533875987122</v>
+        <v>0.03922237251611751</v>
       </c>
       <c r="W93">
-        <v>0.2264497312042237</v>
+        <v>0.2265513645606995</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1982669379935611</v>
+        <v>0.1961118625805875</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2981056717150233</v>
+        <v>0.3000056717150233</v>
       </c>
       <c r="C94">
-        <v>-122.5320450498164</v>
+        <v>-125.3556435733019</v>
       </c>
       <c r="D94">
-        <v>77.13115495018361</v>
+        <v>76.5546564266981</v>
       </c>
       <c r="E94">
-        <v>200.2232</v>
+        <v>202.4703</v>
       </c>
       <c r="F94">
-        <v>206.7332</v>
+        <v>208.9803</v>
       </c>
       <c r="G94">
         <v>7.07</v>
@@ -8995,37 +8995,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M94">
-        <v>48.74768856</v>
+        <v>49.27755474</v>
       </c>
       <c r="N94">
-        <v>-39.18768856</v>
+        <v>-39.71755474</v>
       </c>
       <c r="O94">
-        <v>-7.837537712</v>
+        <v>-7.943510948</v>
       </c>
       <c r="P94">
-        <v>-31.350150848</v>
+        <v>-31.774043792</v>
       </c>
       <c r="Q94">
-        <v>-25.910150848</v>
+        <v>-26.334043792</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.120980203989748</v>
+        <v>1.274577375988283</v>
       </c>
       <c r="T94">
-        <v>11.77366392416928</v>
+        <v>13.45561591333632</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03922237251611751</v>
+        <v>0.03880062657508399</v>
       </c>
       <c r="W94">
-        <v>0.2265513645606995</v>
+        <v>0.2266508122535952</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1961118625805875</v>
+        <v>0.19400313287542</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3000056717150233</v>
+        <v>0.3019056717150234</v>
       </c>
       <c r="C95">
-        <v>-125.3556435733019</v>
+        <v>-128.1706882276966</v>
       </c>
       <c r="D95">
-        <v>76.5546564266981</v>
+        <v>75.98671177230334</v>
       </c>
       <c r="E95">
-        <v>202.4703</v>
+        <v>204.7174</v>
       </c>
       <c r="F95">
-        <v>208.9803</v>
+        <v>211.2274</v>
       </c>
       <c r="G95">
         <v>7.07</v>
@@ -9077,37 +9077,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M95">
-        <v>49.27755474</v>
+        <v>49.80742092</v>
       </c>
       <c r="N95">
-        <v>-39.71755474</v>
+        <v>-40.24742092</v>
       </c>
       <c r="O95">
-        <v>-7.943510948</v>
+        <v>-8.049484183999999</v>
       </c>
       <c r="P95">
-        <v>-31.774043792</v>
+        <v>-32.197936736</v>
       </c>
       <c r="Q95">
-        <v>-26.334043792</v>
+        <v>-26.75793673599999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.274577375988283</v>
+        <v>1.479373605319664</v>
       </c>
       <c r="T95">
-        <v>13.45561591333632</v>
+        <v>15.69821856555905</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03880062657508399</v>
+        <v>0.0383878539519448</v>
       </c>
       <c r="W95">
-        <v>0.2266508122535952</v>
+        <v>0.2267481440381314</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.19400313287542</v>
+        <v>0.1919392697597241</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3019056717150234</v>
+        <v>0.3038056717150234</v>
       </c>
       <c r="C96">
-        <v>-128.1706882276966</v>
+        <v>-130.9773679896751</v>
       </c>
       <c r="D96">
-        <v>75.98671177230334</v>
+        <v>75.42713201032491</v>
       </c>
       <c r="E96">
-        <v>204.7174</v>
+        <v>206.9645</v>
       </c>
       <c r="F96">
-        <v>211.2274</v>
+        <v>213.4745</v>
       </c>
       <c r="G96">
         <v>7.07</v>
@@ -9159,37 +9159,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M96">
-        <v>49.80742092</v>
+        <v>50.3372871</v>
       </c>
       <c r="N96">
-        <v>-40.24742092</v>
+        <v>-40.77728710000001</v>
       </c>
       <c r="O96">
-        <v>-8.049484183999999</v>
+        <v>-8.155457420000003</v>
       </c>
       <c r="P96">
-        <v>-32.197936736</v>
+        <v>-32.62182968</v>
       </c>
       <c r="Q96">
-        <v>-26.75793673599999</v>
+        <v>-27.18182968</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.479373605319664</v>
+        <v>1.766088326383598</v>
       </c>
       <c r="T96">
-        <v>15.69821856555905</v>
+        <v>18.83786227867087</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0383878539519448</v>
+        <v>0.03798377127876643</v>
       </c>
       <c r="W96">
-        <v>0.2267481440381314</v>
+        <v>0.2268434267324669</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1919392697597241</v>
+        <v>0.189918856393832</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3038056717150234</v>
+        <v>0.3057056717150233</v>
       </c>
       <c r="C97">
-        <v>-130.9773679896751</v>
+        <v>-133.7758663099732</v>
       </c>
       <c r="D97">
-        <v>75.42713201032491</v>
+        <v>74.87573369002682</v>
       </c>
       <c r="E97">
-        <v>206.9645</v>
+        <v>209.2116</v>
       </c>
       <c r="F97">
-        <v>213.4745</v>
+        <v>215.7216</v>
       </c>
       <c r="G97">
         <v>7.07</v>
@@ -9241,37 +9241,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M97">
-        <v>50.3372871</v>
+        <v>50.86715328</v>
       </c>
       <c r="N97">
-        <v>-40.77728710000001</v>
+        <v>-41.30715328000001</v>
       </c>
       <c r="O97">
-        <v>-8.155457420000003</v>
+        <v>-8.261430656000002</v>
       </c>
       <c r="P97">
-        <v>-32.62182968</v>
+        <v>-33.04572262400001</v>
       </c>
       <c r="Q97">
-        <v>-27.18182968</v>
+        <v>-27.60572262400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.766088326383598</v>
+        <v>2.196160407979499</v>
       </c>
       <c r="T97">
-        <v>18.83786227867087</v>
+        <v>23.5473278483386</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03798377127876643</v>
+        <v>0.03758810699461261</v>
       </c>
       <c r="W97">
-        <v>0.2268434267324669</v>
+        <v>0.2269367243706704</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.189918856393832</v>
+        <v>0.187940534973063</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3057056717150233</v>
+        <v>0.3076056717150233</v>
       </c>
       <c r="C98">
-        <v>-133.7758663099731</v>
+        <v>-136.5663613139054</v>
       </c>
       <c r="D98">
-        <v>74.87573369002682</v>
+        <v>74.33233868609463</v>
       </c>
       <c r="E98">
-        <v>209.2116</v>
+        <v>211.4587</v>
       </c>
       <c r="F98">
-        <v>215.7216</v>
+        <v>217.9687</v>
       </c>
       <c r="G98">
         <v>7.07</v>
@@ -9323,37 +9323,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M98">
-        <v>50.86715328</v>
+        <v>51.39701946</v>
       </c>
       <c r="N98">
-        <v>-41.30715327999999</v>
+        <v>-41.83701945999999</v>
       </c>
       <c r="O98">
-        <v>-8.261430656</v>
+        <v>-8.367403891999999</v>
       </c>
       <c r="P98">
-        <v>-33.04572262399999</v>
+        <v>-33.46961556799999</v>
       </c>
       <c r="Q98">
-        <v>-27.60572262399999</v>
+        <v>-28.02961556799999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.196160407979493</v>
+        <v>2.912947210639324</v>
       </c>
       <c r="T98">
-        <v>23.54732784833853</v>
+        <v>31.39643713111805</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03758810699461262</v>
+        <v>0.0372006007369362</v>
       </c>
       <c r="W98">
-        <v>0.2269367243706704</v>
+        <v>0.2270280983462304</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1879405349730632</v>
+        <v>0.186003003684681</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3076056717150233</v>
+        <v>0.3095056717150233</v>
       </c>
       <c r="C99">
-        <v>-136.5663613139054</v>
+        <v>-139.3490259932126</v>
       </c>
       <c r="D99">
-        <v>74.33233868609463</v>
+        <v>73.79677400678732</v>
       </c>
       <c r="E99">
-        <v>211.4587</v>
+        <v>213.7058</v>
       </c>
       <c r="F99">
-        <v>217.9687</v>
+        <v>220.2158</v>
       </c>
       <c r="G99">
         <v>7.07</v>
@@ -9405,37 +9405,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M99">
-        <v>51.39701946</v>
+        <v>51.92688563999999</v>
       </c>
       <c r="N99">
-        <v>-41.83701945999999</v>
+        <v>-42.36688563999999</v>
       </c>
       <c r="O99">
-        <v>-8.367403891999999</v>
+        <v>-8.473377127999999</v>
       </c>
       <c r="P99">
-        <v>-33.46961556799999</v>
+        <v>-33.893508512</v>
       </c>
       <c r="Q99">
-        <v>-28.02961556799999</v>
+        <v>-28.453508512</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.912947210639324</v>
+        <v>4.346520815958985</v>
       </c>
       <c r="T99">
-        <v>31.39643713111805</v>
+        <v>47.09465569667706</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0372006007369362</v>
+        <v>0.03682100277023276</v>
       </c>
       <c r="W99">
-        <v>0.2270280983462304</v>
+        <v>0.2271176075467791</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.186003003684681</v>
+        <v>0.1841050138511638</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3095056717150233</v>
+        <v>0.3114056717150233</v>
       </c>
       <c r="C100">
-        <v>-139.3490259932126</v>
+        <v>-142.1240283896771</v>
       </c>
       <c r="D100">
-        <v>73.79677400678732</v>
+        <v>73.26887161032292</v>
       </c>
       <c r="E100">
-        <v>213.7058</v>
+        <v>215.9529</v>
       </c>
       <c r="F100">
-        <v>220.2158</v>
+        <v>222.4629</v>
       </c>
       <c r="G100">
         <v>7.07</v>
@@ -9487,37 +9487,37 @@
         <v>9.559999999999999</v>
       </c>
       <c r="M100">
-        <v>51.92688563999999</v>
+        <v>52.45675182</v>
       </c>
       <c r="N100">
-        <v>-42.36688563999999</v>
+        <v>-42.89675182000001</v>
       </c>
       <c r="O100">
-        <v>-8.473377127999999</v>
+        <v>-8.579350364000002</v>
       </c>
       <c r="P100">
-        <v>-33.893508512</v>
+        <v>-34.31740145600001</v>
       </c>
       <c r="Q100">
-        <v>-28.453508512</v>
+        <v>-28.877401456</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.346520815958985</v>
+        <v>8.64724163191797</v>
       </c>
       <c r="T100">
-        <v>47.09465569667706</v>
+        <v>94.18931139335412</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03682100277023276</v>
+        <v>0.03644907344932132</v>
       </c>
       <c r="W100">
-        <v>0.2271176075467791</v>
+        <v>0.22720530848065</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1841050138511638</v>
+        <v>0.1822453672466066</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3114056717150233</v>
-      </c>
-      <c r="C101">
-        <v>-142.1240283896771</v>
-      </c>
-      <c r="D101">
-        <v>73.26887161032292</v>
-      </c>
-      <c r="E101">
-        <v>215.9529</v>
-      </c>
-      <c r="F101">
-        <v>222.4629</v>
-      </c>
-      <c r="G101">
-        <v>7.07</v>
-      </c>
-      <c r="H101">
-        <v>218.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>15</v>
-      </c>
-      <c r="K101">
-        <v>5.44</v>
-      </c>
-      <c r="L101">
-        <v>9.559999999999999</v>
-      </c>
-      <c r="M101">
-        <v>52.45675182</v>
-      </c>
-      <c r="N101">
-        <v>-42.89675182000001</v>
-      </c>
-      <c r="O101">
-        <v>-8.579350364000002</v>
-      </c>
-      <c r="P101">
-        <v>-34.31740145600001</v>
-      </c>
-      <c r="Q101">
-        <v>-28.877401456</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.64724163191797</v>
-      </c>
-      <c r="T101">
-        <v>94.18931139335412</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03644907344932132</v>
-      </c>
-      <c r="W101">
-        <v>0.22720530848065</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1822453672466066</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
